--- a/backend/scripts/table_exams.xlsx
+++ b/backend/scripts/table_exams.xlsx
@@ -636,10 +636,10 @@
         </is>
       </c>
       <c r="Y2" t="n">
-        <v>0.3796222805976868</v>
+        <v>18.8962345123291</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.3796370923519135</v>
+        <v>23.27688217163086</v>
       </c>
     </row>
     <row r="3">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="Y3" t="n">
-        <v>0.3796044588088989</v>
+        <v>20.38213920593262</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3796340823173523</v>
+        <v>23.55276489257812</v>
       </c>
     </row>
     <row r="4">
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Y4" t="n">
-        <v>0.3795927166938782</v>
+        <v>20.74859237670898</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.3796301186084747</v>
+        <v>23.45502662658691</v>
       </c>
     </row>
     <row r="5">
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="Y5" t="n">
-        <v>0.3795721530914307</v>
+        <v>21.20321655273438</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.3796277940273285</v>
+        <v>24.76762199401855</v>
       </c>
     </row>
     <row r="6">
@@ -991,7 +991,7 @@
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>0.3796238005161285</v>
+        <v>25.27677726745605</v>
       </c>
     </row>
     <row r="7">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="n">
-        <v>0.3793249428272247</v>
+        <v>14.60817050933838</v>
       </c>
     </row>
     <row r="8">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="n">
-        <v>0.3790097832679749</v>
+        <v>15.48456573486328</v>
       </c>
     </row>
     <row r="9">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="n">
-        <v>0.3787857890129089</v>
+        <v>15.73067378997803</v>
       </c>
     </row>
     <row r="10">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="n">
-        <v>0.3785094618797302</v>
+        <v>16.08383941650391</v>
       </c>
     </row>
     <row r="11">
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="Y11" t="n">
-        <v>0.3796374499797821</v>
+        <v>23.14578819274902</v>
       </c>
       <c r="Z11" t="inlineStr"/>
     </row>
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="Y12" t="n">
-        <v>0.379634827375412</v>
+        <v>24.01560020446777</v>
       </c>
       <c r="Z12" t="inlineStr"/>
     </row>
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="Y13" t="n">
-        <v>0.3796295523643494</v>
+        <v>22.9150218963623</v>
       </c>
       <c r="Z13" t="inlineStr"/>
     </row>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="Y14" t="n">
-        <v>0.3796268701553345</v>
+        <v>24.82825660705566</v>
       </c>
       <c r="Z14" t="inlineStr"/>
     </row>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="Y15" t="n">
-        <v>0.3796231150627136</v>
+        <v>24.41648292541504</v>
       </c>
       <c r="Z15" t="inlineStr"/>
     </row>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>0.3796156346797943</v>
+        <v>23.87802505493164</v>
       </c>
       <c r="Z16" t="inlineStr"/>
     </row>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="Y17" t="n">
-        <v>0.3796022236347198</v>
+        <v>23.24247932434082</v>
       </c>
       <c r="Z17" t="inlineStr"/>
     </row>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="Y18" t="n">
-        <v>0.3795937895774841</v>
+        <v>23.46785736083984</v>
       </c>
       <c r="Z18" t="inlineStr"/>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="n">
-        <v>0.3796345889568329</v>
+        <v>23.2201976776123</v>
       </c>
     </row>
     <row r="20">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="n">
-        <v>0.3796291351318359</v>
+        <v>23.00050926208496</v>
       </c>
     </row>
     <row r="21">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="n">
-        <v>0.3796199262142181</v>
+        <v>22.8978214263916</v>
       </c>
     </row>
     <row r="22">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="n">
-        <v>0.3795623481273651</v>
+        <v>22.4381046295166</v>
       </c>
     </row>
     <row r="23">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="n">
-        <v>0.3795478940010071</v>
+        <v>22.58504295349121</v>
       </c>
     </row>
     <row r="24">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="n">
-        <v>0.3796348571777344</v>
+        <v>22.33139991760254</v>
       </c>
     </row>
     <row r="25">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="n">
-        <v>0.3796296715736389</v>
+        <v>23.19303321838379</v>
       </c>
     </row>
     <row r="26">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="n">
-        <v>0.3796065151691437</v>
+        <v>21.75533676147461</v>
       </c>
     </row>
     <row r="27">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="n">
-        <v>0.3795960545539856</v>
+        <v>23.23283576965332</v>
       </c>
     </row>
     <row r="28">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="n">
-        <v>0.3795462548732758</v>
+        <v>21.66755867004395</v>
       </c>
     </row>
     <row r="29">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="n">
-        <v>0.3795295059680939</v>
+        <v>22.46603393554688</v>
       </c>
     </row>
     <row r="30">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="n">
-        <v>0.379503607749939</v>
+        <v>22.76629447937012</v>
       </c>
     </row>
     <row r="31">
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="Y31" t="n">
-        <v>0.3784109354019165</v>
+        <v>11.89662933349609</v>
       </c>
       <c r="Z31" t="inlineStr"/>
     </row>
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="Y32" t="n">
-        <v>0.3771820068359375</v>
+        <v>13.27876853942871</v>
       </c>
       <c r="Z32" t="inlineStr"/>
     </row>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="Y33" t="n">
-        <v>0.3710061013698578</v>
+        <v>12.86683177947998</v>
       </c>
       <c r="Z33" t="inlineStr"/>
     </row>
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="Y34" t="n">
-        <v>0.3672343492507935</v>
+        <v>12.93962383270264</v>
       </c>
       <c r="Z34" t="inlineStr"/>
     </row>
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="Y35" t="n">
-        <v>0.2943736016750336</v>
+        <v>12.4185209274292</v>
       </c>
       <c r="Z35" t="inlineStr"/>
     </row>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Y36" t="n">
-        <v>0.3796347677707672</v>
+        <v>22.77808570861816</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.379620224237442</v>
+        <v>20.44668006896973</v>
       </c>
     </row>
     <row r="37">
@@ -3156,10 +3156,10 @@
         </is>
       </c>
       <c r="Y37" t="n">
-        <v>0.3796294331550598</v>
+        <v>23.11749458312988</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.3796003460884094</v>
+        <v>20.23455619812012</v>
       </c>
     </row>
     <row r="38">
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Y38" t="n">
-        <v>0.3796277344226837</v>
+        <v>24.35267448425293</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.3795905709266663</v>
+        <v>22.11513900756836</v>
       </c>
     </row>
     <row r="39">
@@ -3344,10 +3344,10 @@
         </is>
       </c>
       <c r="Y39" t="n">
-        <v>0.3796261250972748</v>
+        <v>25.38765144348145</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.379582554101944</v>
+        <v>23.15633964538574</v>
       </c>
     </row>
     <row r="40">
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="Y40" t="n">
-        <v>0.3796219229698181</v>
+        <v>24.31294059753418</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.3795781135559082</v>
+        <v>23.13885688781738</v>
       </c>
     </row>
     <row r="41">
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="Y41" t="n">
-        <v>0.379243940114975</v>
+        <v>13.76689720153809</v>
       </c>
       <c r="Z41" t="inlineStr"/>
     </row>
@@ -3580,7 +3580,7 @@
         </is>
       </c>
       <c r="Y42" t="n">
-        <v>0.3788478672504425</v>
+        <v>14.56055545806885</v>
       </c>
       <c r="Z42" t="inlineStr"/>
     </row>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="Y43" t="n">
-        <v>0.3780442178249359</v>
+        <v>14.2462854385376</v>
       </c>
       <c r="Z43" t="inlineStr"/>
     </row>
@@ -3720,7 +3720,7 @@
         </is>
       </c>
       <c r="Y44" t="n">
-        <v>0.3732605874538422</v>
+        <v>13.86766719818115</v>
       </c>
       <c r="Z44" t="inlineStr"/>
     </row>
@@ -3790,7 +3790,7 @@
         </is>
       </c>
       <c r="Y45" t="n">
-        <v>0.3712639212608337</v>
+        <v>13.63369560241699</v>
       </c>
       <c r="Z45" t="inlineStr"/>
     </row>
@@ -3860,7 +3860,7 @@
         </is>
       </c>
       <c r="Y46" t="n">
-        <v>0.3702563345432281</v>
+        <v>13.51712799072266</v>
       </c>
       <c r="Z46" t="inlineStr"/>
     </row>
@@ -3930,7 +3930,7 @@
         </is>
       </c>
       <c r="Y47" t="n">
-        <v>0.3688234984874725</v>
+        <v>14.2670373916626</v>
       </c>
       <c r="Z47" t="inlineStr"/>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="n">
-        <v>0.3790625929832458</v>
+        <v>12.81750297546387</v>
       </c>
     </row>
     <row r="49">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="n">
-        <v>0.3784849941730499</v>
+        <v>14.2772855758667</v>
       </c>
     </row>
     <row r="50">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="n">
-        <v>0.3784250319004059</v>
+        <v>15.83260726928711</v>
       </c>
     </row>
     <row r="51">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="n">
-        <v>0.3781467974185944</v>
+        <v>16.43428802490234</v>
       </c>
     </row>
     <row r="52">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="n">
-        <v>0.3777460753917694</v>
+        <v>15.85498714447021</v>
       </c>
     </row>
     <row r="53">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="Y53" t="n">
-        <v>0.379638671875</v>
+        <v>25.04668235778809</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.3796394169330597</v>
+        <v>25.58678245544434</v>
       </c>
     </row>
     <row r="54">
@@ -4466,10 +4466,10 @@
         </is>
       </c>
       <c r="Y54" t="n">
-        <v>0.3796373009681702</v>
+        <v>25.30640411376953</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.3796387612819672</v>
+        <v>26.08587074279785</v>
       </c>
     </row>
     <row r="55">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Y55" t="n">
-        <v>0.3796355724334717</v>
+        <v>25.04967308044434</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.3796367049217224</v>
+        <v>25.18362998962402</v>
       </c>
     </row>
     <row r="56">
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="Y56" t="n">
-        <v>0.379632979631424</v>
+        <v>25.52732849121094</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.3796309530735016</v>
+        <v>24.8332691192627</v>
       </c>
     </row>
     <row r="57">
@@ -4748,10 +4748,10 @@
         </is>
       </c>
       <c r="Y57" t="n">
-        <v>0.3796274662017822</v>
+        <v>24.5501594543457</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.3796255588531494</v>
+        <v>24.6572265625</v>
       </c>
     </row>
     <row r="58">
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="Y58" t="n">
-        <v>0.3796198070049286</v>
+        <v>20.27242851257324</v>
       </c>
       <c r="Z58" t="inlineStr"/>
     </row>
@@ -4870,7 +4870,7 @@
         </is>
       </c>
       <c r="Y59" t="n">
-        <v>0.3795995116233826</v>
+        <v>19.74624443054199</v>
       </c>
       <c r="Z59" t="inlineStr"/>
     </row>
@@ -4930,7 +4930,7 @@
         </is>
       </c>
       <c r="Y60" t="n">
-        <v>0.3795240819454193</v>
+        <v>20.07914543151855</v>
       </c>
       <c r="Z60" t="inlineStr"/>
     </row>
@@ -4990,7 +4990,7 @@
         </is>
       </c>
       <c r="Y61" t="n">
-        <v>0.3795015215873718</v>
+        <v>20.52958488464355</v>
       </c>
       <c r="Z61" t="inlineStr"/>
     </row>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Y62" t="n">
-        <v>0.3796381652355194</v>
+        <v>24.48284149169922</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.3796137273311615</v>
+        <v>19.78721809387207</v>
       </c>
     </row>
     <row r="63">
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="Y63" t="n">
-        <v>0.3796362280845642</v>
+        <v>24.89326095581055</v>
       </c>
       <c r="Z63" t="n">
-        <v>0.3795874118804932</v>
+        <v>19.63995933532715</v>
       </c>
     </row>
     <row r="64">
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="Y64" t="n">
-        <v>0.3777463138103485</v>
+        <v>18.90670585632324</v>
       </c>
       <c r="Z64" t="n">
-        <v>0.3795626759529114</v>
+        <v>19.65990257263184</v>
       </c>
     </row>
     <row r="65">
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="Y65" t="n">
-        <v>0.3755089044570923</v>
+        <v>18.17337608337402</v>
       </c>
       <c r="Z65" t="n">
-        <v>0.3794843554496765</v>
+        <v>21.14868354797363</v>
       </c>
     </row>
     <row r="66">
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="Y66" t="n">
-        <v>0.3730294704437256</v>
+        <v>19.00742530822754</v>
       </c>
       <c r="Z66" t="n">
-        <v>0.3794713318347931</v>
+        <v>22.00320816040039</v>
       </c>
     </row>
     <row r="67">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="n">
-        <v>0.3794528543949127</v>
+        <v>22.51974678039551</v>
       </c>
     </row>
     <row r="68">
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Y68" t="n">
-        <v>0.3795381486415863</v>
+        <v>16.20741653442383</v>
       </c>
       <c r="Z68" t="n">
-        <v>0.379607081413269</v>
+        <v>12.9914436340332</v>
       </c>
     </row>
     <row r="69">
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="Y69" t="n">
-        <v>0.3794362545013428</v>
+        <v>16.54186630249023</v>
       </c>
       <c r="Z69" t="n">
-        <v>0.3795740902423859</v>
+        <v>19.27005958557129</v>
       </c>
     </row>
     <row r="70">
@@ -5810,10 +5810,10 @@
         </is>
       </c>
       <c r="Y70" t="n">
-        <v>0.3792353868484497</v>
+        <v>16.86870002746582</v>
       </c>
       <c r="Z70" t="n">
-        <v>0.3795570433139801</v>
+        <v>18.17769241333008</v>
       </c>
     </row>
     <row r="71">
@@ -5904,10 +5904,10 @@
         </is>
       </c>
       <c r="Y71" t="n">
-        <v>0.3788138329982758</v>
+        <v>16.24711608886719</v>
       </c>
       <c r="Z71" t="n">
-        <v>0.3795270323753357</v>
+        <v>17.68392372131348</v>
       </c>
     </row>
     <row r="72">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="n">
-        <v>0.3793433904647827</v>
+        <v>15.53071022033691</v>
       </c>
     </row>
     <row r="73">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="n">
-        <v>0.3790467381477356</v>
+        <v>16.26268768310547</v>
       </c>
     </row>
     <row r="74">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="n">
-        <v>0.3787345886230469</v>
+        <v>16.61716842651367</v>
       </c>
     </row>
     <row r="75">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="n">
-        <v>0.3784830868244171</v>
+        <v>17.15262031555176</v>
       </c>
     </row>
     <row r="76">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="n">
-        <v>0.3783865571022034</v>
+        <v>18.08442115783691</v>
       </c>
     </row>
     <row r="77">
@@ -6327,7 +6327,7 @@
       </c>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
-        <v>0.3796378374099731</v>
+        <v>23.75501823425293</v>
       </c>
     </row>
     <row r="78">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="n">
-        <v>0.3796356022357941</v>
+        <v>24.6086597442627</v>
       </c>
     </row>
     <row r="79">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="n">
-        <v>0.379622757434845</v>
+        <v>22.92251014709473</v>
       </c>
     </row>
     <row r="80">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="n">
-        <v>0.379615843296051</v>
+        <v>24.12940979003906</v>
       </c>
     </row>
     <row r="81">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
-        <v>0.3796124458312988</v>
+        <v>23.90937995910645</v>
       </c>
     </row>
     <row r="82">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="n">
-        <v>0.3796381652355194</v>
+        <v>24.13961982727051</v>
       </c>
     </row>
     <row r="83">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="n">
-        <v>0.3796362280845642</v>
+        <v>25.19907760620117</v>
       </c>
     </row>
     <row r="84">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="n">
-        <v>0.3796304166316986</v>
+        <v>23.15984916687012</v>
       </c>
     </row>
     <row r="85">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="n">
-        <v>0.3796216249465942</v>
+        <v>23.30803489685059</v>
       </c>
     </row>
     <row r="86">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="n">
-        <v>0.3792551755905151</v>
+        <v>21.42658805847168</v>
       </c>
     </row>
     <row r="87">
@@ -7048,10 +7048,10 @@
         </is>
       </c>
       <c r="Y87" t="n">
-        <v>0.3796356022357941</v>
+        <v>22.95236396789551</v>
       </c>
       <c r="Z87" t="n">
-        <v>0.3796394765377045</v>
+        <v>24.98410606384277</v>
       </c>
     </row>
     <row r="88">
@@ -7142,10 +7142,10 @@
         </is>
       </c>
       <c r="Y88" t="n">
-        <v>0.3796311616897583</v>
+        <v>22.78695869445801</v>
       </c>
       <c r="Z88" t="n">
-        <v>0.3796388804912567</v>
+        <v>26.09096908569336</v>
       </c>
     </row>
     <row r="89">
@@ -7236,10 +7236,10 @@
         </is>
       </c>
       <c r="Y89" t="n">
-        <v>0.3796197772026062</v>
+        <v>22.44659996032715</v>
       </c>
       <c r="Z89" t="n">
-        <v>0.3796376883983612</v>
+        <v>25.52620506286621</v>
       </c>
     </row>
     <row r="90">
@@ -7330,10 +7330,10 @@
         </is>
       </c>
       <c r="Y90" t="n">
-        <v>0.3795651495456696</v>
+        <v>21.40190315246582</v>
       </c>
       <c r="Z90" t="n">
-        <v>0.3796371519565582</v>
+        <v>26.1712703704834</v>
       </c>
     </row>
     <row r="91">
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="Y91" t="n">
-        <v>0.3795324862003326</v>
+        <v>21.76372528076172</v>
       </c>
       <c r="Z91" t="n">
-        <v>0.3796364068984985</v>
+        <v>26.54031944274902</v>
       </c>
     </row>
     <row r="92">
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="Y92" t="n">
-        <v>0.3793894350528717</v>
+        <v>20.02974891662598</v>
       </c>
       <c r="Z92" t="n">
-        <v>0.3796353340148926</v>
+        <v>26.1048412322998</v>
       </c>
     </row>
     <row r="93">
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="Y93" t="n">
-        <v>0.3795718550682068</v>
+        <v>18.61631202697754</v>
       </c>
       <c r="Z93" t="inlineStr"/>
     </row>
@@ -7660,7 +7660,7 @@
         </is>
       </c>
       <c r="Y94" t="n">
-        <v>0.3795036673545837</v>
+        <v>18.14398765563965</v>
       </c>
       <c r="Z94" t="inlineStr"/>
     </row>
@@ -7730,7 +7730,7 @@
         </is>
       </c>
       <c r="Y95" t="n">
-        <v>0.3793503642082214</v>
+        <v>19.0782527923584</v>
       </c>
       <c r="Z95" t="inlineStr"/>
     </row>
@@ -7800,7 +7800,7 @@
         </is>
       </c>
       <c r="Y96" t="n">
-        <v>0.3790956437587738</v>
+        <v>17.82406044006348</v>
       </c>
       <c r="Z96" t="inlineStr"/>
     </row>
@@ -7870,7 +7870,7 @@
         </is>
       </c>
       <c r="Y97" t="n">
-        <v>0.3789313435554504</v>
+        <v>17.83099174499512</v>
       </c>
       <c r="Z97" t="inlineStr"/>
     </row>
@@ -7940,7 +7940,7 @@
         </is>
       </c>
       <c r="Y98" t="n">
-        <v>0.3795434832572937</v>
+        <v>15.63015842437744</v>
       </c>
       <c r="Z98" t="inlineStr"/>
     </row>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="Y99" t="n">
-        <v>0.3794468939304352</v>
+        <v>17.25191688537598</v>
       </c>
       <c r="Z99" t="inlineStr"/>
     </row>
@@ -8080,7 +8080,7 @@
         </is>
       </c>
       <c r="Y100" t="n">
-        <v>0.3793798685073853</v>
+        <v>17.66477584838867</v>
       </c>
       <c r="Z100" t="inlineStr"/>
     </row>
@@ -8150,7 +8150,7 @@
         </is>
       </c>
       <c r="Y101" t="n">
-        <v>0.3793297111988068</v>
+        <v>19.11247062683105</v>
       </c>
       <c r="Z101" t="inlineStr"/>
     </row>
@@ -8220,7 +8220,7 @@
         </is>
       </c>
       <c r="Y102" t="n">
-        <v>0.3792312145233154</v>
+        <v>18.63239479064941</v>
       </c>
       <c r="Z102" t="inlineStr"/>
     </row>
@@ -8290,7 +8290,7 @@
         </is>
       </c>
       <c r="Y103" t="n">
-        <v>0.3791964650154114</v>
+        <v>19.69631385803223</v>
       </c>
       <c r="Z103" t="inlineStr"/>
     </row>
@@ -8360,7 +8360,7 @@
         </is>
       </c>
       <c r="Y104" t="n">
-        <v>0.3791558444499969</v>
+        <v>19.80424690246582</v>
       </c>
       <c r="Z104" t="inlineStr"/>
     </row>
@@ -8430,7 +8430,7 @@
         </is>
       </c>
       <c r="Y105" t="n">
-        <v>0.3796381950378418</v>
+        <v>24.20821571350098</v>
       </c>
       <c r="Z105" t="inlineStr"/>
     </row>
@@ -8500,7 +8500,7 @@
         </is>
       </c>
       <c r="Y106" t="n">
-        <v>0.3796363174915314</v>
+        <v>24.28452491760254</v>
       </c>
       <c r="Z106" t="inlineStr"/>
     </row>
@@ -8570,7 +8570,7 @@
         </is>
       </c>
       <c r="Y107" t="n">
-        <v>0.3796335756778717</v>
+        <v>24.22764015197754</v>
       </c>
       <c r="Z107" t="inlineStr"/>
     </row>
@@ -8640,7 +8640,7 @@
         </is>
       </c>
       <c r="Y108" t="n">
-        <v>0.3796316683292389</v>
+        <v>25.49049186706543</v>
       </c>
       <c r="Z108" t="inlineStr"/>
     </row>
@@ -8710,7 +8710,7 @@
         </is>
       </c>
       <c r="Y109" t="n">
-        <v>0.3796308934688568</v>
+        <v>25.69119071960449</v>
       </c>
       <c r="Z109" t="inlineStr"/>
     </row>
@@ -8770,7 +8770,7 @@
         </is>
       </c>
       <c r="Y110" t="n">
-        <v>0.3792031705379486</v>
+        <v>13.63620376586914</v>
       </c>
       <c r="Z110" t="inlineStr"/>
     </row>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="Y111" t="n">
-        <v>0.3787663578987122</v>
+        <v>14.69663715362549</v>
       </c>
       <c r="Z111" t="inlineStr"/>
     </row>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="Y112" t="n">
-        <v>0.3657726943492889</v>
+        <v>13.350998878479</v>
       </c>
       <c r="Z112" t="inlineStr"/>
     </row>
@@ -8950,7 +8950,7 @@
         </is>
       </c>
       <c r="Y113" t="n">
-        <v>0.3616540133953094</v>
+        <v>12.62268161773682</v>
       </c>
       <c r="Z113" t="inlineStr"/>
     </row>
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="Y114" t="n">
-        <v>0.3796204030513763</v>
+        <v>20.30829238891602</v>
       </c>
       <c r="Z114" t="inlineStr"/>
     </row>
@@ -9090,7 +9090,7 @@
         </is>
       </c>
       <c r="Y115" t="n">
-        <v>0.3796007335186005</v>
+        <v>19.97149658203125</v>
       </c>
       <c r="Z115" t="inlineStr"/>
     </row>
@@ -9160,7 +9160,7 @@
         </is>
       </c>
       <c r="Y116" t="n">
-        <v>0.3795934319496155</v>
+        <v>22.31131935119629</v>
       </c>
       <c r="Z116" t="inlineStr"/>
     </row>
@@ -9230,7 +9230,7 @@
         </is>
       </c>
       <c r="Y117" t="n">
-        <v>0.379457026720047</v>
+        <v>20.29179191589355</v>
       </c>
       <c r="Z117" t="inlineStr"/>
     </row>
@@ -9302,10 +9302,10 @@
         </is>
       </c>
       <c r="Y118" t="n">
-        <v>0.3796391189098358</v>
+        <v>25.04868507385254</v>
       </c>
       <c r="Z118" t="n">
-        <v>0.3796243667602539</v>
+        <v>20.54109382629395</v>
       </c>
     </row>
     <row r="119">
@@ -9376,10 +9376,10 @@
         </is>
       </c>
       <c r="Y119" t="n">
-        <v>0.379638135433197</v>
+        <v>25.94673919677734</v>
       </c>
       <c r="Z119" t="n">
-        <v>0.3796086311340332</v>
+        <v>20.56247901916504</v>
       </c>
     </row>
     <row r="120">
@@ -9450,10 +9450,10 @@
         </is>
       </c>
       <c r="Y120" t="n">
-        <v>0.3796370029449463</v>
+        <v>25.70434761047363</v>
       </c>
       <c r="Z120" t="n">
-        <v>0.3795920312404633</v>
+        <v>21.34435844421387</v>
       </c>
     </row>
     <row r="121">
@@ -9524,10 +9524,10 @@
         </is>
       </c>
       <c r="Y121" t="n">
-        <v>0.3796241879463196</v>
+        <v>23.95318222045898</v>
       </c>
       <c r="Z121" t="n">
-        <v>0.379571408033371</v>
+        <v>21.22954750061035</v>
       </c>
     </row>
     <row r="122">
@@ -9618,10 +9618,10 @@
         </is>
       </c>
       <c r="Y122" t="n">
-        <v>0.3796393275260925</v>
+        <v>25.18052101135254</v>
       </c>
       <c r="Z122" t="n">
-        <v>0.3796396553516388</v>
+        <v>25.41709327697754</v>
       </c>
     </row>
     <row r="123">
@@ -9712,10 +9712,10 @@
         </is>
       </c>
       <c r="Y123" t="n">
-        <v>0.3796385824680328</v>
+        <v>26.25165367126465</v>
       </c>
       <c r="Z123" t="n">
-        <v>0.379639208316803</v>
+        <v>26.67430305480957</v>
       </c>
     </row>
     <row r="124">
@@ -9806,10 +9806,10 @@
         </is>
       </c>
       <c r="Y124" t="n">
-        <v>0.3796369135379791</v>
+        <v>25.53103637695312</v>
       </c>
       <c r="Z124" t="n">
-        <v>0.379638671875</v>
+        <v>26.47438430786133</v>
       </c>
     </row>
     <row r="125">
@@ -9900,10 +9900,10 @@
         </is>
       </c>
       <c r="Y125" t="n">
-        <v>0.3796364367008209</v>
+        <v>26.73400688171387</v>
       </c>
       <c r="Z125" t="n">
-        <v>0.379638284444809</v>
+        <v>27.05850791931152</v>
       </c>
     </row>
     <row r="126">
@@ -9994,10 +9994,10 @@
         </is>
       </c>
       <c r="Y126" t="n">
-        <v>0.3796347677707672</v>
+        <v>25.98882102966309</v>
       </c>
       <c r="Z126" t="n">
-        <v>0.379637748003006</v>
+        <v>26.77681541442871</v>
       </c>
     </row>
     <row r="127">
@@ -10088,10 +10088,10 @@
         </is>
       </c>
       <c r="Y127" t="n">
-        <v>0.3796339631080627</v>
+        <v>26.34908103942871</v>
       </c>
       <c r="Z127" t="n">
-        <v>0.3796373903751373</v>
+        <v>26.86684226989746</v>
       </c>
     </row>
     <row r="128">
@@ -10182,10 +10182,10 @@
         </is>
       </c>
       <c r="Y128" t="n">
-        <v>0.3796306550502777</v>
+        <v>21.50384140014648</v>
       </c>
       <c r="Z128" t="n">
-        <v>0.3796303868293762</v>
+        <v>21.4272518157959</v>
       </c>
     </row>
     <row r="129">
@@ -10276,10 +10276,10 @@
         </is>
       </c>
       <c r="Y129" t="n">
-        <v>0.3796212077140808</v>
+        <v>21.4486198425293</v>
       </c>
       <c r="Z129" t="n">
-        <v>0.3796207010746002</v>
+        <v>21.12310028076172</v>
       </c>
     </row>
     <row r="130">
@@ -10370,10 +10370,10 @@
         </is>
       </c>
       <c r="Y130" t="n">
-        <v>0.3796168267726898</v>
+        <v>22.87942695617676</v>
       </c>
       <c r="Z130" t="n">
-        <v>0.37960484623909</v>
+        <v>21.53729820251465</v>
       </c>
     </row>
     <row r="131">
@@ -10464,10 +10464,10 @@
         </is>
       </c>
       <c r="Y131" t="n">
-        <v>0.3796123862266541</v>
+        <v>24.03066062927246</v>
       </c>
       <c r="Z131" t="n">
-        <v>0.379593163728714</v>
+        <v>22.64959907531738</v>
       </c>
     </row>
     <row r="132">
@@ -10558,10 +10558,10 @@
         </is>
       </c>
       <c r="Y132" t="n">
-        <v>0.3796075284481049</v>
+        <v>23.40751838684082</v>
       </c>
       <c r="Z132" t="n">
-        <v>0.3795850872993469</v>
+        <v>22.71357536315918</v>
       </c>
     </row>
     <row r="133">
@@ -10652,10 +10652,10 @@
         </is>
       </c>
       <c r="Y133" t="n">
-        <v>0.3796035945415497</v>
+        <v>23.54510498046875</v>
       </c>
       <c r="Z133" t="n">
-        <v>0.3795805275440216</v>
+        <v>23.25110054016113</v>
       </c>
     </row>
     <row r="134">
@@ -10746,10 +10746,10 @@
         </is>
       </c>
       <c r="Y134" t="n">
-        <v>0.379638135433197</v>
+        <v>24.03154945373535</v>
       </c>
       <c r="Z134" t="n">
-        <v>0.3796330392360687</v>
+        <v>22.29207229614258</v>
       </c>
     </row>
     <row r="135">
@@ -10840,10 +10840,10 @@
         </is>
       </c>
       <c r="Y135" t="n">
-        <v>0.3796362280845642</v>
+        <v>24.31199836730957</v>
       </c>
       <c r="Z135" t="n">
-        <v>0.3796259760856628</v>
+        <v>22.00619316101074</v>
       </c>
     </row>
     <row r="136">
@@ -10934,10 +10934,10 @@
         </is>
       </c>
       <c r="Y136" t="n">
-        <v>0.3796346187591553</v>
+        <v>24.49942588806152</v>
       </c>
       <c r="Z136" t="n">
-        <v>0.3796113729476929</v>
+        <v>22.01093101501465</v>
       </c>
     </row>
     <row r="137">
@@ -11028,10 +11028,10 @@
         </is>
       </c>
       <c r="Y137" t="n">
-        <v>0.3796327710151672</v>
+        <v>25.15817642211914</v>
       </c>
       <c r="Z137" t="n">
-        <v>0.3796069622039795</v>
+        <v>23.63705062866211</v>
       </c>
     </row>
     <row r="138">
@@ -11122,10 +11122,10 @@
         </is>
       </c>
       <c r="Y138" t="n">
-        <v>0.379583477973938</v>
+        <v>18.5027027130127</v>
       </c>
       <c r="Z138" t="n">
-        <v>0.3796001970767975</v>
+        <v>19.28909111022949</v>
       </c>
     </row>
     <row r="139">
@@ -11216,10 +11216,10 @@
         </is>
       </c>
       <c r="Y139" t="n">
-        <v>0.3795269131660461</v>
+        <v>17.89865303039551</v>
       </c>
       <c r="Z139" t="n">
-        <v>0.3795603215694427</v>
+        <v>18.58600616455078</v>
       </c>
     </row>
     <row r="140">
@@ -11310,10 +11310,10 @@
         </is>
       </c>
       <c r="Y140" t="n">
-        <v>0.3795204758644104</v>
+        <v>21.20558738708496</v>
       </c>
       <c r="Z140" t="n">
-        <v>0.3795122504234314</v>
+        <v>19.84844398498535</v>
       </c>
     </row>
     <row r="141">
@@ -11404,10 +11404,10 @@
         </is>
       </c>
       <c r="Y141" t="n">
-        <v>0.3795183897018433</v>
+        <v>23.80387115478516</v>
       </c>
       <c r="Z141" t="n">
-        <v>0.3795080482959747</v>
+        <v>22.91438674926758</v>
       </c>
     </row>
     <row r="142">
@@ -11498,10 +11498,10 @@
         </is>
       </c>
       <c r="Y142" t="n">
-        <v>0.3795165717601776</v>
+        <v>23.18221664428711</v>
       </c>
       <c r="Z142" t="n">
-        <v>0.3795047700405121</v>
+        <v>23.12286949157715</v>
       </c>
     </row>
     <row r="143">
@@ -11592,10 +11592,10 @@
         </is>
       </c>
       <c r="Y143" t="n">
-        <v>0.3796138763427734</v>
+        <v>18.93901252746582</v>
       </c>
       <c r="Z143" t="n">
-        <v>0.3796389997005463</v>
+        <v>24.59476280212402</v>
       </c>
     </row>
     <row r="144">
@@ -11686,10 +11686,10 @@
         </is>
       </c>
       <c r="Y144" t="n">
-        <v>0.3795876801013947</v>
+        <v>19.23104667663574</v>
       </c>
       <c r="Z144" t="n">
-        <v>0.3796379268169403</v>
+        <v>25.42917442321777</v>
       </c>
     </row>
     <row r="145">
@@ -11780,10 +11780,10 @@
         </is>
       </c>
       <c r="Y145" t="n">
-        <v>0.3795522153377533</v>
+        <v>20.17878532409668</v>
       </c>
       <c r="Z145" t="n">
-        <v>0.3796361684799194</v>
+        <v>24.98178863525391</v>
       </c>
     </row>
     <row r="146">
@@ -11874,10 +11874,10 @@
         </is>
       </c>
       <c r="Y146" t="n">
-        <v>0.3795506358146667</v>
+        <v>23.38103294372559</v>
       </c>
       <c r="Z146" t="n">
-        <v>0.3796336054801941</v>
+        <v>25.10439491271973</v>
       </c>
     </row>
     <row r="147">
@@ -11968,10 +11968,10 @@
         </is>
       </c>
       <c r="Y147" t="n">
-        <v>0.3796389997005463</v>
+        <v>24.93081474304199</v>
       </c>
       <c r="Z147" t="n">
-        <v>0.3788162767887115</v>
+        <v>8.758796691894531</v>
       </c>
     </row>
     <row r="148">
@@ -12062,10 +12062,10 @@
         </is>
       </c>
       <c r="Y148" t="n">
-        <v>0.3796379268169403</v>
+        <v>25.69237327575684</v>
       </c>
       <c r="Z148" t="n">
-        <v>0.3779926598072052</v>
+        <v>14.65681934356689</v>
       </c>
     </row>
     <row r="149">
@@ -12156,10 +12156,10 @@
         </is>
       </c>
       <c r="Y149" t="n">
-        <v>0.3796288967132568</v>
+        <v>23.7233829498291</v>
       </c>
       <c r="Z149" t="n">
-        <v>0.3776521980762482</v>
+        <v>13.58108139038086</v>
       </c>
     </row>
     <row r="150">
@@ -12250,10 +12250,10 @@
         </is>
       </c>
       <c r="Y150" t="n">
-        <v>0.3796258866786957</v>
+        <v>25.11989212036133</v>
       </c>
       <c r="Z150" t="n">
-        <v>0.3771544694900513</v>
+        <v>13.61655139923096</v>
       </c>
     </row>
     <row r="151">
@@ -12344,10 +12344,10 @@
         </is>
       </c>
       <c r="Y151" t="n">
-        <v>0.3796237409114838</v>
+        <v>25.61156463623047</v>
       </c>
       <c r="Z151" t="n">
-        <v>0.3761172592639923</v>
+        <v>13.2659215927124</v>
       </c>
     </row>
     <row r="152">
@@ -12416,7 +12416,7 @@
         </is>
       </c>
       <c r="Y152" t="n">
-        <v>0.3709528148174286</v>
+        <v>8.28873348236084</v>
       </c>
       <c r="Z152" t="inlineStr"/>
     </row>
@@ -12486,7 +12486,7 @@
         </is>
       </c>
       <c r="Y153" t="n">
-        <v>0.3622815012931824</v>
+        <v>10.66897106170654</v>
       </c>
       <c r="Z153" t="inlineStr"/>
     </row>
@@ -12556,7 +12556,7 @@
         </is>
       </c>
       <c r="Y154" t="n">
-        <v>0.2918746471405029</v>
+        <v>10.77929592132568</v>
       </c>
       <c r="Z154" t="inlineStr"/>
     </row>
@@ -12626,7 +12626,7 @@
         </is>
       </c>
       <c r="Y155" t="n">
-        <v>0.2755361795425415</v>
+        <v>10.81907081604004</v>
       </c>
       <c r="Z155" t="inlineStr"/>
     </row>
@@ -12718,10 +12718,10 @@
         </is>
       </c>
       <c r="Y156" t="n">
-        <v>0.379639059305191</v>
+        <v>25.42172431945801</v>
       </c>
       <c r="Z156" t="n">
-        <v>0.3796380460262299</v>
+        <v>24.40272903442383</v>
       </c>
     </row>
     <row r="157">
@@ -12812,10 +12812,10 @@
         </is>
       </c>
       <c r="Y157" t="n">
-        <v>0.3796380162239075</v>
+        <v>26.03066444396973</v>
       </c>
       <c r="Z157" t="n">
-        <v>0.3796360194683075</v>
+        <v>24.74835395812988</v>
       </c>
     </row>
     <row r="158">
@@ -12906,10 +12906,10 @@
         </is>
       </c>
       <c r="Y158" t="n">
-        <v>0.3796365857124329</v>
+        <v>25.46421241760254</v>
       </c>
       <c r="Z158" t="n">
-        <v>0.3796336054801941</v>
+        <v>24.44573020935059</v>
       </c>
     </row>
     <row r="159">
@@ -13000,10 +13000,10 @@
         </is>
       </c>
       <c r="Y159" t="n">
-        <v>0.379634290933609</v>
+        <v>25.19592094421387</v>
       </c>
       <c r="Z159" t="n">
-        <v>0.3796304762363434</v>
+        <v>24.52349472045898</v>
       </c>
     </row>
     <row r="160">
@@ -13094,10 +13094,10 @@
         </is>
       </c>
       <c r="Y160" t="n">
-        <v>0.3796384036540985</v>
+        <v>24.65409278869629</v>
       </c>
       <c r="Z160" t="n">
-        <v>0.3796388804912567</v>
+        <v>25.0428295135498</v>
       </c>
     </row>
     <row r="161">
@@ -13188,10 +13188,10 @@
         </is>
       </c>
       <c r="Y161" t="n">
-        <v>0.3796367347240448</v>
+        <v>24.8654613494873</v>
       </c>
       <c r="Z161" t="n">
-        <v>0.3796377182006836</v>
+        <v>25.55008888244629</v>
       </c>
     </row>
     <row r="162">
@@ -13282,10 +13282,10 @@
         </is>
       </c>
       <c r="Y162" t="n">
-        <v>0.3796341717243195</v>
+        <v>24.53545951843262</v>
       </c>
       <c r="Z162" t="n">
-        <v>0.3796358406543732</v>
+        <v>25.08271408081055</v>
       </c>
     </row>
     <row r="163">
@@ -13376,10 +13376,10 @@
         </is>
       </c>
       <c r="Y163" t="n">
-        <v>0.3796320855617523</v>
+        <v>25.55240821838379</v>
       </c>
       <c r="Z163" t="n">
-        <v>0.3796336948871613</v>
+        <v>25.72835540771484</v>
       </c>
     </row>
     <row r="164">
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="Y164" t="n">
-        <v>0.3795937299728394</v>
+        <v>15.94089221954346</v>
       </c>
       <c r="Z164" t="n">
-        <v>0.3796130120754242</v>
+        <v>13.55747509002686</v>
       </c>
     </row>
     <row r="165">
@@ -13564,10 +13564,10 @@
         </is>
       </c>
       <c r="Y165" t="n">
-        <v>0.3795474171638489</v>
+        <v>19.33171081542969</v>
       </c>
       <c r="Z165" t="n">
-        <v>0.3795859217643738</v>
+        <v>19.8248233795166</v>
       </c>
     </row>
     <row r="166">
@@ -13658,10 +13658,10 @@
         </is>
       </c>
       <c r="Y166" t="n">
-        <v>0.3793329298496246</v>
+        <v>16.76715660095215</v>
       </c>
       <c r="Z166" t="n">
-        <v>0.379572331905365</v>
+        <v>18.45160865783691</v>
       </c>
     </row>
     <row r="167">
@@ -13752,10 +13752,10 @@
         </is>
       </c>
       <c r="Y167" t="n">
-        <v>0.3793201446533203</v>
+        <v>19.35457229614258</v>
       </c>
       <c r="Z167" t="n">
-        <v>0.3795526325702667</v>
+        <v>18.2776050567627</v>
       </c>
     </row>
     <row r="168">
@@ -13846,10 +13846,10 @@
         </is>
       </c>
       <c r="Y168" t="n">
-        <v>0.3796131312847137</v>
+        <v>20.51694107055664</v>
       </c>
       <c r="Z168" t="n">
-        <v>0.3795817792415619</v>
+        <v>18.70695304870605</v>
       </c>
     </row>
     <row r="169">
@@ -13940,10 +13940,10 @@
         </is>
       </c>
       <c r="Y169" t="n">
-        <v>0.3795861899852753</v>
+        <v>20.4039421081543</v>
       </c>
       <c r="Z169" t="n">
-        <v>0.3795235157012939</v>
+        <v>18.81877326965332</v>
       </c>
     </row>
     <row r="170">
@@ -14034,10 +14034,10 @@
         </is>
       </c>
       <c r="Y170" t="n">
-        <v>0.3795817196369171</v>
+        <v>23.31559944152832</v>
       </c>
       <c r="Z170" t="n">
-        <v>0.3795133829116821</v>
+        <v>21.69782447814941</v>
       </c>
     </row>
     <row r="171">
@@ -14128,10 +14128,10 @@
         </is>
       </c>
       <c r="Y171" t="n">
-        <v>0.3795797228813171</v>
+        <v>24.53913688659668</v>
       </c>
       <c r="Z171" t="n">
-        <v>0.3795071542263031</v>
+        <v>22.79102897644043</v>
       </c>
     </row>
     <row r="172">
@@ -14222,10 +14222,10 @@
         </is>
       </c>
       <c r="Y172" t="n">
-        <v>0.3796371817588806</v>
+        <v>23.82098197937012</v>
       </c>
       <c r="Z172" t="n">
-        <v>0.3796378076076508</v>
+        <v>23.97561836242676</v>
       </c>
     </row>
     <row r="173">
@@ -14316,10 +14316,10 @@
         </is>
       </c>
       <c r="Y173" t="n">
-        <v>0.3796342611312866</v>
+        <v>23.58302307128906</v>
       </c>
       <c r="Z173" t="n">
-        <v>0.3796355426311493</v>
+        <v>24.06174087524414</v>
       </c>
     </row>
     <row r="174">
@@ -14410,10 +14410,10 @@
         </is>
       </c>
       <c r="Y174" t="n">
-        <v>0.3796327114105225</v>
+        <v>24.61639213562012</v>
       </c>
       <c r="Z174" t="n">
-        <v>0.3796335756778717</v>
+        <v>24.42523765563965</v>
       </c>
     </row>
     <row r="175">
@@ -14504,10 +14504,10 @@
         </is>
       </c>
       <c r="Y175" t="n">
-        <v>0.3796315491199493</v>
+        <v>25.65814590454102</v>
       </c>
       <c r="Z175" t="n">
-        <v>0.3796311020851135</v>
+        <v>24.96186637878418</v>
       </c>
     </row>
     <row r="176">
@@ -14598,10 +14598,10 @@
         </is>
       </c>
       <c r="Y176" t="n">
-        <v>0.3796307742595673</v>
+        <v>25.71256256103516</v>
       </c>
       <c r="Z176" t="n">
-        <v>0.3796301186084747</v>
+        <v>25.4659481048584</v>
       </c>
     </row>
     <row r="177">
@@ -14692,10 +14692,10 @@
         </is>
       </c>
       <c r="Y177" t="n">
-        <v>0.3796388506889343</v>
+        <v>25.52655410766602</v>
       </c>
       <c r="Z177" t="n">
-        <v>0.379639208316803</v>
+        <v>25.79126358032227</v>
       </c>
     </row>
     <row r="178">
@@ -14786,10 +14786,10 @@
         </is>
       </c>
       <c r="Y178" t="n">
-        <v>0.379637598991394</v>
+        <v>25.91356086730957</v>
       </c>
       <c r="Z178" t="n">
-        <v>0.3796383738517761</v>
+        <v>26.3453197479248</v>
       </c>
     </row>
     <row r="179">
@@ -14880,10 +14880,10 @@
         </is>
       </c>
       <c r="Y179" t="n">
-        <v>0.3796369135379791</v>
+        <v>25.8425407409668</v>
       </c>
       <c r="Z179" t="n">
-        <v>0.3796379268169403</v>
+        <v>26.16219520568848</v>
       </c>
     </row>
     <row r="180">
@@ -14974,10 +14974,10 @@
         </is>
       </c>
       <c r="Y180" t="n">
-        <v>0.3796197772026062</v>
+        <v>24.31498527526855</v>
       </c>
       <c r="Z180" t="n">
-        <v>0.3796367943286896</v>
+        <v>26.64544486999512</v>
       </c>
     </row>
     <row r="181">
@@ -15068,10 +15068,10 @@
         </is>
       </c>
       <c r="Y181" t="n">
-        <v>0.3796383440494537</v>
+        <v>24.34527587890625</v>
       </c>
       <c r="Z181" t="n">
-        <v>0.37961345911026</v>
+        <v>19.62554931640625</v>
       </c>
     </row>
     <row r="182">
@@ -15162,10 +15162,10 @@
         </is>
       </c>
       <c r="Y182" t="n">
-        <v>0.3796366453170776</v>
+        <v>24.69660758972168</v>
       </c>
       <c r="Z182" t="n">
-        <v>0.3795868754386902</v>
+        <v>19.22729682922363</v>
       </c>
     </row>
     <row r="183">
@@ -15256,10 +15256,10 @@
         </is>
       </c>
       <c r="Y183" t="n">
-        <v>0.379634827375412</v>
+        <v>23.5112247467041</v>
       </c>
       <c r="Z183" t="n">
-        <v>0.3795701265335083</v>
+        <v>19.77610969543457</v>
       </c>
     </row>
     <row r="184">
@@ -15350,10 +15350,10 @@
         </is>
       </c>
       <c r="Y184" t="n">
-        <v>0.3796310126781464</v>
+        <v>25.78423118591309</v>
       </c>
       <c r="Z184" t="n">
-        <v>0.3795460760593414</v>
+        <v>22.09528160095215</v>
       </c>
     </row>
     <row r="185">
@@ -15444,10 +15444,10 @@
         </is>
       </c>
       <c r="Y185" t="n">
-        <v>0.3796222805976868</v>
+        <v>23.63099479675293</v>
       </c>
       <c r="Z185" t="n">
-        <v>0.3795149922370911</v>
+        <v>20.60183715820312</v>
       </c>
     </row>
     <row r="186">
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="Y186" t="n">
-        <v>0.3796388804912567</v>
+        <v>24.45508766174316</v>
       </c>
       <c r="Z186" t="n">
-        <v>0.379639059305191</v>
+        <v>24.74200248718262</v>
       </c>
     </row>
     <row r="187">
@@ -15632,10 +15632,10 @@
         </is>
       </c>
       <c r="Y187" t="n">
-        <v>0.3796377182006836</v>
+        <v>25.35879707336426</v>
       </c>
       <c r="Z187" t="n">
-        <v>0.3796380460262299</v>
+        <v>25.2735710144043</v>
       </c>
     </row>
     <row r="188">
@@ -15726,10 +15726,10 @@
         </is>
       </c>
       <c r="Y188" t="n">
-        <v>0.3796364963054657</v>
+        <v>25.2875919342041</v>
       </c>
       <c r="Z188" t="n">
-        <v>0.379633754491806</v>
+        <v>23.97983932495117</v>
       </c>
     </row>
     <row r="189">
@@ -15820,10 +15820,10 @@
         </is>
       </c>
       <c r="Y189" t="n">
-        <v>0.3796354234218597</v>
+        <v>25.79355430603027</v>
       </c>
       <c r="Z189" t="n">
-        <v>0.379631370306015</v>
+        <v>24.99002647399902</v>
       </c>
     </row>
     <row r="190">
@@ -15914,10 +15914,10 @@
         </is>
       </c>
       <c r="Y190" t="n">
-        <v>0.379634827375412</v>
+        <v>26.35423851013184</v>
       </c>
       <c r="Z190" t="n">
-        <v>0.37962806224823</v>
+        <v>25.04243278503418</v>
       </c>
     </row>
     <row r="191">
@@ -16008,10 +16008,10 @@
         </is>
       </c>
       <c r="Y191" t="n">
-        <v>0.379634290933609</v>
+        <v>26.14211273193359</v>
       </c>
       <c r="Z191" t="n">
-        <v>0.3796254694461823</v>
+        <v>24.51986122131348</v>
       </c>
     </row>
     <row r="192">
@@ -16102,10 +16102,10 @@
         </is>
       </c>
       <c r="Y192" t="n">
-        <v>0.3796344995498657</v>
+        <v>23.02286338806152</v>
       </c>
       <c r="Z192" t="n">
-        <v>0.3796371817588806</v>
+        <v>23.96051979064941</v>
       </c>
     </row>
     <row r="193">
@@ -16196,10 +16196,10 @@
         </is>
       </c>
       <c r="Y193" t="n">
-        <v>0.3796289265155792</v>
+        <v>23.21726417541504</v>
       </c>
       <c r="Z193" t="n">
-        <v>0.3796342611312866</v>
+        <v>24.35904693603516</v>
       </c>
     </row>
     <row r="194">
@@ -16290,10 +16290,10 @@
         </is>
       </c>
       <c r="Y194" t="n">
-        <v>0.3796217739582062</v>
+        <v>23.32250785827637</v>
       </c>
       <c r="Z194" t="n">
-        <v>0.3796316981315613</v>
+        <v>24.51750946044922</v>
       </c>
     </row>
     <row r="195">
@@ -16384,10 +16384,10 @@
         </is>
       </c>
       <c r="Y195" t="n">
-        <v>0.3796180486679077</v>
+        <v>24.69840240478516</v>
       </c>
       <c r="Z195" t="n">
-        <v>0.3796265423297882</v>
+        <v>24.76419258117676</v>
       </c>
     </row>
     <row r="196">
@@ -16478,10 +16478,10 @@
         </is>
       </c>
       <c r="Y196" t="n">
-        <v>0.379617303609848</v>
+        <v>25.84748649597168</v>
       </c>
       <c r="Z196" t="n">
-        <v>0.3796258866786957</v>
+        <v>26.04158973693848</v>
       </c>
     </row>
     <row r="197">
@@ -16572,10 +16572,10 @@
         </is>
       </c>
       <c r="Y197" t="n">
-        <v>0.3796162307262421</v>
+        <v>25.93120002746582</v>
       </c>
       <c r="Z197" t="n">
-        <v>0.379624217748642</v>
+        <v>25.84699821472168</v>
       </c>
     </row>
     <row r="198">
@@ -16666,10 +16666,10 @@
         </is>
       </c>
       <c r="Y198" t="n">
-        <v>0.379638671875</v>
+        <v>25.00695419311523</v>
       </c>
       <c r="Z198" t="n">
-        <v>0.37675541639328</v>
+        <v>10.41920375823975</v>
       </c>
     </row>
     <row r="199">
@@ -16760,10 +16760,10 @@
         </is>
       </c>
       <c r="Y199" t="n">
-        <v>0.3796373009681702</v>
+        <v>25.64667129516602</v>
       </c>
       <c r="Z199" t="n">
-        <v>0.373872697353363</v>
+        <v>11.44028186798096</v>
       </c>
     </row>
     <row r="200">
@@ -16854,10 +16854,10 @@
         </is>
       </c>
       <c r="Y200" t="n">
-        <v>0.3796356618404388</v>
+        <v>25.2981128692627</v>
       </c>
       <c r="Z200" t="n">
-        <v>0.3542651534080505</v>
+        <v>11.19142436981201</v>
       </c>
     </row>
     <row r="201">
@@ -16948,10 +16948,10 @@
         </is>
       </c>
       <c r="Y201" t="n">
-        <v>0.3796347677707672</v>
+        <v>26.35046577453613</v>
       </c>
       <c r="Z201" t="n">
-        <v>0.3482180535793304</v>
+        <v>12.96360874176025</v>
       </c>
     </row>
     <row r="202">
@@ -17042,10 +17042,10 @@
         </is>
       </c>
       <c r="Y202" t="n">
-        <v>0.3796336352825165</v>
+        <v>26.31686401367188</v>
       </c>
       <c r="Z202" t="n">
-        <v>0.3407611846923828</v>
+        <v>13.69285106658936</v>
       </c>
     </row>
     <row r="203">
@@ -17136,10 +17136,10 @@
         </is>
       </c>
       <c r="Y203" t="n">
-        <v>0.3796393871307373</v>
+        <v>25.20186614990234</v>
       </c>
       <c r="Z203" t="n">
-        <v>0.379638671875</v>
+        <v>18.58771133422852</v>
       </c>
     </row>
     <row r="204">
@@ -17230,10 +17230,10 @@
         </is>
       </c>
       <c r="Y204" t="n">
-        <v>0.379638671875</v>
+        <v>25.92230033874512</v>
       </c>
       <c r="Z204" t="n">
-        <v>0.3796373009681702</v>
+        <v>24.19836044311523</v>
       </c>
     </row>
     <row r="205">
@@ -17324,10 +17324,10 @@
         </is>
       </c>
       <c r="Y205" t="n">
-        <v>0.3796379268169403</v>
+        <v>25.59093284606934</v>
       </c>
       <c r="Z205" t="n">
-        <v>0.3796346485614777</v>
+        <v>23.1826000213623</v>
       </c>
     </row>
     <row r="206">
@@ -17418,10 +17418,10 @@
         </is>
       </c>
       <c r="Y206" t="n">
-        <v>0.3796361684799194</v>
+        <v>26.1877498626709</v>
       </c>
       <c r="Z206" t="n">
-        <v>0.3796309530735016</v>
+        <v>23.15024757385254</v>
       </c>
     </row>
     <row r="207">
@@ -17512,10 +17512,10 @@
         </is>
       </c>
       <c r="Y207" t="n">
-        <v>0.3796347081661224</v>
+        <v>26.02087211608887</v>
       </c>
       <c r="Z207" t="n">
-        <v>0.3796268105506897</v>
+        <v>22.9392261505127</v>
       </c>
     </row>
     <row r="208">
@@ -17606,10 +17606,10 @@
         </is>
       </c>
       <c r="Y208" t="n">
-        <v>0.3796381056308746</v>
+        <v>24.76094055175781</v>
       </c>
       <c r="Z208" t="n">
-        <v>0.3796386122703552</v>
+        <v>24.8641414642334</v>
       </c>
     </row>
     <row r="209">
@@ -17700,10 +17700,10 @@
         </is>
       </c>
       <c r="Y209" t="n">
-        <v>0.3796361088752747</v>
+        <v>25.38848686218262</v>
       </c>
       <c r="Z209" t="n">
-        <v>0.3796371817588806</v>
+        <v>25.60263824462891</v>
       </c>
     </row>
     <row r="210">
@@ -17794,10 +17794,10 @@
         </is>
       </c>
       <c r="Y210" t="n">
-        <v>0.3796350061893463</v>
+        <v>25.65730857849121</v>
       </c>
       <c r="Z210" t="n">
-        <v>0.3796359896659851</v>
+        <v>25.43716239929199</v>
       </c>
     </row>
     <row r="211">
@@ -17888,10 +17888,10 @@
         </is>
       </c>
       <c r="Y211" t="n">
-        <v>0.3796325325965881</v>
+        <v>25.85266494750977</v>
       </c>
       <c r="Z211" t="n">
-        <v>0.3796339333057404</v>
+        <v>25.79909324645996</v>
       </c>
     </row>
     <row r="212">
@@ -17982,10 +17982,10 @@
         </is>
       </c>
       <c r="Y212" t="n">
-        <v>0.3796278536319733</v>
+        <v>20.47559928894043</v>
       </c>
       <c r="Z212" t="n">
-        <v>0.3796378970146179</v>
+        <v>23.79915809631348</v>
       </c>
     </row>
     <row r="213">
@@ -18076,10 +18076,10 @@
         </is>
       </c>
       <c r="Y213" t="n">
-        <v>0.3796156644821167</v>
+        <v>20.55301666259766</v>
       </c>
       <c r="Z213" t="n">
-        <v>0.3796356916427612</v>
+        <v>24.1729736328125</v>
       </c>
     </row>
     <row r="214">
@@ -18170,10 +18170,10 @@
         </is>
       </c>
       <c r="Y214" t="n">
-        <v>0.3796092569828033</v>
+        <v>21.94481468200684</v>
       </c>
       <c r="Z214" t="n">
-        <v>0.3796337246894836</v>
+        <v>24.20870018005371</v>
       </c>
     </row>
     <row r="215">
@@ -18264,10 +18264,10 @@
         </is>
       </c>
       <c r="Y215" t="n">
-        <v>0.3795899152755737</v>
+        <v>22.17461585998535</v>
       </c>
       <c r="Z215" t="n">
-        <v>0.3796319961547852</v>
+        <v>25.44031143188477</v>
       </c>
     </row>
     <row r="216">
@@ -18358,10 +18358,10 @@
         </is>
       </c>
       <c r="Y216" t="n">
-        <v>0.3795594573020935</v>
+        <v>20.77868270874023</v>
       </c>
       <c r="Z216" t="n">
-        <v>0.3796293437480927</v>
+        <v>24.67362785339355</v>
       </c>
     </row>
     <row r="217">
@@ -18452,10 +18452,10 @@
         </is>
       </c>
       <c r="Y217" t="n">
-        <v>0.3796381950378418</v>
+        <v>24.59074211120605</v>
       </c>
       <c r="Z217" t="n">
-        <v>0.3796378374099731</v>
+        <v>24.2480297088623</v>
       </c>
     </row>
     <row r="218">
@@ -18546,10 +18546,10 @@
         </is>
       </c>
       <c r="Y218" t="n">
-        <v>0.3796363174915314</v>
+        <v>24.52533149719238</v>
       </c>
       <c r="Z218" t="n">
-        <v>0.3796356022357941</v>
+        <v>24.0734806060791</v>
       </c>
     </row>
     <row r="219">
@@ -18640,10 +18640,10 @@
         </is>
       </c>
       <c r="Y219" t="n">
-        <v>0.3796305954456329</v>
+        <v>23.41120529174805</v>
       </c>
       <c r="Z219" t="n">
-        <v>0.3796298503875732</v>
+        <v>23.14091110229492</v>
       </c>
     </row>
     <row r="220">
@@ -18734,10 +18734,10 @@
         </is>
       </c>
       <c r="Y220" t="n">
-        <v>0.379626601934433</v>
+        <v>24.91095161437988</v>
       </c>
       <c r="Z220" t="n">
-        <v>0.3796245455741882</v>
+        <v>24.36325836181641</v>
       </c>
     </row>
     <row r="221">
@@ -18828,10 +18828,10 @@
         </is>
       </c>
       <c r="Y221" t="n">
-        <v>0.3795709311962128</v>
+        <v>17.5189380645752</v>
       </c>
       <c r="Z221" t="n">
-        <v>0.3796291351318359</v>
+        <v>21.51308250427246</v>
       </c>
     </row>
     <row r="222">
@@ -18922,10 +18922,10 @@
         </is>
       </c>
       <c r="Y222" t="n">
-        <v>0.3795017898082733</v>
+        <v>17.96441078186035</v>
       </c>
       <c r="Z222" t="n">
-        <v>0.379618227481842</v>
+        <v>21.3467845916748</v>
       </c>
     </row>
     <row r="223">
@@ -19016,10 +19016,10 @@
         </is>
       </c>
       <c r="Y223" t="n">
-        <v>0.3793957531452179</v>
+        <v>16.45916175842285</v>
       </c>
       <c r="Z223" t="n">
-        <v>0.3795905709266663</v>
+        <v>19.67794418334961</v>
       </c>
     </row>
     <row r="224">
@@ -19110,10 +19110,10 @@
         </is>
       </c>
       <c r="Y224" t="n">
-        <v>0.3793855309486389</v>
+        <v>21.70954895019531</v>
       </c>
       <c r="Z224" t="n">
-        <v>0.3795867562294006</v>
+        <v>24.68449401855469</v>
       </c>
     </row>
     <row r="225">
@@ -19204,10 +19204,10 @@
         </is>
       </c>
       <c r="Y225" t="n">
-        <v>0.3796369135379791</v>
+        <v>23.2055606842041</v>
       </c>
       <c r="Z225" t="n">
-        <v>0.3795995712280273</v>
+        <v>18.36164665222168</v>
       </c>
     </row>
     <row r="226">
@@ -19298,10 +19298,10 @@
         </is>
       </c>
       <c r="Y226" t="n">
-        <v>0.379633754491806</v>
+        <v>23.01064872741699</v>
       </c>
       <c r="Z226" t="n">
-        <v>0.3795590698719025</v>
+        <v>17.72159004211426</v>
       </c>
     </row>
     <row r="227">
@@ -19392,10 +19392,10 @@
         </is>
       </c>
       <c r="Y227" t="n">
-        <v>0.3796246349811554</v>
+        <v>21.88936805725098</v>
       </c>
       <c r="Z227" t="n">
-        <v>0.3795492053031921</v>
+        <v>19.69233894348145</v>
       </c>
     </row>
     <row r="228">
@@ -19486,10 +19486,10 @@
         </is>
       </c>
       <c r="Y228" t="n">
-        <v>0.3796198070049286</v>
+        <v>24.32541084289551</v>
       </c>
       <c r="Z228" t="n">
-        <v>0.3795200288295746</v>
+        <v>20.74316215515137</v>
       </c>
     </row>
     <row r="229">
@@ -19580,10 +19580,10 @@
         </is>
       </c>
       <c r="Y229" t="n">
-        <v>0.3796115219593048</v>
+        <v>23.9190502166748</v>
       </c>
       <c r="Z229" t="n">
-        <v>0.3795072138309479</v>
+        <v>21.11017036437988</v>
       </c>
     </row>
     <row r="230">
@@ -19674,10 +19674,10 @@
         </is>
       </c>
       <c r="Y230" t="n">
-        <v>0.3796194791793823</v>
+        <v>19.55802345275879</v>
       </c>
       <c r="Z230" t="n">
-        <v>0.3796391189098358</v>
+        <v>24.67701721191406</v>
       </c>
     </row>
     <row r="231">
@@ -19768,10 +19768,10 @@
         </is>
       </c>
       <c r="Y231" t="n">
-        <v>0.37959885597229</v>
+        <v>19.36430549621582</v>
       </c>
       <c r="Z231" t="n">
-        <v>0.3796381652355194</v>
+        <v>25.4340877532959</v>
       </c>
     </row>
     <row r="232">
@@ -19862,10 +19862,10 @@
         </is>
       </c>
       <c r="Y232" t="n">
-        <v>0.3795871734619141</v>
+        <v>21.40599632263184</v>
       </c>
       <c r="Z232" t="n">
-        <v>0.3796372413635254</v>
+        <v>25.57293128967285</v>
       </c>
     </row>
     <row r="233">
@@ -19956,10 +19956,10 @@
         </is>
       </c>
       <c r="Y233" t="n">
-        <v>0.3795839846134186</v>
+        <v>23.43264961242676</v>
       </c>
       <c r="Z233" t="n">
-        <v>0.379636824131012</v>
+        <v>26.47029495239258</v>
       </c>
     </row>
     <row r="234">
@@ -20050,10 +20050,10 @@
         </is>
       </c>
       <c r="Y234" t="n">
-        <v>0.3795579969882965</v>
+        <v>21.3541202545166</v>
       </c>
       <c r="Z234" t="n">
-        <v>0.3796356916427612</v>
+        <v>26.02038383483887</v>
       </c>
     </row>
     <row r="235">
@@ -20144,10 +20144,10 @@
         </is>
       </c>
       <c r="Y235" t="n">
-        <v>0.379547655582428</v>
+        <v>21.5084342956543</v>
       </c>
       <c r="Z235" t="n">
-        <v>0.3796344697475433</v>
+        <v>25.61045837402344</v>
       </c>
     </row>
     <row r="236">
@@ -20238,10 +20238,10 @@
         </is>
       </c>
       <c r="Y236" t="n">
-        <v>0.3795390129089355</v>
+        <v>22.8670482635498</v>
       </c>
       <c r="Z236" t="n">
-        <v>0.3796333372592926</v>
+        <v>26.27614784240723</v>
       </c>
     </row>
     <row r="237">
@@ -20332,10 +20332,10 @@
         </is>
       </c>
       <c r="Y237" t="n">
-        <v>0.3796342313289642</v>
+        <v>22.10528373718262</v>
       </c>
       <c r="Z237" t="n">
-        <v>0.3794980347156525</v>
+        <v>15.332688331604</v>
       </c>
     </row>
     <row r="238">
@@ -20426,10 +20426,10 @@
         </is>
       </c>
       <c r="Y238" t="n">
-        <v>0.3796283900737762</v>
+        <v>21.70401954650879</v>
       </c>
       <c r="Z238" t="n">
-        <v>0.3793559968471527</v>
+        <v>15.44547080993652</v>
       </c>
     </row>
     <row r="239">
@@ -20520,10 +20520,10 @@
         </is>
       </c>
       <c r="Y239" t="n">
-        <v>0.3796188831329346</v>
+        <v>22.03613090515137</v>
       </c>
       <c r="Z239" t="n">
-        <v>0.3792878687381744</v>
+        <v>16.48841285705566</v>
       </c>
     </row>
     <row r="240">
@@ -20614,10 +20614,10 @@
         </is>
       </c>
       <c r="Y240" t="n">
-        <v>0.3796041309833527</v>
+        <v>22.83470726013184</v>
       </c>
       <c r="Z240" t="n">
-        <v>0.3792514801025391</v>
+        <v>17.8979663848877</v>
       </c>
     </row>
     <row r="241">
@@ -20708,10 +20708,10 @@
         </is>
       </c>
       <c r="Y241" t="n">
-        <v>0.3795875608921051</v>
+        <v>21.7374324798584</v>
       </c>
       <c r="Z241" t="n">
-        <v>0.3792257905006409</v>
+        <v>18.53005027770996</v>
       </c>
     </row>
     <row r="242">
@@ -20802,10 +20802,10 @@
         </is>
       </c>
       <c r="Y242" t="n">
-        <v>0.3795688152313232</v>
+        <v>21.96993064880371</v>
       </c>
       <c r="Z242" t="n">
-        <v>0.3791774809360504</v>
+        <v>18.43496513366699</v>
       </c>
     </row>
     <row r="243">
@@ -20896,10 +20896,10 @@
         </is>
       </c>
       <c r="Y243" t="n">
-        <v>0.379530280828476</v>
+        <v>21.77663040161133</v>
       </c>
       <c r="Z243" t="n">
-        <v>0.3790704309940338</v>
+        <v>17.93736457824707</v>
       </c>
     </row>
     <row r="244">
@@ -20969,7 +20969,7 @@
       </c>
       <c r="Y244" t="inlineStr"/>
       <c r="Z244" t="n">
-        <v>0.3796373307704926</v>
+        <v>23.46097373962402</v>
       </c>
     </row>
     <row r="245">
@@ -21039,7 +21039,7 @@
       </c>
       <c r="Y245" t="inlineStr"/>
       <c r="Z245" t="n">
-        <v>0.3796346187591553</v>
+        <v>23.47938346862793</v>
       </c>
     </row>
     <row r="246">
@@ -21109,7 +21109,7 @@
       </c>
       <c r="Y246" t="inlineStr"/>
       <c r="Z246" t="n">
-        <v>0.3796325922012329</v>
+        <v>24.00846672058105</v>
       </c>
     </row>
     <row r="247">
@@ -21179,7 +21179,7 @@
       </c>
       <c r="Y247" t="inlineStr"/>
       <c r="Z247" t="n">
-        <v>0.3795326352119446</v>
+        <v>20.89084815979004</v>
       </c>
     </row>
     <row r="248">
@@ -21249,7 +21249,7 @@
       </c>
       <c r="Y248" t="inlineStr"/>
       <c r="Z248" t="n">
-        <v>0.3795295655727386</v>
+        <v>24.56941986083984</v>
       </c>
     </row>
     <row r="249">
@@ -21340,10 +21340,10 @@
         </is>
       </c>
       <c r="Y249" t="n">
-        <v>0.379638671875</v>
+        <v>24.2271556854248</v>
       </c>
       <c r="Z249" t="n">
-        <v>0.379639208316803</v>
+        <v>24.92769050598145</v>
       </c>
     </row>
     <row r="250">
@@ -21434,10 +21434,10 @@
         </is>
       </c>
       <c r="Y250" t="n">
-        <v>0.3796373009681702</v>
+        <v>25.36113166809082</v>
       </c>
       <c r="Z250" t="n">
-        <v>0.3796383738517761</v>
+        <v>25.96327018737793</v>
       </c>
     </row>
     <row r="251">
@@ -21528,10 +21528,10 @@
         </is>
       </c>
       <c r="Y251" t="n">
-        <v>0.3796361088752747</v>
+        <v>25.25097465515137</v>
       </c>
       <c r="Z251" t="n">
-        <v>0.3796371817588806</v>
+        <v>25.55327033996582</v>
       </c>
     </row>
     <row r="252">
@@ -21622,10 +21622,10 @@
         </is>
       </c>
       <c r="Y252" t="n">
-        <v>0.379635363817215</v>
+        <v>26.2459774017334</v>
       </c>
       <c r="Z252" t="n">
-        <v>0.3796364367008209</v>
+        <v>26.45202445983887</v>
       </c>
     </row>
     <row r="253">
@@ -21716,10 +21716,10 @@
         </is>
       </c>
       <c r="Y253" t="n">
-        <v>0.3796334862709045</v>
+        <v>24.68478202819824</v>
       </c>
       <c r="Z253" t="n">
-        <v>0.379634290933609</v>
+        <v>24.73026657104492</v>
       </c>
     </row>
     <row r="254">
@@ -21810,10 +21810,10 @@
         </is>
       </c>
       <c r="Y254" t="n">
-        <v>0.3796369135379791</v>
+        <v>23.13703155517578</v>
       </c>
       <c r="Z254" t="n">
-        <v>0.3796332478523254</v>
+        <v>21.75067329406738</v>
       </c>
     </row>
     <row r="255">
@@ -21904,10 +21904,10 @@
         </is>
       </c>
       <c r="Y255" t="n">
-        <v>0.379633754491806</v>
+        <v>23.10347747802734</v>
       </c>
       <c r="Z255" t="n">
-        <v>0.3796264231204987</v>
+        <v>21.31551170349121</v>
       </c>
     </row>
     <row r="256">
@@ -21998,10 +21998,10 @@
         </is>
       </c>
       <c r="Y256" t="n">
-        <v>0.379609227180481</v>
+        <v>21.6052074432373</v>
       </c>
       <c r="Z256" t="n">
-        <v>0.3796234726905823</v>
+        <v>23.14513206481934</v>
       </c>
     </row>
     <row r="257">
@@ -22092,10 +22092,10 @@
         </is>
       </c>
       <c r="Y257" t="n">
-        <v>0.3795996904373169</v>
+        <v>22.92651176452637</v>
       </c>
       <c r="Z257" t="n">
-        <v>0.3795491755008698</v>
+        <v>21.13325881958008</v>
       </c>
     </row>
     <row r="258">
@@ -22186,10 +22186,10 @@
         </is>
       </c>
       <c r="Y258" t="n">
-        <v>0.3795749843120575</v>
+        <v>22.14194679260254</v>
       </c>
       <c r="Z258" t="n">
-        <v>0.379548043012619</v>
+        <v>23.92120552062988</v>
       </c>
     </row>
     <row r="259">
@@ -22280,10 +22280,10 @@
         </is>
       </c>
       <c r="Y259" t="n">
-        <v>0.3795627653598785</v>
+        <v>23.21275901794434</v>
       </c>
       <c r="Z259" t="n">
-        <v>0.3795464932918549</v>
+        <v>25.22844505310059</v>
       </c>
     </row>
     <row r="260">
@@ -22353,7 +22353,7 @@
       </c>
       <c r="Y260" t="inlineStr"/>
       <c r="Z260" t="n">
-        <v>0.3795410096645355</v>
+        <v>23.03871726989746</v>
       </c>
     </row>
     <row r="261">
@@ -22444,10 +22444,10 @@
         </is>
       </c>
       <c r="Y261" t="n">
-        <v>0.3795295655727386</v>
+        <v>11.54991436004639</v>
       </c>
       <c r="Z261" t="n">
-        <v>0.3796188533306122</v>
+        <v>14.10704803466797</v>
       </c>
     </row>
     <row r="262">
@@ -22538,10 +22538,10 @@
         </is>
       </c>
       <c r="Y262" t="n">
-        <v>0.3794190883636475</v>
+        <v>17.59087181091309</v>
       </c>
       <c r="Z262" t="n">
-        <v>0.3795976042747498</v>
+        <v>20.3756103515625</v>
       </c>
     </row>
     <row r="263">
@@ -22632,10 +22632,10 @@
         </is>
       </c>
       <c r="Y263" t="n">
-        <v>0.3792602121829987</v>
+        <v>15.34986782073975</v>
       </c>
       <c r="Z263" t="n">
-        <v>0.3795035183429718</v>
+        <v>17.36676597595215</v>
       </c>
     </row>
     <row r="264">
@@ -22726,10 +22726,10 @@
         </is>
       </c>
       <c r="Y264" t="n">
-        <v>0.3791170418262482</v>
+        <v>16.24870872497559</v>
       </c>
       <c r="Z264" t="n">
-        <v>0.379092276096344</v>
+        <v>16.00027656555176</v>
       </c>
     </row>
     <row r="265">
@@ -22820,10 +22820,10 @@
         </is>
       </c>
       <c r="Y265" t="n">
-        <v>0.3786779642105103</v>
+        <v>15.39744091033936</v>
       </c>
       <c r="Z265" t="n">
-        <v>0.3788159787654877</v>
+        <v>16.09301948547363</v>
       </c>
     </row>
     <row r="266">
@@ -22914,10 +22914,10 @@
         </is>
       </c>
       <c r="Y266" t="n">
-        <v>0.3795957267284393</v>
+        <v>19.0519962310791</v>
       </c>
       <c r="Z266" t="n">
-        <v>0.3796386122703552</v>
+        <v>24.76716041564941</v>
       </c>
     </row>
     <row r="267">
@@ -23008,10 +23008,10 @@
         </is>
       </c>
       <c r="Y267" t="n">
-        <v>0.3795514106750488</v>
+        <v>18.72305870056152</v>
       </c>
       <c r="Z267" t="n">
-        <v>0.3796371817588806</v>
+        <v>25.15634346008301</v>
       </c>
     </row>
     <row r="268">
@@ -23102,10 +23102,10 @@
         </is>
       </c>
       <c r="Y268" t="n">
-        <v>0.3782335817813873</v>
+        <v>17.2852668762207</v>
       </c>
       <c r="Z268" t="n">
-        <v>0.3796347081661224</v>
+        <v>24.26237678527832</v>
       </c>
     </row>
     <row r="269">
@@ -23196,10 +23196,10 @@
         </is>
       </c>
       <c r="Y269" t="n">
-        <v>0.3781550824642181</v>
+        <v>19.65757942199707</v>
       </c>
       <c r="Z269" t="n">
-        <v>0.3796330392360687</v>
+        <v>26.28471946716309</v>
       </c>
     </row>
     <row r="270">
@@ -23270,10 +23270,10 @@
         </is>
       </c>
       <c r="Y270" t="n">
-        <v>0.3796288371086121</v>
+        <v>20.99609565734863</v>
       </c>
       <c r="Z270" t="n">
-        <v>0.3790803551673889</v>
+        <v>13.09455585479736</v>
       </c>
     </row>
     <row r="271">
@@ -23344,10 +23344,10 @@
         </is>
       </c>
       <c r="Y271" t="n">
-        <v>0.3796176016330719</v>
+        <v>20.46683311462402</v>
       </c>
       <c r="Z271" t="n">
-        <v>0.378520667552948</v>
+        <v>13.92189121246338</v>
       </c>
     </row>
     <row r="272">
@@ -23418,10 +23418,10 @@
         </is>
       </c>
       <c r="Y272" t="n">
-        <v>0.3795903027057648</v>
+        <v>21.03094673156738</v>
       </c>
       <c r="Z272" t="n">
-        <v>0.3783242404460907</v>
+        <v>14.86188125610352</v>
       </c>
     </row>
     <row r="273">
@@ -23492,10 +23492,10 @@
         </is>
       </c>
       <c r="Y273" t="n">
-        <v>0.3795746266841888</v>
+        <v>21.86505508422852</v>
       </c>
       <c r="Z273" t="n">
-        <v>0.3774330615997314</v>
+        <v>14.53626537322998</v>
       </c>
     </row>
     <row r="274">
@@ -23554,7 +23554,7 @@
         </is>
       </c>
       <c r="Y274" t="n">
-        <v>0.3795489966869354</v>
+        <v>21.44951820373535</v>
       </c>
       <c r="Z274" t="inlineStr"/>
     </row>
@@ -23646,10 +23646,10 @@
         </is>
       </c>
       <c r="Y275" t="n">
-        <v>0.37909334897995</v>
+        <v>13.58290004730225</v>
       </c>
       <c r="Z275" t="n">
-        <v>0.3786599040031433</v>
+        <v>8.594500541687012</v>
       </c>
     </row>
     <row r="276">
@@ -23740,10 +23740,10 @@
         </is>
       </c>
       <c r="Y276" t="n">
-        <v>0.3785465955734253</v>
+        <v>14.24088382720947</v>
       </c>
       <c r="Z276" t="n">
-        <v>0.3776799738407135</v>
+        <v>14.43083572387695</v>
       </c>
     </row>
     <row r="277">
@@ -23834,10 +23834,10 @@
         </is>
       </c>
       <c r="Y277" t="n">
-        <v>0.3783386051654816</v>
+        <v>15.16430473327637</v>
       </c>
       <c r="Z277" t="n">
-        <v>0.3769303262233734</v>
+        <v>13.04209804534912</v>
       </c>
     </row>
     <row r="278">
@@ -23928,10 +23928,10 @@
         </is>
       </c>
       <c r="Y278" t="n">
-        <v>0.3777771294116974</v>
+        <v>14.98862171173096</v>
       </c>
       <c r="Z278" t="n">
-        <v>0.3751639723777771</v>
+        <v>12.55956077575684</v>
       </c>
     </row>
     <row r="279">
@@ -24022,10 +24022,10 @@
         </is>
       </c>
       <c r="Y279" t="n">
-        <v>0.3775268793106079</v>
+        <v>14.95833110809326</v>
       </c>
       <c r="Z279" t="n">
-        <v>0.3733889758586884</v>
+        <v>11.96781063079834</v>
       </c>
     </row>
     <row r="280">
@@ -24116,10 +24116,10 @@
         </is>
       </c>
       <c r="Y280" t="n">
-        <v>0.3796384036540985</v>
+        <v>24.47809219360352</v>
       </c>
       <c r="Z280" t="n">
-        <v>0.3796383440494537</v>
+        <v>24.17193031311035</v>
       </c>
     </row>
     <row r="281">
@@ -24210,10 +24210,10 @@
         </is>
       </c>
       <c r="Y281" t="n">
-        <v>0.3796367347240448</v>
+        <v>25.0849609375</v>
       </c>
       <c r="Z281" t="n">
-        <v>0.3796366453170776</v>
+        <v>24.91243553161621</v>
       </c>
     </row>
     <row r="282">
@@ -24304,10 +24304,10 @@
         </is>
       </c>
       <c r="Y282" t="n">
-        <v>0.3796353936195374</v>
+        <v>25.16440200805664</v>
       </c>
       <c r="Z282" t="n">
-        <v>0.3796344995498657</v>
+        <v>24.51609230041504</v>
       </c>
     </row>
     <row r="283">
@@ -24398,10 +24398,10 @@
         </is>
       </c>
       <c r="Y283" t="n">
-        <v>0.3796341717243195</v>
+        <v>26.02934074401855</v>
       </c>
       <c r="Z283" t="n">
-        <v>0.3796330690383911</v>
+        <v>25.75007438659668</v>
       </c>
     </row>
     <row r="284">
@@ -24492,10 +24492,10 @@
         </is>
       </c>
       <c r="Y284" t="n">
-        <v>0.3796373307704926</v>
+        <v>23.64777374267578</v>
       </c>
       <c r="Z284" t="n">
-        <v>0.3796196579933167</v>
+        <v>19.90903663635254</v>
       </c>
     </row>
     <row r="285">
@@ -24586,10 +24586,10 @@
         </is>
       </c>
       <c r="Y285" t="n">
-        <v>0.3796345889568329</v>
+        <v>24.18618583679199</v>
       </c>
       <c r="Z285" t="n">
-        <v>0.3795992732048035</v>
+        <v>19.89242744445801</v>
       </c>
     </row>
     <row r="286">
@@ -24680,10 +24680,10 @@
         </is>
       </c>
       <c r="Y286" t="n">
-        <v>0.3796294927597046</v>
+        <v>23.28568649291992</v>
       </c>
       <c r="Z286" t="n">
-        <v>0.3795895576477051</v>
+        <v>21.53503227233887</v>
       </c>
     </row>
     <row r="287">
@@ -24774,10 +24774,10 @@
         </is>
       </c>
       <c r="Y287" t="n">
-        <v>0.3796255588531494</v>
+        <v>25.10554504394531</v>
       </c>
       <c r="Z287" t="n">
-        <v>0.3795779347419739</v>
+        <v>23.07236289978027</v>
       </c>
     </row>
     <row r="288">
@@ -24868,10 +24868,10 @@
         </is>
       </c>
       <c r="Y288" t="n">
-        <v>0.3796307444572449</v>
+        <v>20.98633003234863</v>
       </c>
       <c r="Z288" t="n">
-        <v>0.3796351850032806</v>
+        <v>22.21015167236328</v>
       </c>
     </row>
     <row r="289">
@@ -24962,10 +24962,10 @@
         </is>
       </c>
       <c r="Y289" t="n">
-        <v>0.3796214163303375</v>
+        <v>21.06899452209473</v>
       </c>
       <c r="Z289" t="n">
-        <v>0.3796302974224091</v>
+        <v>21.61586570739746</v>
       </c>
     </row>
     <row r="290">
@@ -25056,10 +25056,10 @@
         </is>
       </c>
       <c r="Y290" t="n">
-        <v>0.3796155452728271</v>
+        <v>22.41999244689941</v>
       </c>
       <c r="Z290" t="n">
-        <v>0.3796212673187256</v>
+        <v>22.17990303039551</v>
       </c>
     </row>
     <row r="291">
@@ -25150,10 +25150,10 @@
         </is>
       </c>
       <c r="Y291" t="n">
-        <v>0.379606157541275</v>
+        <v>23.43299293518066</v>
       </c>
       <c r="Z291" t="n">
-        <v>0.3796135783195496</v>
+        <v>23.47660636901855</v>
       </c>
     </row>
     <row r="292">
@@ -25244,10 +25244,10 @@
         </is>
       </c>
       <c r="Y292" t="n">
-        <v>0.3795860111713409</v>
+        <v>21.53659820556641</v>
       </c>
       <c r="Z292" t="n">
-        <v>0.3796053528785706</v>
+        <v>22.29429244995117</v>
       </c>
     </row>
     <row r="293">
@@ -25338,10 +25338,10 @@
         </is>
       </c>
       <c r="Y293" t="n">
-        <v>0.3795722424983978</v>
+        <v>21.7617130279541</v>
       </c>
       <c r="Z293" t="n">
-        <v>0.3795920312404633</v>
+        <v>22.14233589172363</v>
       </c>
     </row>
     <row r="294">
@@ -25432,10 +25432,10 @@
         </is>
       </c>
       <c r="Y294" t="n">
-        <v>0.3765515983104706</v>
+        <v>10.11653327941895</v>
       </c>
       <c r="Z294" t="n">
-        <v>0.3796104490756989</v>
+        <v>19.23664283752441</v>
       </c>
     </row>
     <row r="295">
@@ -25526,10 +25526,10 @@
         </is>
       </c>
       <c r="Y295" t="n">
-        <v>0.373464822769165</v>
+        <v>12.2392053604126</v>
       </c>
       <c r="Z295" t="n">
-        <v>0.3795807957649231</v>
+        <v>18.65160942077637</v>
       </c>
     </row>
     <row r="296">
@@ -25620,10 +25620,10 @@
         </is>
       </c>
       <c r="Y296" t="n">
-        <v>0.3707796633243561</v>
+        <v>11.8494758605957</v>
       </c>
       <c r="Z296" t="n">
-        <v>0.3794930875301361</v>
+        <v>18.94733619689941</v>
       </c>
     </row>
     <row r="297">
@@ -25714,10 +25714,10 @@
         </is>
       </c>
       <c r="Y297" t="n">
-        <v>0.3672561347484589</v>
+        <v>11.26512432098389</v>
       </c>
       <c r="Z297" t="n">
-        <v>0.3794108927249908</v>
+        <v>18.93807029724121</v>
       </c>
     </row>
     <row r="298">
@@ -25808,10 +25808,10 @@
         </is>
       </c>
       <c r="Y298" t="n">
-        <v>0.3653540313243866</v>
+        <v>11.8195161819458</v>
       </c>
       <c r="Z298" t="n">
-        <v>0.3793842196464539</v>
+        <v>20.19733810424805</v>
       </c>
     </row>
     <row r="299">
@@ -25902,10 +25902,10 @@
         </is>
       </c>
       <c r="Y299" t="n">
-        <v>0.3796381950378418</v>
+        <v>24.17973327636719</v>
       </c>
       <c r="Z299" t="n">
-        <v>0.3796371221542358</v>
+        <v>23.71771621704102</v>
       </c>
     </row>
     <row r="300">
@@ -25996,10 +25996,10 @@
         </is>
       </c>
       <c r="Y300" t="n">
-        <v>0.3796363174915314</v>
+        <v>24.53169250488281</v>
       </c>
       <c r="Z300" t="n">
-        <v>0.3796341717243195</v>
+        <v>23.83077049255371</v>
       </c>
     </row>
     <row r="301">
@@ -26090,10 +26090,10 @@
         </is>
       </c>
       <c r="Y301" t="n">
-        <v>0.3796258270740509</v>
+        <v>22.99184226989746</v>
       </c>
       <c r="Z301" t="n">
-        <v>0.3796288073062897</v>
+        <v>23.45432472229004</v>
       </c>
     </row>
     <row r="302">
@@ -26184,10 +26184,10 @@
         </is>
       </c>
       <c r="Y302" t="n">
-        <v>0.3796225786209106</v>
+        <v>23.53721809387207</v>
       </c>
       <c r="Z302" t="n">
-        <v>0.3796232640743256</v>
+        <v>23.1613941192627</v>
       </c>
     </row>
     <row r="303">
@@ -26278,10 +26278,10 @@
         </is>
       </c>
       <c r="Y303" t="n">
-        <v>0.3796117901802063</v>
+        <v>24.59985160827637</v>
       </c>
       <c r="Z303" t="n">
-        <v>0.3796183466911316</v>
+        <v>25.00343132019043</v>
       </c>
     </row>
     <row r="304">
@@ -26372,10 +26372,10 @@
         </is>
       </c>
       <c r="Y304" t="n">
-        <v>0.3796391785144806</v>
+        <v>25.10055541992188</v>
       </c>
       <c r="Z304" t="n">
-        <v>0.3796377182006836</v>
+        <v>23.97102355957031</v>
       </c>
     </row>
     <row r="305">
@@ -26466,10 +26466,10 @@
         </is>
       </c>
       <c r="Y305" t="n">
-        <v>0.3796382546424866</v>
+        <v>25.77775955200195</v>
       </c>
       <c r="Z305" t="n">
-        <v>0.3796353340148926</v>
+        <v>24.63340187072754</v>
       </c>
     </row>
     <row r="306">
@@ -26560,10 +26560,10 @@
         </is>
       </c>
       <c r="Y306" t="n">
-        <v>0.3796340525150299</v>
+        <v>24.12677192687988</v>
       </c>
       <c r="Z306" t="n">
-        <v>0.3796306550502777</v>
+        <v>23.67996788024902</v>
       </c>
     </row>
     <row r="307">
@@ -26654,10 +26654,10 @@
         </is>
       </c>
       <c r="Y307" t="n">
-        <v>0.3796335160732269</v>
+        <v>26.5407886505127</v>
       </c>
       <c r="Z307" t="n">
-        <v>0.3796293437480927</v>
+        <v>25.92049980163574</v>
       </c>
     </row>
     <row r="308">
@@ -26748,10 +26748,10 @@
         </is>
       </c>
       <c r="Y308" t="n">
-        <v>0.3796384036540985</v>
+        <v>23.54263687133789</v>
       </c>
       <c r="Z308" t="n">
-        <v>0.3796351850032806</v>
+        <v>22.80107688903809</v>
       </c>
     </row>
     <row r="309">
@@ -26842,10 +26842,10 @@
         </is>
       </c>
       <c r="Y309" t="n">
-        <v>0.3796367347240448</v>
+        <v>24.33650207519531</v>
       </c>
       <c r="Z309" t="n">
-        <v>0.3796302974224091</v>
+        <v>22.96444511413574</v>
       </c>
     </row>
     <row r="310">
@@ -26936,10 +26936,10 @@
         </is>
       </c>
       <c r="Y310" t="n">
-        <v>0.3796345889568329</v>
+        <v>23.87649726867676</v>
       </c>
       <c r="Z310" t="n">
-        <v>0.3796171545982361</v>
+        <v>22.35861778259277</v>
       </c>
     </row>
     <row r="311">
@@ -27030,10 +27030,10 @@
         </is>
       </c>
       <c r="Y311" t="n">
-        <v>0.3796016573905945</v>
+        <v>21.16183090209961</v>
       </c>
       <c r="Z311" t="n">
-        <v>0.3794997334480286</v>
+        <v>19.85098838806152</v>
       </c>
     </row>
     <row r="312">
@@ -27124,10 +27124,10 @@
         </is>
       </c>
       <c r="Y312" t="n">
-        <v>0.3699811398983002</v>
+        <v>8.440690994262695</v>
       </c>
       <c r="Z312" t="n">
-        <v>0.378720223903656</v>
+        <v>12.17140865325928</v>
       </c>
     </row>
     <row r="313">
@@ -27218,10 +27218,10 @@
         </is>
       </c>
       <c r="Y313" t="n">
-        <v>0.3603433072566986</v>
+        <v>10.77820301055908</v>
       </c>
       <c r="Z313" t="n">
-        <v>0.3778003752231598</v>
+        <v>13.3051290512085</v>
       </c>
     </row>
     <row r="314">
@@ -27312,10 +27312,10 @@
         </is>
       </c>
       <c r="Y314" t="n">
-        <v>0.3592051863670349</v>
+        <v>11.82165241241455</v>
       </c>
       <c r="Z314" t="n">
-        <v>0.3773256242275238</v>
+        <v>13.98640727996826</v>
       </c>
     </row>
     <row r="315">
@@ -27406,10 +27406,10 @@
         </is>
       </c>
       <c r="Y315" t="n">
-        <v>0.3558497428894043</v>
+        <v>11.77424621582031</v>
       </c>
       <c r="Z315" t="n">
-        <v>0.3768914341926575</v>
+        <v>14.26140308380127</v>
       </c>
     </row>
     <row r="316">
@@ -27500,10 +27500,10 @@
         </is>
       </c>
       <c r="Y316" t="n">
-        <v>0.3496569991111755</v>
+        <v>10.81701374053955</v>
       </c>
       <c r="Z316" t="n">
-        <v>0.3765613436698914</v>
+        <v>14.0366907119751</v>
       </c>
     </row>
     <row r="317">
@@ -27594,10 +27594,10 @@
         </is>
       </c>
       <c r="Y317" t="n">
-        <v>0.3365474343299866</v>
+        <v>11.03101444244385</v>
       </c>
       <c r="Z317" t="n">
-        <v>0.3760345578193665</v>
+        <v>14.26826763153076</v>
       </c>
     </row>
     <row r="318">
@@ -27688,10 +27688,10 @@
         </is>
       </c>
       <c r="Y318" t="n">
-        <v>0.3115057945251465</v>
+        <v>10.31679439544678</v>
       </c>
       <c r="Z318" t="n">
-        <v>0.3753364086151123</v>
+        <v>13.9829683303833</v>
       </c>
     </row>
     <row r="319">
@@ -27782,10 +27782,10 @@
         </is>
       </c>
       <c r="Y319" t="n">
-        <v>0.3796380460262299</v>
+        <v>24.72220039367676</v>
       </c>
       <c r="Z319" t="n">
-        <v>0.3792326748371124</v>
+        <v>14.51059532165527</v>
       </c>
     </row>
     <row r="320">
@@ -27876,10 +27876,10 @@
         </is>
       </c>
       <c r="Y320" t="n">
-        <v>0.3796359896659851</v>
+        <v>24.72174263000488</v>
       </c>
       <c r="Z320" t="n">
-        <v>0.3788252472877502</v>
+        <v>15.00707244873047</v>
       </c>
     </row>
     <row r="321">
@@ -27970,10 +27970,10 @@
         </is>
       </c>
       <c r="Y321" t="n">
-        <v>0.3796343207359314</v>
+        <v>25.15036582946777</v>
       </c>
       <c r="Z321" t="n">
-        <v>0.3773682713508606</v>
+        <v>14.94239139556885</v>
       </c>
     </row>
     <row r="322">
@@ -28064,10 +28064,10 @@
         </is>
       </c>
       <c r="Y322" t="n">
-        <v>0.3796306550502777</v>
+        <v>24.93720626831055</v>
       </c>
       <c r="Z322" t="n">
-        <v>0.3745661973953247</v>
+        <v>14.2759428024292</v>
       </c>
     </row>
     <row r="323">
@@ -28158,10 +28158,10 @@
         </is>
       </c>
       <c r="Y323" t="n">
-        <v>0.3796288669109344</v>
+        <v>20.82341766357422</v>
       </c>
       <c r="Z323" t="n">
-        <v>0.3796339333057404</v>
+        <v>22.04562187194824</v>
       </c>
     </row>
     <row r="324">
@@ -28252,10 +28252,10 @@
         </is>
       </c>
       <c r="Y324" t="n">
-        <v>0.3796176910400391</v>
+        <v>21.36866569519043</v>
       </c>
       <c r="Z324" t="n">
-        <v>0.3796278238296509</v>
+        <v>22.38291358947754</v>
       </c>
     </row>
     <row r="325">
@@ -28346,10 +28346,10 @@
         </is>
       </c>
       <c r="Y325" t="n">
-        <v>0.379579097032547</v>
+        <v>20.18606376647949</v>
       </c>
       <c r="Z325" t="n">
-        <v>0.3795972168445587</v>
+        <v>20.83981513977051</v>
       </c>
     </row>
     <row r="326">
@@ -28440,10 +28440,10 @@
         </is>
       </c>
       <c r="Y326" t="n">
-        <v>0.379559189081192</v>
+        <v>21.95446586608887</v>
       </c>
       <c r="Z326" t="n">
-        <v>0.3795685172080994</v>
+        <v>22.02171897888184</v>
       </c>
     </row>
     <row r="327">
@@ -28513,7 +28513,7 @@
       </c>
       <c r="Y327" t="inlineStr"/>
       <c r="Z327" t="n">
-        <v>0.3795638382434845</v>
+        <v>23.87143135070801</v>
       </c>
     </row>
     <row r="328">
@@ -28582,7 +28582,7 @@
         </is>
       </c>
       <c r="Y328" t="n">
-        <v>0.3791098594665527</v>
+        <v>14.08422660827637</v>
       </c>
       <c r="Z328" t="inlineStr"/>
     </row>
@@ -28652,7 +28652,7 @@
         </is>
       </c>
       <c r="Y329" t="n">
-        <v>0.3785796761512756</v>
+        <v>14.96945381164551</v>
       </c>
       <c r="Z329" t="inlineStr"/>
     </row>
@@ -28722,7 +28722,7 @@
         </is>
       </c>
       <c r="Y330" t="n">
-        <v>0.3757049441337585</v>
+        <v>14.62647342681885</v>
       </c>
       <c r="Z330" t="inlineStr"/>
     </row>
@@ -28792,7 +28792,7 @@
         </is>
       </c>
       <c r="Y331" t="n">
-        <v>0.3726798593997955</v>
+        <v>13.67904376983643</v>
       </c>
       <c r="Z331" t="inlineStr"/>
     </row>
@@ -28884,10 +28884,10 @@
         </is>
       </c>
       <c r="Y332" t="n">
-        <v>0.3796387314796448</v>
+        <v>24.25322914123535</v>
       </c>
       <c r="Z332" t="n">
-        <v>0.3796387314796448</v>
+        <v>24.36778450012207</v>
       </c>
     </row>
     <row r="333">
@@ -28978,10 +28978,10 @@
         </is>
       </c>
       <c r="Y333" t="n">
-        <v>0.3796373903751373</v>
+        <v>25.2880859375</v>
       </c>
       <c r="Z333" t="n">
-        <v>0.3796373903751373</v>
+        <v>25.50226211547852</v>
       </c>
     </row>
     <row r="334">
@@ -29072,10 +29072,10 @@
         </is>
       </c>
       <c r="Y334" t="n">
-        <v>0.3796353042125702</v>
+        <v>24.78006553649902</v>
       </c>
       <c r="Z334" t="n">
-        <v>0.3796359896659851</v>
+        <v>25.35725212097168</v>
       </c>
     </row>
     <row r="335">
@@ -29166,10 +29166,10 @@
         </is>
       </c>
       <c r="Y335" t="n">
-        <v>0.3796339333057404</v>
+        <v>25.62978935241699</v>
       </c>
       <c r="Z335" t="n">
-        <v>0.3796349167823792</v>
+        <v>26.06508827209473</v>
       </c>
     </row>
     <row r="336">
@@ -29260,10 +29260,10 @@
         </is>
       </c>
       <c r="Y336" t="n">
-        <v>0.3796361982822418</v>
+        <v>24.07616806030273</v>
       </c>
       <c r="Z336" t="n">
-        <v>0.3796266615390778</v>
+        <v>21.86168098449707</v>
       </c>
     </row>
     <row r="337">
@@ -29354,10 +29354,10 @@
         </is>
       </c>
       <c r="Y337" t="n">
-        <v>0.3796323537826538</v>
+        <v>23.7179126739502</v>
       </c>
       <c r="Z337" t="n">
-        <v>0.3796132504940033</v>
+        <v>20.83157539367676</v>
       </c>
     </row>
     <row r="338">
@@ -29448,10 +29448,10 @@
         </is>
       </c>
       <c r="Y338" t="n">
-        <v>0.3796222507953644</v>
+        <v>22.9797477722168</v>
       </c>
       <c r="Z338" t="n">
-        <v>0.3795850574970245</v>
+        <v>21.26103401184082</v>
       </c>
     </row>
     <row r="339">
@@ -29542,10 +29542,10 @@
         </is>
       </c>
       <c r="Y339" t="n">
-        <v>0.3796181678771973</v>
+        <v>24.9956111907959</v>
       </c>
       <c r="Z339" t="n">
-        <v>0.3795705735683441</v>
+        <v>22.79844856262207</v>
       </c>
     </row>
     <row r="340">
@@ -29615,7 +29615,7 @@
       </c>
       <c r="Y340" t="inlineStr"/>
       <c r="Z340" t="n">
-        <v>0.3796320855617523</v>
+        <v>22.29793930053711</v>
       </c>
     </row>
     <row r="341">
@@ -29685,7 +29685,7 @@
       </c>
       <c r="Y341" t="inlineStr"/>
       <c r="Z341" t="n">
-        <v>0.3796241283416748</v>
+        <v>21.33503150939941</v>
       </c>
     </row>
     <row r="342">
@@ -29755,7 +29755,7 @@
       </c>
       <c r="Y342" t="inlineStr"/>
       <c r="Z342" t="n">
-        <v>0.3795210421085358</v>
+        <v>19.95660972595215</v>
       </c>
     </row>
     <row r="343">
@@ -29825,7 +29825,7 @@
       </c>
       <c r="Y343" t="inlineStr"/>
       <c r="Z343" t="n">
-        <v>0.3795007765293121</v>
+        <v>22.47974014282227</v>
       </c>
     </row>
     <row r="344">
@@ -29916,10 +29916,10 @@
         </is>
       </c>
       <c r="Y344" t="n">
-        <v>0.3796367943286896</v>
+        <v>23.76485443115234</v>
       </c>
       <c r="Z344" t="n">
-        <v>0.3796350359916687</v>
+        <v>23.03129196166992</v>
       </c>
     </row>
     <row r="345">
@@ -30010,10 +30010,10 @@
         </is>
       </c>
       <c r="Y345" t="n">
-        <v>0.3796335160732269</v>
+        <v>23.78089332580566</v>
       </c>
       <c r="Z345" t="n">
-        <v>0.3796299695968628</v>
+        <v>22.76346588134766</v>
       </c>
     </row>
     <row r="346">
@@ -30104,10 +30104,10 @@
         </is>
       </c>
       <c r="Y346" t="n">
-        <v>0.3796274065971375</v>
+        <v>22.96476936340332</v>
       </c>
       <c r="Z346" t="n">
-        <v>0.3796237111091614</v>
+        <v>22.75234413146973</v>
       </c>
     </row>
     <row r="347">
@@ -30198,10 +30198,10 @@
         </is>
       </c>
       <c r="Y347" t="n">
-        <v>0.3796215355396271</v>
+        <v>23.9678783416748</v>
       </c>
       <c r="Z347" t="n">
-        <v>0.3796182870864868</v>
+        <v>23.9412784576416</v>
       </c>
     </row>
     <row r="348">
@@ -30292,10 +30292,10 @@
         </is>
       </c>
       <c r="Y348" t="n">
-        <v>0.3796185851097107</v>
+        <v>24.86312866210938</v>
       </c>
       <c r="Z348" t="n">
-        <v>0.3796117901802063</v>
+        <v>23.81270790100098</v>
       </c>
     </row>
     <row r="349">
@@ -30386,10 +30386,10 @@
         </is>
       </c>
       <c r="Y349" t="n">
-        <v>0.3796058893203735</v>
+        <v>23.59476661682129</v>
       </c>
       <c r="Z349" t="n">
-        <v>0.3796003758907318</v>
+        <v>22.97253608703613</v>
       </c>
     </row>
     <row r="350">
@@ -30460,10 +30460,10 @@
         </is>
       </c>
       <c r="Y350" t="n">
-        <v>0.3794911503791809</v>
+        <v>15.60523223876953</v>
       </c>
       <c r="Z350" t="n">
-        <v>0.3794659376144409</v>
+        <v>15.20650959014893</v>
       </c>
     </row>
     <row r="351">
@@ -30534,10 +30534,10 @@
         </is>
       </c>
       <c r="Y351" t="n">
-        <v>0.3793421983718872</v>
+        <v>16.05213928222656</v>
       </c>
       <c r="Z351" t="n">
-        <v>0.379291832447052</v>
+        <v>15.80877208709717</v>
       </c>
     </row>
     <row r="352">
@@ -30608,10 +30608,10 @@
         </is>
       </c>
       <c r="Y352" t="n">
-        <v>0.3792167007923126</v>
+        <v>16.82427215576172</v>
       </c>
       <c r="Z352" t="n">
-        <v>0.3792747855186462</v>
+        <v>18.35456275939941</v>
       </c>
     </row>
     <row r="353">
@@ -30682,10 +30682,10 @@
         </is>
       </c>
       <c r="Y353" t="n">
-        <v>0.3792074620723724</v>
+        <v>19.76045417785645</v>
       </c>
       <c r="Z353" t="n">
-        <v>0.3792658150196075</v>
+        <v>20.45795631408691</v>
       </c>
     </row>
     <row r="354">
@@ -30776,10 +30776,10 @@
         </is>
       </c>
       <c r="Y354" t="n">
-        <v>0.3796365261077881</v>
+        <v>23.33345031738281</v>
       </c>
       <c r="Z354" t="n">
-        <v>0.3796384632587433</v>
+        <v>24.23624801635742</v>
       </c>
     </row>
     <row r="355">
@@ -30870,10 +30870,10 @@
         </is>
       </c>
       <c r="Y355" t="n">
-        <v>0.379632979631424</v>
+        <v>22.83307838439941</v>
       </c>
       <c r="Z355" t="n">
-        <v>0.3796368539333344</v>
+        <v>24.71466827392578</v>
       </c>
     </row>
     <row r="356">
@@ -30964,10 +30964,10 @@
         </is>
       </c>
       <c r="Y356" t="n">
-        <v>0.3796282112598419</v>
+        <v>23.37314414978027</v>
       </c>
       <c r="Z356" t="n">
-        <v>0.3796354532241821</v>
+        <v>24.94147300720215</v>
       </c>
     </row>
     <row r="357">
@@ -31058,10 +31058,10 @@
         </is>
       </c>
       <c r="Y357" t="n">
-        <v>0.3796266615390778</v>
+        <v>25.32057571411133</v>
       </c>
       <c r="Z357" t="n">
-        <v>0.3796344995498657</v>
+        <v>26.0684700012207</v>
       </c>
     </row>
     <row r="358">
@@ -31152,10 +31152,10 @@
         </is>
       </c>
       <c r="Y358" t="n">
-        <v>0.3796363770961761</v>
+        <v>23.25318717956543</v>
       </c>
       <c r="Z358" t="n">
-        <v>0.3796322345733643</v>
+        <v>21.93876075744629</v>
       </c>
     </row>
     <row r="359">
@@ -31246,10 +31246,10 @@
         </is>
       </c>
       <c r="Y359" t="n">
-        <v>0.3796326518058777</v>
+        <v>23.20504188537598</v>
       </c>
       <c r="Z359" t="n">
-        <v>0.3796244263648987</v>
+        <v>21.83606719970703</v>
       </c>
     </row>
     <row r="360">
@@ -31340,10 +31340,10 @@
         </is>
       </c>
       <c r="Y360" t="n">
-        <v>0.379630982875824</v>
+        <v>24.0958080291748</v>
       </c>
       <c r="Z360" t="n">
-        <v>0.3796206712722778</v>
+        <v>23.04946327209473</v>
       </c>
     </row>
     <row r="361">
@@ -31434,10 +31434,10 @@
         </is>
       </c>
       <c r="Y361" t="n">
-        <v>0.3796238303184509</v>
+        <v>23.28067970275879</v>
       </c>
       <c r="Z361" t="n">
-        <v>0.3796083629131317</v>
+        <v>22.4300594329834</v>
       </c>
     </row>
     <row r="362">
@@ -31528,10 +31528,10 @@
         </is>
       </c>
       <c r="Y362" t="n">
-        <v>0.3796116411685944</v>
+        <v>23.67695045471191</v>
       </c>
       <c r="Z362" t="n">
-        <v>0.3795885741710663</v>
+        <v>22.71178245544434</v>
       </c>
     </row>
     <row r="363">
@@ -31601,7 +31601,7 @@
       </c>
       <c r="Y363" t="inlineStr"/>
       <c r="Z363" t="n">
-        <v>0.3796003758907318</v>
+        <v>18.40526390075684</v>
       </c>
     </row>
     <row r="364">
@@ -31671,7 +31671,7 @@
       </c>
       <c r="Y364" t="inlineStr"/>
       <c r="Z364" t="n">
-        <v>0.379560649394989</v>
+        <v>18.0196475982666</v>
       </c>
     </row>
     <row r="365">
@@ -31741,7 +31741,7 @@
       </c>
       <c r="Y365" t="inlineStr"/>
       <c r="Z365" t="n">
-        <v>0.3791247308254242</v>
+        <v>17.74242973327637</v>
       </c>
     </row>
     <row r="366">
@@ -31811,7 +31811,7 @@
       </c>
       <c r="Y366" t="inlineStr"/>
       <c r="Z366" t="n">
-        <v>0.3791012763977051</v>
+        <v>19.10095596313477</v>
       </c>
     </row>
     <row r="367">
@@ -31902,10 +31902,10 @@
         </is>
       </c>
       <c r="Y367" t="n">
-        <v>0.3796368539333344</v>
+        <v>23.27985954284668</v>
       </c>
       <c r="Z367" t="n">
-        <v>0.3796356022357941</v>
+        <v>22.82417297363281</v>
       </c>
     </row>
     <row r="368">
@@ -31996,10 +31996,10 @@
         </is>
       </c>
       <c r="Y368" t="n">
-        <v>0.3796336650848389</v>
+        <v>23.4231014251709</v>
       </c>
       <c r="Z368" t="n">
-        <v>0.3796311616897583</v>
+        <v>22.44525337219238</v>
       </c>
     </row>
     <row r="369">
@@ -32090,10 +32090,10 @@
         </is>
       </c>
       <c r="Y369" t="n">
-        <v>0.3796315789222717</v>
+        <v>24.10013580322266</v>
       </c>
       <c r="Z369" t="n">
-        <v>0.3796278834342957</v>
+        <v>23.54573249816895</v>
       </c>
     </row>
     <row r="370">
@@ -32184,10 +32184,10 @@
         </is>
       </c>
       <c r="Y370" t="n">
-        <v>0.3796294927597046</v>
+        <v>25.05768775939941</v>
       </c>
       <c r="Z370" t="n">
-        <v>0.3796246945858002</v>
+        <v>24.44772720336914</v>
       </c>
     </row>
     <row r="371">
@@ -32278,10 +32278,10 @@
         </is>
       </c>
       <c r="Y371" t="n">
-        <v>0.3796279430389404</v>
+        <v>25.28738212585449</v>
       </c>
       <c r="Z371" t="n">
-        <v>0.3796233534812927</v>
+        <v>25.07270812988281</v>
       </c>
     </row>
     <row r="372">
@@ -32372,10 +32372,10 @@
         </is>
       </c>
       <c r="Y372" t="n">
-        <v>0.3796259462833405</v>
+        <v>25.07697868347168</v>
       </c>
       <c r="Z372" t="n">
-        <v>0.3796213269233704</v>
+        <v>24.81965065002441</v>
       </c>
     </row>
     <row r="373">
@@ -32466,10 +32466,10 @@
         </is>
       </c>
       <c r="Y373" t="n">
-        <v>0.3796247243881226</v>
+        <v>25.15244483947754</v>
       </c>
       <c r="Z373" t="n">
-        <v>0.3796199262142181</v>
+        <v>24.75155830383301</v>
       </c>
     </row>
     <row r="374">
@@ -32560,10 +32560,10 @@
         </is>
       </c>
       <c r="Y374" t="n">
-        <v>0.3796219527721405</v>
+        <v>25.34474563598633</v>
       </c>
       <c r="Z374" t="n">
-        <v>0.3796164989471436</v>
+        <v>24.95413589477539</v>
       </c>
     </row>
     <row r="375">
@@ -32654,10 +32654,10 @@
         </is>
       </c>
       <c r="Y375" t="n">
-        <v>0.379628449678421</v>
+        <v>21.00268936157227</v>
       </c>
       <c r="Z375" t="n">
-        <v>0.379631519317627</v>
+        <v>21.67945098876953</v>
       </c>
     </row>
     <row r="376">
@@ -32748,10 +32748,10 @@
         </is>
       </c>
       <c r="Y376" t="n">
-        <v>0.3796168267726898</v>
+        <v>20.20948600769043</v>
       </c>
       <c r="Z376" t="n">
-        <v>0.3796229362487793</v>
+        <v>20.82916831970215</v>
       </c>
     </row>
     <row r="377">
@@ -32842,10 +32842,10 @@
         </is>
       </c>
       <c r="Y377" t="n">
-        <v>0.3795707523822784</v>
+        <v>19.89325332641602</v>
       </c>
       <c r="Z377" t="n">
-        <v>0.3796117603778839</v>
+        <v>21.49098205566406</v>
       </c>
     </row>
     <row r="378">
@@ -32936,10 +32936,10 @@
         </is>
       </c>
       <c r="Y378" t="n">
-        <v>0.3795020282268524</v>
+        <v>20.00122833251953</v>
       </c>
       <c r="Z378" t="n">
-        <v>0.379585325717926</v>
+        <v>21.74968147277832</v>
       </c>
     </row>
     <row r="379">
@@ -33030,10 +33030,10 @@
         </is>
       </c>
       <c r="Y379" t="n">
-        <v>0.3796389997005463</v>
+        <v>25.07813453674316</v>
       </c>
       <c r="Z379" t="n">
-        <v>0.3796396851539612</v>
+        <v>25.55769729614258</v>
       </c>
     </row>
     <row r="380">
@@ -33124,10 +33124,10 @@
         </is>
       </c>
       <c r="Y380" t="n">
-        <v>0.3796379268169403</v>
+        <v>25.74068641662598</v>
       </c>
       <c r="Z380" t="n">
-        <v>0.3796393275260925</v>
+        <v>26.55404853820801</v>
       </c>
     </row>
     <row r="381">
@@ -33218,10 +33218,10 @@
         </is>
       </c>
       <c r="Y381" t="n">
-        <v>0.3796333074569702</v>
+        <v>24.06049156188965</v>
       </c>
       <c r="Z381" t="n">
-        <v>0.3796384632587433</v>
+        <v>25.85709762573242</v>
       </c>
     </row>
     <row r="382">
@@ -33312,10 +33312,10 @@
         </is>
       </c>
       <c r="Y382" t="n">
-        <v>0.3796302378177643</v>
+        <v>25.35456657409668</v>
       </c>
       <c r="Z382" t="n">
-        <v>0.3796373009681702</v>
+        <v>26.37498092651367</v>
       </c>
     </row>
     <row r="383">
@@ -33406,10 +33406,10 @@
         </is>
       </c>
       <c r="Y383" t="n">
-        <v>0.379626989364624</v>
+        <v>25.32435035705566</v>
       </c>
       <c r="Z383" t="n">
-        <v>0.3796363770961761</v>
+        <v>26.5837574005127</v>
       </c>
     </row>
     <row r="384">
@@ -33500,10 +33500,10 @@
         </is>
       </c>
       <c r="Y384" t="n">
-        <v>0.3796246647834778</v>
+        <v>25.5854434967041</v>
       </c>
       <c r="Z384" t="n">
-        <v>0.3796354830265045</v>
+        <v>26.60186195373535</v>
       </c>
     </row>
     <row r="385">
@@ -33594,10 +33594,10 @@
         </is>
       </c>
       <c r="Y385" t="n">
-        <v>0.3796370923519135</v>
+        <v>22.53558540344238</v>
       </c>
       <c r="Z385" t="n">
-        <v>0.3796329200267792</v>
+        <v>21.01181602478027</v>
       </c>
     </row>
     <row r="386">
@@ -33688,10 +33688,10 @@
         </is>
       </c>
       <c r="Y386" t="n">
-        <v>0.3796340823173523</v>
+        <v>23.34474754333496</v>
       </c>
       <c r="Z386" t="n">
-        <v>0.3796257972717285</v>
+        <v>21.59971237182617</v>
       </c>
     </row>
     <row r="387">
@@ -33782,10 +33782,10 @@
         </is>
       </c>
       <c r="Y387" t="n">
-        <v>0.3796318471431732</v>
+        <v>23.34255790710449</v>
       </c>
       <c r="Z387" t="n">
-        <v>0.3796197474002838</v>
+        <v>21.82931518554688</v>
       </c>
     </row>
     <row r="388">
@@ -33876,10 +33876,10 @@
         </is>
       </c>
       <c r="Y388" t="n">
-        <v>0.3796293139457703</v>
+        <v>24.76235008239746</v>
       </c>
       <c r="Z388" t="n">
-        <v>0.3796177506446838</v>
+        <v>24.24894714355469</v>
       </c>
     </row>
     <row r="389">
@@ -33970,10 +33970,10 @@
         </is>
       </c>
       <c r="Y389" t="n">
-        <v>0.3796266615390778</v>
+        <v>24.09695625305176</v>
       </c>
       <c r="Z389" t="n">
-        <v>0.3796124458312988</v>
+        <v>23.04932403564453</v>
       </c>
     </row>
     <row r="390">
@@ -34064,10 +34064,10 @@
         </is>
       </c>
       <c r="Y390" t="n">
-        <v>0.3782913386821747</v>
+        <v>11.54104900360107</v>
       </c>
       <c r="Z390" t="n">
-        <v>0.3795832693576813</v>
+        <v>17.36753845214844</v>
       </c>
     </row>
     <row r="391">
@@ -34158,10 +34158,10 @@
         </is>
       </c>
       <c r="Y391" t="n">
-        <v>0.3769428431987762</v>
+        <v>12.94642925262451</v>
       </c>
       <c r="Z391" t="n">
-        <v>0.3795264959335327</v>
+        <v>17.45974159240723</v>
       </c>
     </row>
     <row r="392">
@@ -34252,10 +34252,10 @@
         </is>
       </c>
       <c r="Y392" t="n">
-        <v>0.3744293451309204</v>
+        <v>12.80765056610107</v>
       </c>
       <c r="Z392" t="n">
-        <v>0.3794806599617004</v>
+        <v>18.68876075744629</v>
       </c>
     </row>
     <row r="393">
@@ -34346,10 +34346,10 @@
         </is>
       </c>
       <c r="Y393" t="n">
-        <v>0.3705808222293854</v>
+        <v>12.36978149414062</v>
       </c>
       <c r="Z393" t="n">
-        <v>0.3793949484825134</v>
+        <v>18.48968124389648</v>
       </c>
     </row>
     <row r="394">
@@ -34440,10 +34440,10 @@
         </is>
       </c>
       <c r="Y394" t="n">
-        <v>0.3696187138557434</v>
+        <v>12.63399791717529</v>
       </c>
       <c r="Z394" t="n">
-        <v>0.3793772161006927</v>
+        <v>19.1355152130127</v>
       </c>
     </row>
     <row r="395">
@@ -34534,10 +34534,10 @@
         </is>
       </c>
       <c r="Y395" t="n">
-        <v>0.3796286582946777</v>
+        <v>20.92617416381836</v>
       </c>
       <c r="Z395" t="n">
-        <v>0.3796361982822418</v>
+        <v>23.16038703918457</v>
       </c>
     </row>
     <row r="396">
@@ -34628,10 +34628,10 @@
         </is>
       </c>
       <c r="Y396" t="n">
-        <v>0.3796172738075256</v>
+        <v>20.61932754516602</v>
       </c>
       <c r="Z396" t="n">
-        <v>0.3796323537826538</v>
+        <v>22.92670631408691</v>
       </c>
     </row>
     <row r="397">
@@ -34722,10 +34722,10 @@
         </is>
       </c>
       <c r="Y397" t="n">
-        <v>0.3796064257621765</v>
+        <v>21.44702339172363</v>
       </c>
       <c r="Z397" t="n">
-        <v>0.3796280920505524</v>
+        <v>23.15705490112305</v>
       </c>
     </row>
     <row r="398">
@@ -34816,10 +34816,10 @@
         </is>
       </c>
       <c r="Y398" t="n">
-        <v>0.3795854151248932</v>
+        <v>22.11128997802734</v>
       </c>
       <c r="Z398" t="n">
-        <v>0.379625529050827</v>
+        <v>24.93755531311035</v>
       </c>
     </row>
     <row r="399">
@@ -34910,10 +34910,10 @@
         </is>
       </c>
       <c r="Y399" t="n">
-        <v>0.379615306854248</v>
+        <v>19.82049179077148</v>
       </c>
       <c r="Z399" t="n">
-        <v>0.3796201050281525</v>
+        <v>20.08715057373047</v>
       </c>
     </row>
     <row r="400">
@@ -35004,10 +35004,10 @@
         </is>
       </c>
       <c r="Y400" t="n">
-        <v>0.3795905709266663</v>
+        <v>19.02035522460938</v>
       </c>
       <c r="Z400" t="n">
-        <v>0.3796001672744751</v>
+        <v>19.3464183807373</v>
       </c>
     </row>
     <row r="401">
@@ -35098,10 +35098,10 @@
         </is>
       </c>
       <c r="Y401" t="n">
-        <v>0.3795641958713531</v>
+        <v>18.77777862548828</v>
       </c>
       <c r="Z401" t="n">
-        <v>0.3795365691184998</v>
+        <v>18.12932014465332</v>
       </c>
     </row>
     <row r="402">
@@ -35192,10 +35192,10 @@
         </is>
       </c>
       <c r="Y402" t="n">
-        <v>0.3795544505119324</v>
+        <v>22.78024482727051</v>
       </c>
       <c r="Z402" t="n">
-        <v>0.3795322775840759</v>
+        <v>23.10492515563965</v>
       </c>
     </row>
     <row r="403">
@@ -35286,10 +35286,10 @@
         </is>
       </c>
       <c r="Y403" t="n">
-        <v>0.3796330690383911</v>
+        <v>22.00046157836914</v>
       </c>
       <c r="Z403" t="n">
-        <v>0.3796382546424866</v>
+        <v>24.06765174865723</v>
       </c>
     </row>
     <row r="404">
@@ -35380,10 +35380,10 @@
         </is>
       </c>
       <c r="Y404" t="n">
-        <v>0.3796260952949524</v>
+        <v>21.32913017272949</v>
       </c>
       <c r="Z404" t="n">
-        <v>0.3796364068984985</v>
+        <v>24.22502899169922</v>
       </c>
     </row>
     <row r="405">
@@ -35474,10 +35474,10 @@
         </is>
       </c>
       <c r="Y405" t="n">
-        <v>0.3796140551567078</v>
+        <v>22.08719825744629</v>
       </c>
       <c r="Z405" t="n">
-        <v>0.3796351850032806</v>
+        <v>24.80746459960938</v>
       </c>
     </row>
     <row r="406">
@@ -35568,10 +35568,10 @@
         </is>
       </c>
       <c r="Y406" t="n">
-        <v>0.3796006739139557</v>
+        <v>21.74054527282715</v>
       </c>
       <c r="Z406" t="n">
-        <v>0.3796327412128448</v>
+        <v>24.54617500305176</v>
       </c>
     </row>
     <row r="407">
@@ -35662,10 +35662,10 @@
         </is>
       </c>
       <c r="Y407" t="n">
-        <v>0.3795758485794067</v>
+        <v>22.37982559204102</v>
       </c>
       <c r="Z407" t="n">
-        <v>0.3796303272247314</v>
+        <v>25.68392181396484</v>
       </c>
     </row>
     <row r="408">
@@ -35756,10 +35756,10 @@
         </is>
       </c>
       <c r="Y408" t="n">
-        <v>0.3796395361423492</v>
+        <v>25.20073509216309</v>
       </c>
       <c r="Z408" t="n">
-        <v>0.379639208316803</v>
+        <v>24.85833549499512</v>
       </c>
     </row>
     <row r="409">
@@ -35850,10 +35850,10 @@
         </is>
       </c>
       <c r="Y409" t="n">
-        <v>0.3796389997005463</v>
+        <v>26.03021430969238</v>
       </c>
       <c r="Z409" t="n">
-        <v>0.3796383738517761</v>
+        <v>25.41952323913574</v>
       </c>
     </row>
     <row r="410">
@@ -35944,10 +35944,10 @@
         </is>
       </c>
       <c r="Y410" t="n">
-        <v>0.3796384334564209</v>
+        <v>26.12432670593262</v>
       </c>
       <c r="Z410" t="n">
-        <v>0.3796338140964508</v>
+        <v>24.0684986114502</v>
       </c>
     </row>
     <row r="411">
@@ -36038,10 +36038,10 @@
         </is>
       </c>
       <c r="Y411" t="n">
-        <v>0.3796376585960388</v>
+        <v>26.4041805267334</v>
       </c>
       <c r="Z411" t="n">
-        <v>0.3796317279338837</v>
+        <v>25.14895820617676</v>
       </c>
     </row>
     <row r="412">
@@ -36132,10 +36132,10 @@
         </is>
       </c>
       <c r="Y412" t="n">
-        <v>0.3796365857124329</v>
+        <v>26.04217910766602</v>
       </c>
       <c r="Z412" t="n">
-        <v>0.3796305060386658</v>
+        <v>25.70446395874023</v>
       </c>
     </row>
     <row r="413">
@@ -36226,10 +36226,10 @@
         </is>
       </c>
       <c r="Y413" t="n">
-        <v>0.3796371817588806</v>
+        <v>22.85692024230957</v>
       </c>
       <c r="Z413" t="n">
-        <v>0.3796373903751373</v>
+        <v>22.81442451477051</v>
       </c>
     </row>
     <row r="414">
@@ -36320,10 +36320,10 @@
         </is>
       </c>
       <c r="Y414" t="n">
-        <v>0.379634290933609</v>
+        <v>23.78759002685547</v>
       </c>
       <c r="Z414" t="n">
-        <v>0.3796347081661224</v>
+        <v>24.1137638092041</v>
       </c>
     </row>
     <row r="415">
@@ -36414,10 +36414,10 @@
         </is>
       </c>
       <c r="Y415" t="n">
-        <v>0.3796274662017822</v>
+        <v>22.97830772399902</v>
       </c>
       <c r="Z415" t="n">
-        <v>0.3796291947364807</v>
+        <v>23.23278427124023</v>
       </c>
     </row>
     <row r="416">
@@ -36508,10 +36508,10 @@
         </is>
       </c>
       <c r="Y416" t="n">
-        <v>0.3796235620975494</v>
+        <v>24.03005027770996</v>
       </c>
       <c r="Z416" t="n">
-        <v>0.3796251118183136</v>
+        <v>24.05803489685059</v>
       </c>
     </row>
     <row r="417">
@@ -36602,10 +36602,10 @@
         </is>
       </c>
       <c r="Y417" t="n">
-        <v>0.3796201944351196</v>
+        <v>24.0883903503418</v>
       </c>
       <c r="Z417" t="n">
-        <v>0.379619687795639</v>
+        <v>23.74543380737305</v>
       </c>
     </row>
     <row r="418">
@@ -36696,10 +36696,10 @@
         </is>
       </c>
       <c r="Y418" t="n">
-        <v>0.3796382546424866</v>
+        <v>23.9207878112793</v>
       </c>
       <c r="Z418" t="n">
-        <v>0.3796376585960388</v>
+        <v>23.87481307983398</v>
       </c>
     </row>
     <row r="419">
@@ -36790,10 +36790,10 @@
         </is>
       </c>
       <c r="Y419" t="n">
-        <v>0.3796364068984985</v>
+        <v>24.4920654296875</v>
       </c>
       <c r="Z419" t="n">
-        <v>0.3796352446079254</v>
+        <v>23.99041748046875</v>
       </c>
     </row>
     <row r="420">
@@ -36884,10 +36884,10 @@
         </is>
       </c>
       <c r="Y420" t="n">
-        <v>0.3796352446079254</v>
+        <v>24.8891773223877</v>
       </c>
       <c r="Z420" t="n">
-        <v>0.3796335756778717</v>
+        <v>24.50143432617188</v>
       </c>
     </row>
     <row r="421">
@@ -36978,10 +36978,10 @@
         </is>
       </c>
       <c r="Y421" t="n">
-        <v>0.3796345293521881</v>
+        <v>26.02251243591309</v>
       </c>
       <c r="Z421" t="n">
-        <v>0.379631906747818</v>
+        <v>25.43136024475098</v>
       </c>
     </row>
     <row r="422">
@@ -37072,10 +37072,10 @@
         </is>
       </c>
       <c r="Y422" t="n">
-        <v>0.3796339929103851</v>
+        <v>26.05753326416016</v>
       </c>
       <c r="Z422" t="n">
-        <v>0.3796306848526001</v>
+        <v>25.38068008422852</v>
       </c>
     </row>
     <row r="423">
@@ -37166,10 +37166,10 @@
         </is>
       </c>
       <c r="Y423" t="n">
-        <v>0.3796335756778717</v>
+        <v>26.25801849365234</v>
       </c>
       <c r="Z423" t="n">
-        <v>0.3796268105506897</v>
+        <v>24.52912712097168</v>
       </c>
     </row>
     <row r="424">
@@ -37260,10 +37260,10 @@
         </is>
       </c>
       <c r="Y424" t="n">
-        <v>0.3796321749687195</v>
+        <v>25.49005317687988</v>
       </c>
       <c r="Z424" t="n">
-        <v>0.3796215951442719</v>
+        <v>23.91055107116699</v>
       </c>
     </row>
     <row r="425">
@@ -37354,10 +37354,10 @@
         </is>
       </c>
       <c r="Y425" t="n">
-        <v>0.3794711232185364</v>
+        <v>15.36464405059814</v>
       </c>
       <c r="Z425" t="n">
-        <v>0.3790629506111145</v>
+        <v>12.85902881622314</v>
       </c>
     </row>
     <row r="426">
@@ -37448,10 +37448,10 @@
         </is>
       </c>
       <c r="Y426" t="n">
-        <v>0.3793021738529205</v>
+        <v>15.90321636199951</v>
       </c>
       <c r="Z426" t="n">
-        <v>0.3784858584403992</v>
+        <v>13.9992036819458</v>
       </c>
     </row>
     <row r="427">
@@ -37542,10 +37542,10 @@
         </is>
       </c>
       <c r="Y427" t="n">
-        <v>0.3790173828601837</v>
+        <v>16.27259063720703</v>
       </c>
       <c r="Z427" t="n">
-        <v>0.3782921135425568</v>
+        <v>14.89947986602783</v>
       </c>
     </row>
     <row r="428">
@@ -37636,10 +37636,10 @@
         </is>
       </c>
       <c r="Y428" t="n">
-        <v>0.3789148032665253</v>
+        <v>17.6043815612793</v>
       </c>
       <c r="Z428" t="n">
-        <v>0.3782548308372498</v>
+        <v>17.2341136932373</v>
       </c>
     </row>
     <row r="429">
@@ -37730,10 +37730,10 @@
         </is>
       </c>
       <c r="Y429" t="n">
-        <v>0.3403036892414093</v>
+        <v>7.170845031738281</v>
       </c>
       <c r="Z429" t="n">
-        <v>0.3789741694927216</v>
+        <v>12.60393047332764</v>
       </c>
     </row>
     <row r="430">
@@ -37824,10 +37824,10 @@
         </is>
       </c>
       <c r="Y430" t="n">
-        <v>0.3013622760772705</v>
+        <v>9.269199371337891</v>
       </c>
       <c r="Z430" t="n">
-        <v>0.3783082962036133</v>
+        <v>13.61298942565918</v>
       </c>
     </row>
     <row r="431">
@@ -37918,10 +37918,10 @@
         </is>
       </c>
       <c r="Y431" t="n">
-        <v>0.204317644238472</v>
+        <v>7.63679027557373</v>
       </c>
       <c r="Z431" t="n">
-        <v>0.377446711063385</v>
+        <v>12.56849193572998</v>
       </c>
     </row>
     <row r="432">
@@ -38012,10 +38012,10 @@
         </is>
       </c>
       <c r="Y432" t="n">
-        <v>-0.002727210521697998</v>
+        <v>9.424662590026855</v>
       </c>
       <c r="Z432" t="n">
-        <v>0.3761600852012634</v>
+        <v>13.83892154693604</v>
       </c>
     </row>
     <row r="433">
@@ -38106,10 +38106,10 @@
         </is>
       </c>
       <c r="Y433" t="n">
-        <v>-0.1060238778591156</v>
+        <v>9.942734718322754</v>
       </c>
       <c r="Z433" t="n">
-        <v>0.3755107223987579</v>
+        <v>14.21718788146973</v>
       </c>
     </row>
     <row r="434">
@@ -38179,7 +38179,7 @@
       </c>
       <c r="Y434" t="inlineStr"/>
       <c r="Z434" t="n">
-        <v>0.3739219009876251</v>
+        <v>15.07737255096436</v>
       </c>
     </row>
     <row r="435">
@@ -38249,7 +38249,7 @@
       </c>
       <c r="Y435" t="inlineStr"/>
       <c r="Z435" t="n">
-        <v>0.3703052401542664</v>
+        <v>14.31888198852539</v>
       </c>
     </row>
     <row r="436">
@@ -38309,7 +38309,7 @@
       </c>
       <c r="Y436" t="inlineStr"/>
       <c r="Z436" t="n">
-        <v>0.3796393275260925</v>
+        <v>24.14178657531738</v>
       </c>
     </row>
     <row r="437">
@@ -38369,7 +38369,7 @@
       </c>
       <c r="Y437" t="inlineStr"/>
       <c r="Z437" t="n">
-        <v>0.3796385526657104</v>
+        <v>25.54093742370605</v>
       </c>
     </row>
     <row r="438">
@@ -38429,7 +38429,7 @@
       </c>
       <c r="Y438" t="inlineStr"/>
       <c r="Z438" t="n">
-        <v>0.3796369433403015</v>
+        <v>24.70187187194824</v>
       </c>
     </row>
     <row r="439">
@@ -38489,7 +38489,7 @@
       </c>
       <c r="Y439" t="inlineStr"/>
       <c r="Z439" t="n">
-        <v>0.3796348571777344</v>
+        <v>25.36248970031738</v>
       </c>
     </row>
     <row r="440">
@@ -38580,10 +38580,10 @@
         </is>
       </c>
       <c r="Y440" t="n">
-        <v>0.3795515298843384</v>
+        <v>16.99228096008301</v>
       </c>
       <c r="Z440" t="n">
-        <v>0.3796322643756866</v>
+        <v>21.78323745727539</v>
       </c>
     </row>
     <row r="441">
@@ -38674,10 +38674,10 @@
         </is>
       </c>
       <c r="Y441" t="n">
-        <v>0.3794629573822021</v>
+        <v>16.93114280700684</v>
       </c>
       <c r="Z441" t="n">
-        <v>0.3796244263648987</v>
+        <v>21.42486953735352</v>
       </c>
     </row>
     <row r="442">
@@ -38768,10 +38768,10 @@
         </is>
       </c>
       <c r="Y442" t="n">
-        <v>0.3792040348052979</v>
+        <v>17.1103343963623</v>
       </c>
       <c r="Z442" t="n">
-        <v>0.3796194493770599</v>
+        <v>22.74034690856934</v>
       </c>
     </row>
     <row r="443">
@@ -38862,10 +38862,10 @@
         </is>
       </c>
       <c r="Y443" t="n">
-        <v>0.3789659142494202</v>
+        <v>17.47791290283203</v>
       </c>
       <c r="Z443" t="n">
-        <v>0.3796137273311615</v>
+        <v>23.83955574035645</v>
       </c>
     </row>
     <row r="444">
@@ -38956,10 +38956,10 @@
         </is>
       </c>
       <c r="Y444" t="n">
-        <v>0.3796363770961761</v>
+        <v>23.63862609863281</v>
       </c>
       <c r="Z444" t="n">
-        <v>0.3796246647834778</v>
+        <v>20.54939460754395</v>
       </c>
     </row>
     <row r="445">
@@ -39050,10 +39050,10 @@
         </is>
       </c>
       <c r="Y445" t="n">
-        <v>0.3796326518058777</v>
+        <v>23.90968132019043</v>
       </c>
       <c r="Z445" t="n">
-        <v>0.3796092867851257</v>
+        <v>20.89797782897949</v>
       </c>
     </row>
     <row r="446">
@@ -39144,10 +39144,10 @@
         </is>
       </c>
       <c r="Y446" t="n">
-        <v>0.379631519317627</v>
+        <v>24.89766693115234</v>
       </c>
       <c r="Z446" t="n">
-        <v>0.3796058893203735</v>
+        <v>22.84640312194824</v>
       </c>
     </row>
     <row r="447">
@@ -39238,10 +39238,10 @@
         </is>
       </c>
       <c r="Y447" t="n">
-        <v>0.3796308934688568</v>
+        <v>26.38082313537598</v>
       </c>
       <c r="Z447" t="n">
-        <v>0.3796040415763855</v>
+        <v>24.75908470153809</v>
       </c>
     </row>
     <row r="448">
@@ -39332,10 +39332,10 @@
         </is>
       </c>
       <c r="Y448" t="n">
-        <v>0.3796295821666718</v>
+        <v>25.58213043212891</v>
       </c>
       <c r="Z448" t="n">
-        <v>0.3796016275882721</v>
+        <v>23.96539497375488</v>
       </c>
     </row>
     <row r="449">
@@ -39426,10 +39426,10 @@
         </is>
       </c>
       <c r="Y449" t="n">
-        <v>0.3796286880970001</v>
+        <v>26.01288414001465</v>
       </c>
       <c r="Z449" t="n">
-        <v>0.3795999586582184</v>
+        <v>24.48426246643066</v>
       </c>
     </row>
     <row r="450">
@@ -39520,10 +39520,10 @@
         </is>
       </c>
       <c r="Y450" t="n">
-        <v>0.3796279430389404</v>
+        <v>26.16617774963379</v>
       </c>
       <c r="Z450" t="n">
-        <v>0.3795972764492035</v>
+        <v>24.31827735900879</v>
       </c>
     </row>
     <row r="451">
@@ -39614,10 +39614,10 @@
         </is>
       </c>
       <c r="Y451" t="n">
-        <v>0.3796270787715912</v>
+        <v>25.66111755371094</v>
       </c>
       <c r="Z451" t="n">
-        <v>0.3795949816703796</v>
+        <v>23.80331230163574</v>
       </c>
     </row>
     <row r="452">
@@ -39688,10 +39688,10 @@
         </is>
       </c>
       <c r="Y452" t="n">
-        <v>0.3796396553516388</v>
+        <v>25.04120445251465</v>
       </c>
       <c r="Z452" t="n">
-        <v>0.379639744758606</v>
+        <v>25.44246864318848</v>
       </c>
     </row>
     <row r="453">
@@ -39762,10 +39762,10 @@
         </is>
       </c>
       <c r="Y453" t="n">
-        <v>0.379639208316803</v>
+        <v>26.4364185333252</v>
       </c>
       <c r="Z453" t="n">
-        <v>0.3796394169330597</v>
+        <v>26.85225105285645</v>
       </c>
     </row>
     <row r="454">
@@ -39836,10 +39836,10 @@
         </is>
       </c>
       <c r="Y454" t="n">
-        <v>0.3796388804912567</v>
+        <v>26.34877395629883</v>
       </c>
       <c r="Z454" t="n">
-        <v>0.3796383440494537</v>
+        <v>25.78721809387207</v>
       </c>
     </row>
     <row r="455">
@@ -39910,10 +39910,10 @@
         </is>
       </c>
       <c r="Y455" t="n">
-        <v>0.3796385824680328</v>
+        <v>27.0188045501709</v>
       </c>
       <c r="Z455" t="n">
-        <v>0.3796378076076508</v>
+        <v>26.74962043762207</v>
       </c>
     </row>
     <row r="456">
@@ -40004,10 +40004,10 @@
         </is>
       </c>
       <c r="Y456" t="n">
-        <v>0.379639208316803</v>
+        <v>24.59499549865723</v>
       </c>
       <c r="Z456" t="n">
-        <v>0.3796396851539612</v>
+        <v>24.93368339538574</v>
       </c>
     </row>
     <row r="457">
@@ -40098,10 +40098,10 @@
         </is>
       </c>
       <c r="Y457" t="n">
-        <v>0.3796383738517761</v>
+        <v>25.74832344055176</v>
       </c>
       <c r="Z457" t="n">
-        <v>0.3796393275260925</v>
+        <v>26.62918663024902</v>
       </c>
     </row>
     <row r="458">
@@ -40192,10 +40192,10 @@
         </is>
       </c>
       <c r="Y458" t="n">
-        <v>0.3796369731426239</v>
+        <v>25.20210838317871</v>
       </c>
       <c r="Z458" t="n">
-        <v>0.3796387910842896</v>
+        <v>26.27887535095215</v>
       </c>
     </row>
     <row r="459">
@@ -40286,10 +40286,10 @@
         </is>
       </c>
       <c r="Y459" t="n">
-        <v>0.379635363817215</v>
+        <v>25.6513671875</v>
       </c>
       <c r="Z459" t="n">
-        <v>0.3796384036540985</v>
+        <v>26.71175956726074</v>
       </c>
     </row>
     <row r="460">
@@ -40380,10 +40380,10 @@
         </is>
       </c>
       <c r="Y460" t="n">
-        <v>0.3796343803405762</v>
+        <v>25.8575267791748</v>
       </c>
       <c r="Z460" t="n">
-        <v>0.3796376585960388</v>
+        <v>26.35087776184082</v>
       </c>
     </row>
     <row r="461">
@@ -40474,10 +40474,10 @@
         </is>
       </c>
       <c r="Y461" t="n">
-        <v>0.379633367061615</v>
+        <v>26.17838478088379</v>
       </c>
       <c r="Z461" t="n">
-        <v>0.3796372413635254</v>
+        <v>26.78105735778809</v>
       </c>
     </row>
     <row r="462">
@@ -40568,10 +40568,10 @@
         </is>
       </c>
       <c r="Y462" t="n">
-        <v>0.3796324133872986</v>
+        <v>26.06351470947266</v>
       </c>
       <c r="Z462" t="n">
-        <v>0.3796363770961761</v>
+        <v>26.46835327148438</v>
       </c>
     </row>
     <row r="463">
@@ -40662,10 +40662,10 @@
         </is>
       </c>
       <c r="Y463" t="n">
-        <v>0.3796311020851135</v>
+        <v>25.92570877075195</v>
       </c>
       <c r="Z463" t="n">
-        <v>0.3796354532241821</v>
+        <v>26.40457344055176</v>
       </c>
     </row>
     <row r="464">
@@ -40756,10 +40756,10 @@
         </is>
       </c>
       <c r="Y464" t="n">
-        <v>0.3796381056308746</v>
+        <v>24.25417137145996</v>
       </c>
       <c r="Z464" t="n">
-        <v>0.3796380460262299</v>
+        <v>24.18964576721191</v>
       </c>
     </row>
     <row r="465">
@@ -40850,10 +40850,10 @@
         </is>
       </c>
       <c r="Y465" t="n">
-        <v>0.379636138677597</v>
+        <v>24.50756645202637</v>
       </c>
       <c r="Z465" t="n">
-        <v>0.3796360194683075</v>
+        <v>24.56155967712402</v>
       </c>
     </row>
     <row r="466">
@@ -40944,10 +40944,10 @@
         </is>
       </c>
       <c r="Y466" t="n">
-        <v>0.3796317279338837</v>
+        <v>23.7761058807373</v>
       </c>
       <c r="Z466" t="n">
-        <v>0.3796301186084747</v>
+        <v>23.56135368347168</v>
       </c>
     </row>
     <row r="467">
@@ -41038,10 +41038,10 @@
         </is>
       </c>
       <c r="Y467" t="n">
-        <v>0.3796305358409882</v>
+        <v>25.66540908813477</v>
       </c>
       <c r="Z467" t="n">
-        <v>0.379628449678421</v>
+        <v>25.34332275390625</v>
       </c>
     </row>
     <row r="468">
@@ -41132,10 +41132,10 @@
         </is>
       </c>
       <c r="Y468" t="n">
-        <v>0.379628598690033</v>
+        <v>25.3884334564209</v>
       </c>
       <c r="Z468" t="n">
-        <v>0.3796273767948151</v>
+        <v>25.90947151184082</v>
       </c>
     </row>
     <row r="469">
@@ -41226,10 +41226,10 @@
         </is>
       </c>
       <c r="Y469" t="n">
-        <v>0.3796282410621643</v>
+        <v>26.46379470825195</v>
       </c>
       <c r="Z469" t="n">
-        <v>0.3796264827251434</v>
+        <v>25.93077659606934</v>
       </c>
     </row>
     <row r="470">
@@ -41320,10 +41320,10 @@
         </is>
       </c>
       <c r="Y470" t="n">
-        <v>0.3796259462833405</v>
+        <v>25.06472969055176</v>
       </c>
       <c r="Z470" t="n">
-        <v>0.3796243965625763</v>
+        <v>25.12867164611816</v>
       </c>
     </row>
     <row r="471">
@@ -41414,10 +41414,10 @@
         </is>
       </c>
       <c r="Y471" t="n">
-        <v>0.3796381950378418</v>
+        <v>24.01064300537109</v>
       </c>
       <c r="Z471" t="n">
-        <v>0.3796387314796448</v>
+        <v>24.5064868927002</v>
       </c>
     </row>
     <row r="472">
@@ -41508,10 +41508,10 @@
         </is>
       </c>
       <c r="Y472" t="n">
-        <v>0.3796363174915314</v>
+        <v>24.48935127258301</v>
       </c>
       <c r="Z472" t="n">
-        <v>0.3796373903751373</v>
+        <v>24.83477783203125</v>
       </c>
     </row>
     <row r="473">
@@ -41602,10 +41602,10 @@
         </is>
       </c>
       <c r="Y473" t="n">
-        <v>0.3796327412128448</v>
+        <v>23.80872535705566</v>
       </c>
       <c r="Z473" t="n">
-        <v>0.3796342313289642</v>
+        <v>23.93769073486328</v>
       </c>
     </row>
     <row r="474">
@@ -41696,10 +41696,10 @@
         </is>
       </c>
       <c r="Y474" t="n">
-        <v>0.379628449678421</v>
+        <v>24.41507911682129</v>
       </c>
       <c r="Z474" t="n">
-        <v>0.3796304762363434</v>
+        <v>24.53914260864258</v>
       </c>
     </row>
     <row r="475">
@@ -41790,10 +41790,10 @@
         </is>
       </c>
       <c r="Y475" t="n">
-        <v>0.3796393573284149</v>
+        <v>25.0772533416748</v>
       </c>
       <c r="Z475" t="n">
-        <v>0.379638671875</v>
+        <v>24.43289756774902</v>
       </c>
     </row>
     <row r="476">
@@ -41884,10 +41884,10 @@
         </is>
       </c>
       <c r="Y476" t="n">
-        <v>0.379638671875</v>
+        <v>25.39509773254395</v>
       </c>
       <c r="Z476" t="n">
-        <v>0.3796373009681702</v>
+        <v>23.87612724304199</v>
       </c>
     </row>
     <row r="477">
@@ -41978,10 +41978,10 @@
         </is>
       </c>
       <c r="Y477" t="n">
-        <v>0.3796378672122955</v>
+        <v>25.43439674377441</v>
       </c>
       <c r="Z477" t="n">
-        <v>0.3796369135379791</v>
+        <v>25.51173782348633</v>
       </c>
     </row>
     <row r="478">
@@ -42072,10 +42072,10 @@
         </is>
       </c>
       <c r="Y478" t="n">
-        <v>0.3796326220035553</v>
+        <v>24.4037036895752</v>
       </c>
       <c r="Z478" t="n">
-        <v>0.379633754491806</v>
+        <v>24.6743335723877</v>
       </c>
     </row>
     <row r="479">
@@ -42166,10 +42166,10 @@
         </is>
       </c>
       <c r="Y479" t="n">
-        <v>0.3796299993991852</v>
+        <v>24.76729583740234</v>
       </c>
       <c r="Z479" t="n">
-        <v>0.3796318769454956</v>
+        <v>24.55119132995605</v>
       </c>
     </row>
     <row r="480">
@@ -42260,10 +42260,10 @@
         </is>
       </c>
       <c r="Y480" t="n">
-        <v>0.3796245753765106</v>
+        <v>24.20319557189941</v>
       </c>
       <c r="Z480" t="n">
-        <v>0.3796273171901703</v>
+        <v>23.91405487060547</v>
       </c>
     </row>
     <row r="481">
@@ -42354,10 +42354,10 @@
         </is>
       </c>
       <c r="Y481" t="n">
-        <v>0.3796224296092987</v>
+        <v>25.03495025634766</v>
       </c>
       <c r="Z481" t="n">
-        <v>0.3796244859695435</v>
+        <v>24.46209144592285</v>
       </c>
     </row>
     <row r="482">
@@ -42448,10 +42448,10 @@
         </is>
       </c>
       <c r="Y482" t="n">
-        <v>0.379620224237442</v>
+        <v>25.2700309753418</v>
       </c>
       <c r="Z482" t="n">
-        <v>0.3796185255050659</v>
+        <v>23.88794136047363</v>
       </c>
     </row>
     <row r="483">
@@ -42542,10 +42542,10 @@
         </is>
       </c>
       <c r="Y483" t="n">
-        <v>0.3796167969703674</v>
+        <v>24.85064125061035</v>
       </c>
       <c r="Z483" t="n">
-        <v>0.3796161413192749</v>
+        <v>24.6402759552002</v>
       </c>
     </row>
     <row r="484">
@@ -42636,10 +42636,10 @@
         </is>
       </c>
       <c r="Y484" t="n">
-        <v>0.3677246868610382</v>
+        <v>8.72215747833252</v>
       </c>
       <c r="Z484" t="n">
-        <v>0.3796233832836151</v>
+        <v>21.25163459777832</v>
       </c>
     </row>
     <row r="485">
@@ -42730,10 +42730,10 @@
         </is>
       </c>
       <c r="Y485" t="n">
-        <v>0.3558403849601746</v>
+        <v>10.90604877471924</v>
       </c>
       <c r="Z485" t="n">
-        <v>0.379606693983078</v>
+        <v>20.52120399475098</v>
       </c>
     </row>
     <row r="486">
@@ -42824,10 +42824,10 @@
         </is>
       </c>
       <c r="Y486" t="n">
-        <v>0.3550896942615509</v>
+        <v>12.64800453186035</v>
       </c>
       <c r="Z486" t="n">
-        <v>0.379588782787323</v>
+        <v>22.01986694335938</v>
       </c>
     </row>
     <row r="487">
@@ -42918,10 +42918,10 @@
         </is>
       </c>
       <c r="Y487" t="n">
-        <v>0.353019505739212</v>
+        <v>12.31871223449707</v>
       </c>
       <c r="Z487" t="n">
-        <v>0.3795514404773712</v>
+        <v>21.46755599975586</v>
       </c>
     </row>
     <row r="488">
@@ -43012,10 +43012,10 @@
         </is>
       </c>
       <c r="Y488" t="n">
-        <v>0.3486285209655762</v>
+        <v>12.51127910614014</v>
       </c>
       <c r="Z488" t="n">
-        <v>0.3795313537120819</v>
+        <v>21.88650703430176</v>
       </c>
     </row>
     <row r="489">
@@ -43106,10 +43106,10 @@
         </is>
       </c>
       <c r="Y489" t="n">
-        <v>0.3796388804912567</v>
+        <v>25.36201286315918</v>
       </c>
       <c r="Z489" t="n">
-        <v>0.3796388804912567</v>
+        <v>25.40682983398438</v>
       </c>
     </row>
     <row r="490">
@@ -43200,10 +43200,10 @@
         </is>
       </c>
       <c r="Y490" t="n">
-        <v>0.3796377182006836</v>
+        <v>25.61120796203613</v>
       </c>
       <c r="Z490" t="n">
-        <v>0.3796377182006836</v>
+        <v>25.35957908630371</v>
       </c>
     </row>
     <row r="491">
@@ -43294,10 +43294,10 @@
         </is>
       </c>
       <c r="Y491" t="n">
-        <v>0.3796349465847015</v>
+        <v>24.25167846679688</v>
       </c>
       <c r="Z491" t="n">
-        <v>0.3796360492706299</v>
+        <v>24.63300132751465</v>
       </c>
     </row>
     <row r="492">
@@ -43388,10 +43388,10 @@
         </is>
       </c>
       <c r="Y492" t="n">
-        <v>0.379632830619812</v>
+        <v>26.37454414367676</v>
       </c>
       <c r="Z492" t="n">
-        <v>0.3796343803405762</v>
+        <v>26.60465431213379</v>
       </c>
     </row>
     <row r="493">
@@ -43461,7 +43461,7 @@
       </c>
       <c r="Y493" t="inlineStr"/>
       <c r="Z493" t="n">
-        <v>0.3796209096908569</v>
+        <v>24.26099967956543</v>
       </c>
     </row>
     <row r="494">
@@ -43552,10 +43552,10 @@
         </is>
       </c>
       <c r="Y494" t="n">
-        <v>0.3786669671535492</v>
+        <v>13.18616199493408</v>
       </c>
       <c r="Z494" t="n">
-        <v>0.3796383142471313</v>
+        <v>24.80050468444824</v>
       </c>
     </row>
     <row r="495">
@@ -43646,10 +43646,10 @@
         </is>
       </c>
       <c r="Y495" t="n">
-        <v>0.3776939213275909</v>
+        <v>14.18134307861328</v>
       </c>
       <c r="Z495" t="n">
-        <v>0.3796365261077881</v>
+        <v>24.56633377075195</v>
       </c>
     </row>
     <row r="496">
@@ -43740,10 +43740,10 @@
         </is>
       </c>
       <c r="Y496" t="n">
-        <v>0.3760727047920227</v>
+        <v>14.43231868743896</v>
       </c>
       <c r="Z496" t="n">
-        <v>0.379625678062439</v>
+        <v>23.47049522399902</v>
       </c>
     </row>
     <row r="497">
@@ -43834,10 +43834,10 @@
         </is>
       </c>
       <c r="Y497" t="n">
-        <v>0.3755589425563812</v>
+        <v>14.25782871246338</v>
       </c>
       <c r="Z497" t="n">
-        <v>0.3796016275882721</v>
+        <v>22.66205787658691</v>
       </c>
     </row>
     <row r="498">
@@ -43906,7 +43906,7 @@
         </is>
       </c>
       <c r="Y498" t="n">
-        <v>0.3753073811531067</v>
+        <v>15.4865550994873</v>
       </c>
       <c r="Z498" t="inlineStr"/>
     </row>
@@ -43998,10 +43998,10 @@
         </is>
       </c>
       <c r="Y499" t="n">
-        <v>0.3796393275260925</v>
+        <v>24.66985130310059</v>
       </c>
       <c r="Z499" t="n">
-        <v>0.3796348869800568</v>
+        <v>21.79261589050293</v>
       </c>
     </row>
     <row r="500">
@@ -44092,10 +44092,10 @@
         </is>
       </c>
       <c r="Y500" t="n">
-        <v>0.3796385824680328</v>
+        <v>25.96782684326172</v>
       </c>
       <c r="Z500" t="n">
-        <v>0.3796296715736389</v>
+        <v>22.8336353302002</v>
       </c>
     </row>
     <row r="501">
@@ -44186,10 +44186,10 @@
         </is>
       </c>
       <c r="Y501" t="n">
-        <v>0.3796361088752747</v>
+        <v>24.56549263000488</v>
       </c>
       <c r="Z501" t="n">
-        <v>0.379618763923645</v>
+        <v>21.6784839630127</v>
       </c>
     </row>
     <row r="502">
@@ -44280,10 +44280,10 @@
         </is>
       </c>
       <c r="Y502" t="n">
-        <v>0.379620373249054</v>
+        <v>22.48638725280762</v>
       </c>
       <c r="Z502" t="n">
-        <v>0.3795936703681946</v>
+        <v>20.40844535827637</v>
       </c>
     </row>
     <row r="503">
@@ -44374,10 +44374,10 @@
         </is>
       </c>
       <c r="Y503" t="n">
-        <v>0.3796217739582062</v>
+        <v>19.89461517333984</v>
       </c>
       <c r="Z503" t="n">
-        <v>0.3796260952949524</v>
+        <v>20.78631401062012</v>
       </c>
     </row>
     <row r="504">
@@ -44468,10 +44468,10 @@
         </is>
       </c>
       <c r="Y504" t="n">
-        <v>0.3796034753322601</v>
+        <v>20.31484985351562</v>
       </c>
       <c r="Z504" t="n">
-        <v>0.3796121180057526</v>
+        <v>21.04891014099121</v>
       </c>
     </row>
     <row r="505">
@@ -44562,10 +44562,10 @@
         </is>
       </c>
       <c r="Y505" t="n">
-        <v>0.379595160484314</v>
+        <v>21.89671897888184</v>
       </c>
       <c r="Z505" t="n">
-        <v>0.3796015977859497</v>
+        <v>22.06643295288086</v>
       </c>
     </row>
     <row r="506">
@@ -44656,10 +44656,10 @@
         </is>
       </c>
       <c r="Y506" t="n">
-        <v>0.379570335149765</v>
+        <v>21.77062225341797</v>
       </c>
       <c r="Z506" t="n">
-        <v>0.379595011472702</v>
+        <v>23.22584533691406</v>
       </c>
     </row>
     <row r="507">
@@ -44750,10 +44750,10 @@
         </is>
       </c>
       <c r="Y507" t="n">
-        <v>0.3795554041862488</v>
+        <v>21.69523429870605</v>
       </c>
       <c r="Z507" t="n">
-        <v>0.3795758783817291</v>
+        <v>22.22450828552246</v>
       </c>
     </row>
     <row r="508">
@@ -44844,10 +44844,10 @@
         </is>
       </c>
       <c r="Y508" t="n">
-        <v>0.3795386254787445</v>
+        <v>21.5811824798584</v>
       </c>
       <c r="Z508" t="n">
-        <v>0.379545271396637</v>
+        <v>21.22298240661621</v>
       </c>
     </row>
     <row r="509">
@@ -44938,10 +44938,10 @@
         </is>
       </c>
       <c r="Y509" t="n">
-        <v>0.3794909417629242</v>
+        <v>15.88374423980713</v>
       </c>
       <c r="Z509" t="n">
-        <v>0.379637748003006</v>
+        <v>24.04595565795898</v>
       </c>
     </row>
     <row r="510">
@@ -45032,10 +45032,10 @@
         </is>
       </c>
       <c r="Y510" t="n">
-        <v>0.3793418109416962</v>
+        <v>15.86382579803467</v>
       </c>
       <c r="Z510" t="n">
-        <v>0.3796354532241821</v>
+        <v>23.86852836608887</v>
       </c>
     </row>
     <row r="511">
@@ -45126,10 +45126,10 @@
         </is>
       </c>
       <c r="Y511" t="n">
-        <v>0.3790336549282074</v>
+        <v>16.03314590454102</v>
       </c>
       <c r="Z511" t="n">
-        <v>0.3796335160732269</v>
+        <v>24.0390567779541</v>
       </c>
     </row>
     <row r="512">
@@ -45220,10 +45220,10 @@
         </is>
       </c>
       <c r="Y512" t="n">
-        <v>0.3787049949169159</v>
+        <v>16.40918159484863</v>
       </c>
       <c r="Z512" t="n">
-        <v>0.3796297013759613</v>
+        <v>24.92405128479004</v>
       </c>
     </row>
     <row r="513">
@@ -45314,10 +45314,10 @@
         </is>
       </c>
       <c r="Y513" t="n">
-        <v>0.3779793679714203</v>
+        <v>16.32690048217773</v>
       </c>
       <c r="Z513" t="n">
-        <v>0.3796272873878479</v>
+        <v>24.55129814147949</v>
       </c>
     </row>
     <row r="514">
@@ -45408,10 +45408,10 @@
         </is>
       </c>
       <c r="Y514" t="n">
-        <v>0.3777990937232971</v>
+        <v>17.14836120605469</v>
       </c>
       <c r="Z514" t="n">
-        <v>0.3796238005161285</v>
+        <v>24.43945121765137</v>
       </c>
     </row>
     <row r="515">
@@ -45502,10 +45502,10 @@
         </is>
       </c>
       <c r="Y515" t="n">
-        <v>0.3775480091571808</v>
+        <v>17.52303123474121</v>
       </c>
       <c r="Z515" t="n">
-        <v>0.3796205818653107</v>
+        <v>24.78896141052246</v>
       </c>
     </row>
     <row r="516">
@@ -45596,10 +45596,10 @@
         </is>
       </c>
       <c r="Y516" t="n">
-        <v>0.3772430419921875</v>
+        <v>17.43680381774902</v>
       </c>
       <c r="Z516" t="n">
-        <v>0.3796161413192749</v>
+        <v>24.03577995300293</v>
       </c>
     </row>
     <row r="517">
@@ -45659,7 +45659,7 @@
       </c>
       <c r="Y517" t="inlineStr"/>
       <c r="Z517" t="n">
-        <v>0.3690465986728668</v>
+        <v>8.462862968444824</v>
       </c>
     </row>
     <row r="518">
@@ -45719,7 +45719,7 @@
       </c>
       <c r="Y518" t="inlineStr"/>
       <c r="Z518" t="n">
-        <v>0.3584786653518677</v>
+        <v>10.7980375289917</v>
       </c>
     </row>
     <row r="519">
@@ -45779,7 +45779,7 @@
       </c>
       <c r="Y519" t="inlineStr"/>
       <c r="Z519" t="n">
-        <v>0.352751761674881</v>
+        <v>11.07095623016357</v>
       </c>
     </row>
     <row r="520">
@@ -45839,7 +45839,7 @@
       </c>
       <c r="Y520" t="inlineStr"/>
       <c r="Z520" t="n">
-        <v>0.3507013916969299</v>
+        <v>11.25950145721436</v>
       </c>
     </row>
     <row r="521">
@@ -45930,10 +45930,10 @@
         </is>
       </c>
       <c r="Y521" t="n">
-        <v>0.3795366585254669</v>
+        <v>16.80183410644531</v>
       </c>
       <c r="Z521" t="n">
-        <v>0.3783026933670044</v>
+        <v>11.70072746276855</v>
       </c>
     </row>
     <row r="522">
@@ -46024,10 +46024,10 @@
         </is>
       </c>
       <c r="Y522" t="n">
-        <v>0.3794332146644592</v>
+        <v>16.67097473144531</v>
       </c>
       <c r="Z522" t="n">
-        <v>0.3769655227661133</v>
+        <v>13.06322479248047</v>
       </c>
     </row>
     <row r="523">
@@ -46118,10 +46118,10 @@
         </is>
       </c>
       <c r="Y523" t="n">
-        <v>0.3793458640575409</v>
+        <v>17.92171287536621</v>
       </c>
       <c r="Z523" t="n">
-        <v>0.3768187761306763</v>
+        <v>14.49361515045166</v>
       </c>
     </row>
     <row r="524">
@@ -46212,10 +46212,10 @@
         </is>
       </c>
       <c r="Y524" t="n">
-        <v>0.3786232471466064</v>
+        <v>17.08944129943848</v>
       </c>
       <c r="Z524" t="n">
-        <v>0.3758810460567474</v>
+        <v>14.18660831451416</v>
       </c>
     </row>
     <row r="525">
@@ -46306,10 +46306,10 @@
         </is>
       </c>
       <c r="Y525" t="n">
-        <v>0.3782095313072205</v>
+        <v>17.19306755065918</v>
       </c>
       <c r="Z525" t="n">
-        <v>0.3748463094234467</v>
+        <v>14.20054912567139</v>
       </c>
     </row>
     <row r="526">
@@ -46400,10 +46400,10 @@
         </is>
       </c>
       <c r="Y526" t="n">
-        <v>0.3774643242359161</v>
+        <v>16.81802940368652</v>
       </c>
       <c r="Z526" t="n">
-        <v>0.3710201978683472</v>
+        <v>13.66251659393311</v>
       </c>
     </row>
     <row r="527">
@@ -46494,10 +46494,10 @@
         </is>
       </c>
       <c r="Y527" t="n">
-        <v>0.3762491941452026</v>
+        <v>16.6643123626709</v>
       </c>
       <c r="Z527" t="n">
-        <v>0.3694652020931244</v>
+        <v>13.99290180206299</v>
       </c>
     </row>
     <row r="528">
@@ -46588,10 +46588,10 @@
         </is>
       </c>
       <c r="Y528" t="n">
-        <v>0.3795802295207977</v>
+        <v>12.08987903594971</v>
       </c>
       <c r="Z528" t="n">
-        <v>0.3791457712650299</v>
+        <v>9.350812911987305</v>
       </c>
     </row>
     <row r="529">
@@ -46682,10 +46682,10 @@
         </is>
       </c>
       <c r="Y529" t="n">
-        <v>0.3795204162597656</v>
+        <v>18.30075645446777</v>
       </c>
       <c r="Z529" t="n">
-        <v>0.3786515891551971</v>
+        <v>15.26309299468994</v>
       </c>
     </row>
     <row r="530">
@@ -46776,10 +46776,10 @@
         </is>
       </c>
       <c r="Y530" t="n">
-        <v>0.3794746398925781</v>
+        <v>16.49150848388672</v>
       </c>
       <c r="Z530" t="n">
-        <v>0.3781748116016388</v>
+        <v>13.41614818572998</v>
       </c>
     </row>
     <row r="531">
@@ -46870,10 +46870,10 @@
         </is>
       </c>
       <c r="Y531" t="n">
-        <v>0.379375547170639</v>
+        <v>16.15574264526367</v>
       </c>
       <c r="Z531" t="n">
-        <v>0.374406486749649</v>
+        <v>12.72239589691162</v>
       </c>
     </row>
     <row r="532">
@@ -46964,10 +46964,10 @@
         </is>
       </c>
       <c r="Y532" t="n">
-        <v>0.3796330094337463</v>
+        <v>22.09012794494629</v>
       </c>
       <c r="Z532" t="n">
-        <v>0.3796316087245941</v>
+        <v>21.91936302185059</v>
       </c>
     </row>
     <row r="533">
@@ -47058,10 +47058,10 @@
         </is>
       </c>
       <c r="Y533" t="n">
-        <v>0.3796259760856628</v>
+        <v>22.04802513122559</v>
       </c>
       <c r="Z533" t="n">
-        <v>0.379623144865036</v>
+        <v>21.72161865234375</v>
       </c>
     </row>
     <row r="534">
@@ -47152,10 +47152,10 @@
         </is>
       </c>
       <c r="Y534" t="n">
-        <v>0.3796233236789703</v>
+        <v>23.91852378845215</v>
       </c>
       <c r="Z534" t="n">
-        <v>0.379621297121048</v>
+        <v>24.27052879333496</v>
       </c>
     </row>
     <row r="535">
@@ -47246,10 +47246,10 @@
         </is>
       </c>
       <c r="Y535" t="n">
-        <v>0.3796213567256927</v>
+        <v>25.07811546325684</v>
       </c>
       <c r="Z535" t="n">
-        <v>0.3796192407608032</v>
+        <v>25.09746551513672</v>
       </c>
     </row>
     <row r="536">
@@ -47340,10 +47340,10 @@
         </is>
       </c>
       <c r="Y536" t="n">
-        <v>0.3796196281909943</v>
+        <v>24.73824501037598</v>
       </c>
       <c r="Z536" t="n">
-        <v>0.3796174824237823</v>
+        <v>24.65141105651855</v>
       </c>
     </row>
     <row r="537">
@@ -47434,10 +47434,10 @@
         </is>
       </c>
       <c r="Y537" t="n">
-        <v>0.3796181976795197</v>
+        <v>25.21674919128418</v>
       </c>
       <c r="Z537" t="n">
-        <v>0.3796158134937286</v>
+        <v>25.09554481506348</v>
       </c>
     </row>
     <row r="538">
@@ -47528,10 +47528,10 @@
         </is>
       </c>
       <c r="Y538" t="n">
-        <v>0.3796155452728271</v>
+        <v>24.80143356323242</v>
       </c>
       <c r="Z538" t="n">
-        <v>0.379612922668457</v>
+        <v>24.48612403869629</v>
       </c>
     </row>
     <row r="539">
@@ -47622,10 +47622,10 @@
         </is>
       </c>
       <c r="Y539" t="n">
-        <v>0.3796032667160034</v>
+        <v>23.17031478881836</v>
       </c>
       <c r="Z539" t="n">
-        <v>0.3796111345291138</v>
+        <v>24.5789623260498</v>
       </c>
     </row>
     <row r="540">
@@ -47694,7 +47694,7 @@
         </is>
       </c>
       <c r="Y540" t="n">
-        <v>0.3796010911464691</v>
+        <v>24.76193809509277</v>
       </c>
       <c r="Z540" t="inlineStr"/>
     </row>
@@ -47786,10 +47786,10 @@
         </is>
       </c>
       <c r="Y541" t="n">
-        <v>0.3796399235725403</v>
+        <v>26.37510108947754</v>
       </c>
       <c r="Z541" t="n">
-        <v>0.3796383440494537</v>
+        <v>24.289794921875</v>
       </c>
     </row>
     <row r="542">
@@ -47880,10 +47880,10 @@
         </is>
       </c>
       <c r="Y542" t="n">
-        <v>0.379639744758606</v>
+        <v>27.14152336120605</v>
       </c>
       <c r="Z542" t="n">
-        <v>0.3796366453170776</v>
+        <v>24.43025588989258</v>
       </c>
     </row>
     <row r="543">
@@ -47974,10 +47974,10 @@
         </is>
       </c>
       <c r="Y543" t="n">
-        <v>0.3796289265155792</v>
+        <v>23.83744812011719</v>
       </c>
       <c r="Z543" t="n">
-        <v>0.3796349763870239</v>
+        <v>24.53658485412598</v>
       </c>
     </row>
     <row r="544">
@@ -48068,10 +48068,10 @@
         </is>
       </c>
       <c r="Y544" t="n">
-        <v>0.3796285390853882</v>
+        <v>26.80295753479004</v>
       </c>
       <c r="Z544" t="n">
-        <v>0.3796328902244568</v>
+        <v>25.42013359069824</v>
       </c>
     </row>
     <row r="545">
@@ -48140,7 +48140,7 @@
         </is>
       </c>
       <c r="Y545" t="n">
-        <v>0.3795450627803802</v>
+        <v>21.89929962158203</v>
       </c>
       <c r="Z545" t="inlineStr"/>
     </row>
@@ -48232,10 +48232,10 @@
         </is>
       </c>
       <c r="Y546" t="n">
-        <v>0.3796382546424866</v>
+        <v>23.92720603942871</v>
       </c>
       <c r="Z546" t="n">
-        <v>0.3796371817588806</v>
+        <v>23.26761436462402</v>
       </c>
     </row>
     <row r="547">
@@ -48326,10 +48326,10 @@
         </is>
       </c>
       <c r="Y547" t="n">
-        <v>0.3796364367008209</v>
+        <v>24.99098777770996</v>
       </c>
       <c r="Z547" t="n">
-        <v>0.3796342611312866</v>
+        <v>24.21951866149902</v>
       </c>
     </row>
     <row r="548">
@@ -48420,10 +48420,10 @@
         </is>
       </c>
       <c r="Y548" t="n">
-        <v>0.379632830619812</v>
+        <v>24.07018089294434</v>
       </c>
       <c r="Z548" t="n">
-        <v>0.3796322047710419</v>
+        <v>24.2551326751709</v>
       </c>
     </row>
     <row r="549">
@@ -48514,10 +48514,10 @@
         </is>
       </c>
       <c r="Y549" t="n">
-        <v>0.3796081840991974</v>
+        <v>22.34340667724609</v>
       </c>
       <c r="Z549" t="n">
-        <v>0.3796255588531494</v>
+        <v>23.83514213562012</v>
       </c>
     </row>
     <row r="550">
@@ -48608,10 +48608,10 @@
         </is>
       </c>
       <c r="Y550" t="n">
-        <v>0.3795590400695801</v>
+        <v>21.04234886169434</v>
       </c>
       <c r="Z550" t="n">
-        <v>0.3796214759349823</v>
+        <v>24.14440536499023</v>
       </c>
     </row>
     <row r="551">
@@ -48702,10 +48702,10 @@
         </is>
       </c>
       <c r="Y551" t="n">
-        <v>0.3793120384216309</v>
+        <v>19.07952308654785</v>
       </c>
       <c r="Z551" t="n">
-        <v>0.3796076476573944</v>
+        <v>23.09374237060547</v>
       </c>
     </row>
     <row r="552">
@@ -48796,10 +48796,10 @@
         </is>
       </c>
       <c r="Y552" t="n">
-        <v>0.379082202911377</v>
+        <v>18.8378849029541</v>
       </c>
       <c r="Z552" t="n">
-        <v>0.3789944648742676</v>
+        <v>19.32001686096191</v>
       </c>
     </row>
     <row r="553">
@@ -48870,10 +48870,10 @@
         </is>
       </c>
       <c r="Y553" t="n">
-        <v>0.379639744758606</v>
+        <v>26.02213478088379</v>
       </c>
       <c r="Z553" t="n">
-        <v>0.3796395361423492</v>
+        <v>25.53619575500488</v>
       </c>
     </row>
     <row r="554">
@@ -48944,10 +48944,10 @@
         </is>
       </c>
       <c r="Y554" t="n">
-        <v>0.3796394169330597</v>
+        <v>26.75403022766113</v>
       </c>
       <c r="Z554" t="n">
-        <v>0.3796389997005463</v>
+        <v>26.24165534973145</v>
       </c>
     </row>
     <row r="555">
@@ -49018,10 +49018,10 @@
         </is>
       </c>
       <c r="Y555" t="n">
-        <v>0.379639059305191</v>
+        <v>26.52211570739746</v>
       </c>
       <c r="Z555" t="n">
-        <v>0.3796384036540985</v>
+        <v>26.09045219421387</v>
       </c>
     </row>
     <row r="556">
@@ -49092,10 +49092,10 @@
         </is>
       </c>
       <c r="Y556" t="n">
-        <v>0.379638671875</v>
+        <v>26.9426212310791</v>
       </c>
       <c r="Z556" t="n">
-        <v>0.3796378374099731</v>
+        <v>26.64287376403809</v>
       </c>
     </row>
     <row r="557">
@@ -49186,10 +49186,10 @@
         </is>
       </c>
       <c r="Y557" t="n">
-        <v>0.3796316683292389</v>
+        <v>22.10465049743652</v>
       </c>
       <c r="Z557" t="n">
-        <v>0.3796342313289642</v>
+        <v>22.8352108001709</v>
       </c>
     </row>
     <row r="558">
@@ -49280,10 +49280,10 @@
         </is>
       </c>
       <c r="Y558" t="n">
-        <v>0.3796232640743256</v>
+        <v>22.08426856994629</v>
       </c>
       <c r="Z558" t="n">
-        <v>0.3796283900737762</v>
+        <v>22.86274147033691</v>
       </c>
     </row>
     <row r="559">
@@ -49374,10 +49374,10 @@
         </is>
       </c>
       <c r="Y559" t="n">
-        <v>0.3796212673187256</v>
+        <v>22.73059272766113</v>
       </c>
       <c r="Z559" t="n">
-        <v>0.3796190023422241</v>
+        <v>21.61989212036133</v>
       </c>
     </row>
     <row r="560">
@@ -49468,10 +49468,10 @@
         </is>
       </c>
       <c r="Y560" t="n">
-        <v>0.3796198666095734</v>
+        <v>26.0167179107666</v>
       </c>
       <c r="Z560" t="n">
-        <v>0.3796125054359436</v>
+        <v>25.13974189758301</v>
       </c>
     </row>
     <row r="561">
@@ -49562,10 +49562,10 @@
         </is>
       </c>
       <c r="Y561" t="n">
-        <v>0.3796354532241821</v>
+        <v>23.3084888458252</v>
       </c>
       <c r="Z561" t="n">
-        <v>0.3796396553516388</v>
+        <v>25.92510414123535</v>
       </c>
     </row>
     <row r="562">
@@ -49656,10 +49656,10 @@
         </is>
       </c>
       <c r="Y562" t="n">
-        <v>0.379630833864212</v>
+        <v>22.94011497497559</v>
       </c>
       <c r="Z562" t="n">
-        <v>0.379639208316803</v>
+        <v>26.6277904510498</v>
       </c>
     </row>
     <row r="563">
@@ -49750,10 +49750,10 @@
         </is>
       </c>
       <c r="Y563" t="n">
-        <v>0.3796204626560211</v>
+        <v>22.85529899597168</v>
       </c>
       <c r="Z563" t="n">
-        <v>0.379638671875</v>
+        <v>26.59509468078613</v>
       </c>
     </row>
     <row r="564">
@@ -49844,10 +49844,10 @@
         </is>
       </c>
       <c r="Y564" t="n">
-        <v>0.3796012699604034</v>
+        <v>22.6292839050293</v>
       </c>
       <c r="Z564" t="n">
-        <v>0.3796373903751373</v>
+        <v>26.2268009185791</v>
       </c>
     </row>
     <row r="565">
@@ -49938,10 +49938,10 @@
         </is>
       </c>
       <c r="Y565" t="n">
-        <v>0.3795927166938782</v>
+        <v>22.72782325744629</v>
       </c>
       <c r="Z565" t="n">
-        <v>0.3796357810497284</v>
+        <v>25.60487365722656</v>
       </c>
     </row>
     <row r="566">
@@ -50032,10 +50032,10 @@
         </is>
       </c>
       <c r="Y566" t="n">
-        <v>0.379639595746994</v>
+        <v>25.39296531677246</v>
       </c>
       <c r="Z566" t="n">
-        <v>0.3796384036540985</v>
+        <v>24.27328681945801</v>
       </c>
     </row>
     <row r="567">
@@ -50126,10 +50126,10 @@
         </is>
       </c>
       <c r="Y567" t="n">
-        <v>0.3796390891075134</v>
+        <v>26.49495506286621</v>
       </c>
       <c r="Z567" t="n">
-        <v>0.3796367347240448</v>
+        <v>24.91592597961426</v>
       </c>
     </row>
     <row r="568">
@@ -50220,10 +50220,10 @@
         </is>
       </c>
       <c r="Y568" t="n">
-        <v>0.3796378672122955</v>
+        <v>25.51824760437012</v>
       </c>
       <c r="Z568" t="n">
-        <v>0.3796346485614777</v>
+        <v>24.34741020202637</v>
       </c>
     </row>
     <row r="569">
@@ -50314,10 +50314,10 @@
         </is>
       </c>
       <c r="Y569" t="n">
-        <v>0.3796357810497284</v>
+        <v>26.0145092010498</v>
       </c>
       <c r="Z569" t="n">
-        <v>0.3796318173408508</v>
+        <v>25.50374794006348</v>
       </c>
     </row>
     <row r="570">
@@ -50408,10 +50408,10 @@
         </is>
       </c>
       <c r="Y570" t="n">
-        <v>0.3796340525150299</v>
+        <v>25.39739418029785</v>
       </c>
       <c r="Z570" t="n">
-        <v>0.3796285688877106</v>
+        <v>24.40121650695801</v>
       </c>
     </row>
     <row r="571">
@@ -50502,10 +50502,10 @@
         </is>
       </c>
       <c r="Y571" t="n">
-        <v>0.3796319663524628</v>
+        <v>26.22554588317871</v>
       </c>
       <c r="Z571" t="n">
-        <v>0.3796263635158539</v>
+        <v>25.68350791931152</v>
       </c>
     </row>
     <row r="572">
@@ -50596,10 +50596,10 @@
         </is>
       </c>
       <c r="Y572" t="n">
-        <v>0.3796301484107971</v>
+        <v>25.9614429473877</v>
       </c>
       <c r="Z572" t="n">
-        <v>0.3796209394931793</v>
+        <v>24.70855903625488</v>
       </c>
     </row>
     <row r="573">
@@ -50690,10 +50690,10 @@
         </is>
       </c>
       <c r="Y573" t="n">
-        <v>0.3796385228633881</v>
+        <v>24.18180274963379</v>
       </c>
       <c r="Z573" t="n">
-        <v>0.3796367943286896</v>
+        <v>22.94814872741699</v>
       </c>
     </row>
     <row r="574">
@@ -50784,10 +50784,10 @@
         </is>
       </c>
       <c r="Y574" t="n">
-        <v>0.3796369731426239</v>
+        <v>24.89341163635254</v>
       </c>
       <c r="Z574" t="n">
-        <v>0.3796335458755493</v>
+        <v>23.75550270080566</v>
       </c>
     </row>
     <row r="575">
@@ -50878,10 +50878,10 @@
         </is>
       </c>
       <c r="Y575" t="n">
-        <v>0.3796353936195374</v>
+        <v>24.72877311706543</v>
       </c>
       <c r="Z575" t="n">
-        <v>0.3796320855617523</v>
+        <v>24.30647659301758</v>
       </c>
     </row>
     <row r="576">
@@ -50972,10 +50972,10 @@
         </is>
       </c>
       <c r="Y576" t="n">
-        <v>0.3796337842941284</v>
+        <v>25.44967842102051</v>
       </c>
       <c r="Z576" t="n">
-        <v>0.3796275854110718</v>
+        <v>24.3550853729248</v>
       </c>
     </row>
     <row r="577">
@@ -51066,10 +51066,10 @@
         </is>
       </c>
       <c r="Y577" t="n">
-        <v>0.3796317577362061</v>
+        <v>25.31822776794434</v>
       </c>
       <c r="Z577" t="n">
-        <v>0.3796249330043793</v>
+        <v>24.50379371643066</v>
       </c>
     </row>
     <row r="578">
@@ -51160,10 +51160,10 @@
         </is>
       </c>
       <c r="Y578" t="n">
-        <v>0.3796301484107971</v>
+        <v>25.7108268737793</v>
       </c>
       <c r="Z578" t="n">
-        <v>0.3796229064464569</v>
+        <v>25.28235816955566</v>
       </c>
     </row>
     <row r="579">
@@ -51254,10 +51254,10 @@
         </is>
       </c>
       <c r="Y579" t="n">
-        <v>0.3796285390853882</v>
+        <v>25.02969169616699</v>
       </c>
       <c r="Z579" t="n">
-        <v>0.3796209096908569</v>
+        <v>24.81535720825195</v>
       </c>
     </row>
     <row r="580">
@@ -51348,10 +51348,10 @@
         </is>
       </c>
       <c r="Y580" t="n">
-        <v>0.3794760406017303</v>
+        <v>15.58182716369629</v>
       </c>
       <c r="Z580" t="n">
-        <v>0.3796361982822418</v>
+        <v>22.62618827819824</v>
       </c>
     </row>
     <row r="581">
@@ -51442,10 +51442,10 @@
         </is>
       </c>
       <c r="Y581" t="n">
-        <v>0.3793120682239532</v>
+        <v>15.82109546661377</v>
       </c>
       <c r="Z581" t="n">
-        <v>0.3796323239803314</v>
+        <v>23.26965522766113</v>
       </c>
     </row>
     <row r="582">
@@ -51536,10 +51536,10 @@
         </is>
       </c>
       <c r="Y582" t="n">
-        <v>0.3790818750858307</v>
+        <v>16.04510879516602</v>
       </c>
       <c r="Z582" t="n">
-        <v>0.3796239495277405</v>
+        <v>22.37150382995605</v>
       </c>
     </row>
     <row r="583">
@@ -51630,10 +51630,10 @@
         </is>
       </c>
       <c r="Y583" t="n">
-        <v>0.3784874975681305</v>
+        <v>15.75306797027588</v>
       </c>
       <c r="Z583" t="n">
-        <v>0.3796088099479675</v>
+        <v>22.58120155334473</v>
       </c>
     </row>
     <row r="584">
@@ -51724,10 +51724,10 @@
         </is>
       </c>
       <c r="Y584" t="n">
-        <v>0.3773716986179352</v>
+        <v>16.04923629760742</v>
       </c>
       <c r="Z584" t="n">
-        <v>0.379603773355484</v>
+        <v>24.13974761962891</v>
       </c>
     </row>
     <row r="585">
@@ -51818,10 +51818,10 @@
         </is>
       </c>
       <c r="Y585" t="n">
-        <v>0.3765433430671692</v>
+        <v>16.32761192321777</v>
       </c>
       <c r="Z585" t="n">
-        <v>0.3795709908008575</v>
+        <v>22.36600494384766</v>
       </c>
     </row>
     <row r="586">
@@ -51892,10 +51892,10 @@
         </is>
       </c>
       <c r="Y586" t="n">
-        <v>0.3796380460262299</v>
+        <v>24.29758644104004</v>
       </c>
       <c r="Z586" t="n">
-        <v>0.3796385228633881</v>
+        <v>24.88761329650879</v>
       </c>
     </row>
     <row r="587">
@@ -51966,10 +51966,10 @@
         </is>
       </c>
       <c r="Y587" t="n">
-        <v>0.3796360194683075</v>
+        <v>24.70676422119141</v>
       </c>
       <c r="Z587" t="n">
-        <v>0.3796369433403015</v>
+        <v>25.23718643188477</v>
       </c>
     </row>
     <row r="588">
@@ -52040,10 +52040,10 @@
         </is>
       </c>
       <c r="Y588" t="n">
-        <v>0.379635363817215</v>
+        <v>25.66017723083496</v>
       </c>
       <c r="Z588" t="n">
-        <v>0.3796363174915314</v>
+        <v>25.71549797058105</v>
       </c>
     </row>
     <row r="589">
@@ -52114,10 +52114,10 @@
         </is>
       </c>
       <c r="Y589" t="n">
-        <v>0.3796323537826538</v>
+        <v>25.27987480163574</v>
       </c>
       <c r="Z589" t="n">
-        <v>0.3796347677707672</v>
+        <v>25.93181228637695</v>
       </c>
     </row>
     <row r="590">
@@ -52187,7 +52187,7 @@
       </c>
       <c r="Y590" t="inlineStr"/>
       <c r="Z590" t="n">
-        <v>0.3794353306293488</v>
+        <v>15.27466869354248</v>
       </c>
     </row>
     <row r="591">
@@ -52257,7 +52257,7 @@
       </c>
       <c r="Y591" t="inlineStr"/>
       <c r="Z591" t="n">
-        <v>0.3792306184768677</v>
+        <v>16.00475120544434</v>
       </c>
     </row>
     <row r="592">
@@ -52327,7 +52327,7 @@
       </c>
       <c r="Y592" t="inlineStr"/>
       <c r="Z592" t="n">
-        <v>0.3791783452033997</v>
+        <v>16.60091781616211</v>
       </c>
     </row>
     <row r="593">
@@ -52397,7 +52397,7 @@
       </c>
       <c r="Y593" t="inlineStr"/>
       <c r="Z593" t="n">
-        <v>0.379127711057663</v>
+        <v>18.02962493896484</v>
       </c>
     </row>
     <row r="594">
@@ -52488,10 +52488,10 @@
         </is>
       </c>
       <c r="Y594" t="n">
-        <v>0.379599004983902</v>
+        <v>18.92009544372559</v>
       </c>
       <c r="Z594" t="n">
-        <v>0.3796029984951019</v>
+        <v>19.17419242858887</v>
       </c>
     </row>
     <row r="595">
@@ -52582,10 +52582,10 @@
         </is>
       </c>
       <c r="Y595" t="n">
-        <v>0.3795579075813293</v>
+        <v>18.47519302368164</v>
       </c>
       <c r="Z595" t="n">
-        <v>0.379565954208374</v>
+        <v>18.61703300476074</v>
       </c>
     </row>
     <row r="596">
@@ -52676,10 +52676,10 @@
         </is>
       </c>
       <c r="Y596" t="n">
-        <v>0.3795525431632996</v>
+        <v>21.96733474731445</v>
       </c>
       <c r="Z596" t="n">
-        <v>0.3795154988765717</v>
+        <v>19.89643669128418</v>
       </c>
     </row>
     <row r="597">
@@ -52770,10 +52770,10 @@
         </is>
       </c>
       <c r="Y597" t="n">
-        <v>0.3795469403266907</v>
+        <v>22.9505615234375</v>
       </c>
       <c r="Z597" t="n">
-        <v>0.3794838786125183</v>
+        <v>20.70607566833496</v>
       </c>
     </row>
     <row r="598">
@@ -52864,10 +52864,10 @@
         </is>
       </c>
       <c r="Y598" t="n">
-        <v>0.3795348405838013</v>
+        <v>21.6463794708252</v>
       </c>
       <c r="Z598" t="n">
-        <v>0.3794589042663574</v>
+        <v>20.88357543945312</v>
       </c>
     </row>
     <row r="599">
@@ -52958,10 +52958,10 @@
         </is>
       </c>
       <c r="Y599" t="n">
-        <v>0.3795140981674194</v>
+        <v>20.96353912353516</v>
       </c>
       <c r="Z599" t="n">
-        <v>0.3793380260467529</v>
+        <v>19.4839038848877</v>
       </c>
     </row>
     <row r="600">
@@ -53052,10 +53052,10 @@
         </is>
       </c>
       <c r="Y600" t="n">
-        <v>0.37950199842453</v>
+        <v>22.30802536010742</v>
       </c>
       <c r="Z600" t="n">
-        <v>0.3792924284934998</v>
+        <v>20.63479042053223</v>
       </c>
     </row>
     <row r="601">
@@ -53146,10 +53146,10 @@
         </is>
       </c>
       <c r="Y601" t="n">
-        <v>0.3794906437397003</v>
+        <v>21.69820976257324</v>
       </c>
       <c r="Z601" t="n">
-        <v>0.379189670085907</v>
+        <v>19.24006462097168</v>
       </c>
     </row>
     <row r="602">
@@ -53240,10 +53240,10 @@
         </is>
       </c>
       <c r="Y602" t="n">
-        <v>0.3796260952949524</v>
+        <v>20.84699821472168</v>
       </c>
       <c r="Z602" t="n">
-        <v>0.3795425295829773</v>
+        <v>16.97238922119141</v>
       </c>
     </row>
     <row r="603">
@@ -53334,10 +53334,10 @@
         </is>
       </c>
       <c r="Y603" t="n">
-        <v>0.3796121180057526</v>
+        <v>20.60477256774902</v>
       </c>
       <c r="Z603" t="n">
-        <v>0.3794450163841248</v>
+        <v>16.98517227172852</v>
       </c>
     </row>
     <row r="604">
@@ -53428,10 +53428,10 @@
         </is>
       </c>
       <c r="Y604" t="n">
-        <v>0.3795890212059021</v>
+        <v>21.06275177001953</v>
       </c>
       <c r="Z604" t="n">
-        <v>0.3793623149394989</v>
+        <v>17.9011287689209</v>
       </c>
     </row>
     <row r="605">
@@ -53522,10 +53522,10 @@
         </is>
       </c>
       <c r="Y605" t="n">
-        <v>0.3795730471611023</v>
+        <v>22.33587837219238</v>
       </c>
       <c r="Z605" t="n">
-        <v>0.3791403770446777</v>
+        <v>17.81133651733398</v>
       </c>
     </row>
     <row r="606">
@@ -53616,10 +53616,10 @@
         </is>
       </c>
       <c r="Y606" t="n">
-        <v>0.3795559108257294</v>
+        <v>22.02549934387207</v>
       </c>
       <c r="Z606" t="n">
-        <v>0.3789542019367218</v>
+        <v>17.64113426208496</v>
       </c>
     </row>
     <row r="607">
@@ -53710,10 +53710,10 @@
         </is>
       </c>
       <c r="Y607" t="n">
-        <v>0.3796388804912567</v>
+        <v>24.49508094787598</v>
       </c>
       <c r="Z607" t="n">
-        <v>0.3796385228633881</v>
+        <v>24.0205249786377</v>
       </c>
     </row>
     <row r="608">
@@ -53804,10 +53804,10 @@
         </is>
       </c>
       <c r="Y608" t="n">
-        <v>0.3796377182006836</v>
+        <v>25.48502540588379</v>
       </c>
       <c r="Z608" t="n">
-        <v>0.3796369731426239</v>
+        <v>24.93560981750488</v>
       </c>
     </row>
     <row r="609">
@@ -53898,10 +53898,10 @@
         </is>
       </c>
       <c r="Y609" t="n">
-        <v>0.3796367943286896</v>
+        <v>25.46509742736816</v>
       </c>
       <c r="Z609" t="n">
-        <v>0.3796345889568329</v>
+        <v>24.32879066467285</v>
       </c>
     </row>
     <row r="610">
@@ -53992,10 +53992,10 @@
         </is>
       </c>
       <c r="Y610" t="n">
-        <v>0.3796343207359314</v>
+        <v>25.37873649597168</v>
       </c>
       <c r="Z610" t="n">
-        <v>0.379631906747818</v>
+        <v>24.88538551330566</v>
       </c>
     </row>
     <row r="611">
@@ -54086,10 +54086,10 @@
         </is>
       </c>
       <c r="Y611" t="n">
-        <v>0.379632294178009</v>
+        <v>25.66364860534668</v>
       </c>
       <c r="Z611" t="n">
-        <v>0.3796277046203613</v>
+        <v>24.8943042755127</v>
       </c>
     </row>
     <row r="612">
@@ -54180,10 +54180,10 @@
         </is>
       </c>
       <c r="Y612" t="n">
-        <v>0.3796314001083374</v>
+        <v>25.87404441833496</v>
       </c>
       <c r="Z612" t="n">
-        <v>0.3796260356903076</v>
+        <v>25.04075622558594</v>
       </c>
     </row>
     <row r="613">
@@ -54274,10 +54274,10 @@
         </is>
       </c>
       <c r="Y613" t="n">
-        <v>0.3796353936195374</v>
+        <v>22.25951385498047</v>
       </c>
       <c r="Z613" t="n">
-        <v>0.3792872726917267</v>
+        <v>13.43308258056641</v>
       </c>
     </row>
     <row r="614">
@@ -54368,10 +54368,10 @@
         </is>
       </c>
       <c r="Y614" t="n">
-        <v>0.3796307146549225</v>
+        <v>22.06403160095215</v>
       </c>
       <c r="Z614" t="n">
-        <v>0.3789344727993011</v>
+        <v>14.33312892913818</v>
       </c>
     </row>
     <row r="615">
@@ -54462,10 +54462,10 @@
         </is>
       </c>
       <c r="Y615" t="n">
-        <v>0.3796237111091614</v>
+        <v>22.34551620483398</v>
       </c>
       <c r="Z615" t="n">
-        <v>0.3787217140197754</v>
+        <v>15.0470609664917</v>
       </c>
     </row>
     <row r="616">
@@ -54556,10 +54556,10 @@
         </is>
       </c>
       <c r="Y616" t="n">
-        <v>0.379597395658493</v>
+        <v>22.26027870178223</v>
       </c>
       <c r="Z616" t="n">
-        <v>0.3776885569095612</v>
+        <v>14.66685581207275</v>
       </c>
     </row>
     <row r="617">
@@ -54650,10 +54650,10 @@
         </is>
       </c>
       <c r="Y617" t="n">
-        <v>0.3794731497764587</v>
+        <v>15.54642963409424</v>
       </c>
       <c r="Z617" t="n">
-        <v>0.3796141147613525</v>
+        <v>19.83895683288574</v>
       </c>
     </row>
     <row r="618">
@@ -54744,10 +54744,10 @@
         </is>
       </c>
       <c r="Y618" t="n">
-        <v>0.3793062269687653</v>
+        <v>15.53219127655029</v>
       </c>
       <c r="Z618" t="n">
-        <v>0.3795881569385529</v>
+        <v>19.08680534362793</v>
       </c>
     </row>
     <row r="619">
@@ -54838,10 +54838,10 @@
         </is>
       </c>
       <c r="Y619" t="n">
-        <v>0.3788293898105621</v>
+        <v>15.55461597442627</v>
       </c>
       <c r="Z619" t="n">
-        <v>0.3795562982559204</v>
+        <v>20.5507869720459</v>
       </c>
     </row>
     <row r="620">
@@ -54932,10 +54932,10 @@
         </is>
       </c>
       <c r="Y620" t="n">
-        <v>0.3785053491592407</v>
+        <v>16.0265064239502</v>
       </c>
       <c r="Z620" t="n">
-        <v>0.3795057535171509</v>
+        <v>20.85459899902344</v>
       </c>
     </row>
     <row r="621">
@@ -55026,10 +55026,10 @@
         </is>
       </c>
       <c r="Y621" t="n">
-        <v>0.3777599334716797</v>
+        <v>15.88221836090088</v>
       </c>
       <c r="Z621" t="n">
-        <v>0.3794645965099335</v>
+        <v>20.5494499206543</v>
       </c>
     </row>
     <row r="622">
@@ -55120,10 +55120,10 @@
         </is>
       </c>
       <c r="Y622" t="n">
-        <v>0.3775607645511627</v>
+        <v>16.66645622253418</v>
       </c>
       <c r="Z622" t="n">
-        <v>0.3793557584285736</v>
+        <v>20.00625991821289</v>
       </c>
     </row>
     <row r="623">
@@ -55214,10 +55214,10 @@
         </is>
       </c>
       <c r="Y623" t="n">
-        <v>0.3796252310276031</v>
+        <v>20.0130615234375</v>
       </c>
       <c r="Z623" t="n">
-        <v>0.379639059305191</v>
+        <v>24.51744270324707</v>
       </c>
     </row>
     <row r="624">
@@ -55308,10 +55308,10 @@
         </is>
       </c>
       <c r="Y624" t="n">
-        <v>0.3796103596687317</v>
+        <v>20.3483715057373</v>
       </c>
       <c r="Z624" t="n">
-        <v>0.3796380460262299</v>
+        <v>25.41297340393066</v>
       </c>
     </row>
     <row r="625">
@@ -55402,10 +55402,10 @@
         </is>
       </c>
       <c r="Y625" t="n">
-        <v>0.3796008229255676</v>
+        <v>21.33550643920898</v>
       </c>
       <c r="Z625" t="n">
-        <v>0.3796351253986359</v>
+        <v>24.18823051452637</v>
       </c>
     </row>
     <row r="626">
@@ -55496,10 +55496,10 @@
         </is>
       </c>
       <c r="Y626" t="n">
-        <v>0.3795790672302246</v>
+        <v>22.12487983703613</v>
       </c>
       <c r="Z626" t="n">
-        <v>0.3796332180500031</v>
+        <v>25.43814659118652</v>
       </c>
     </row>
     <row r="627">
@@ -55590,10 +55590,10 @@
         </is>
       </c>
       <c r="Y627" t="n">
-        <v>0.3795720934867859</v>
+        <v>22.07315444946289</v>
       </c>
       <c r="Z627" t="n">
-        <v>0.3796316087245941</v>
+        <v>25.44439697265625</v>
       </c>
     </row>
     <row r="628">
@@ -55684,10 +55684,10 @@
         </is>
       </c>
       <c r="Y628" t="n">
-        <v>0.3790168166160583</v>
+        <v>12.61657333374023</v>
       </c>
       <c r="Z628" t="n">
-        <v>0.3791402578353882</v>
+        <v>13.38163280487061</v>
       </c>
     </row>
     <row r="629">
@@ -55778,10 +55778,10 @@
         </is>
       </c>
       <c r="Y629" t="n">
-        <v>0.378393679857254</v>
+        <v>13.61515045166016</v>
       </c>
       <c r="Z629" t="n">
-        <v>0.3786404728889465</v>
+        <v>14.12705039978027</v>
       </c>
     </row>
     <row r="630">
@@ -55872,10 +55872,10 @@
         </is>
       </c>
       <c r="Y630" t="n">
-        <v>0.3775631487369537</v>
+        <v>14.02861309051514</v>
       </c>
       <c r="Z630" t="n">
-        <v>0.3783994317054749</v>
+        <v>15.01890754699707</v>
       </c>
     </row>
     <row r="631">
@@ -55966,10 +55966,10 @@
         </is>
       </c>
       <c r="Y631" t="n">
-        <v>0.377020537853241</v>
+        <v>14.68259048461914</v>
       </c>
       <c r="Z631" t="n">
-        <v>0.3782225847244263</v>
+        <v>15.64880847930908</v>
       </c>
     </row>
     <row r="632">
@@ -56060,10 +56060,10 @@
         </is>
       </c>
       <c r="Y632" t="n">
-        <v>0.3744025230407715</v>
+        <v>13.78947067260742</v>
       </c>
       <c r="Z632" t="n">
-        <v>0.3781124353408813</v>
+        <v>15.82069683074951</v>
       </c>
     </row>
     <row r="633">
@@ -56133,7 +56133,7 @@
       </c>
       <c r="Y633" t="inlineStr"/>
       <c r="Z633" t="n">
-        <v>0.3780848979949951</v>
+        <v>17.3786449432373</v>
       </c>
     </row>
     <row r="634">
@@ -56203,7 +56203,7 @@
       </c>
       <c r="Y634" t="inlineStr"/>
       <c r="Z634" t="n">
-        <v>0.377973735332489</v>
+        <v>16.95029640197754</v>
       </c>
     </row>
     <row r="635">
@@ -56294,10 +56294,10 @@
         </is>
       </c>
       <c r="Y635" t="n">
-        <v>0.3796285688877106</v>
+        <v>21.08350372314453</v>
       </c>
       <c r="Z635" t="n">
-        <v>0.379614919424057</v>
+        <v>19.75503730773926</v>
       </c>
     </row>
     <row r="636">
@@ -56388,10 +56388,10 @@
         </is>
       </c>
       <c r="Y636" t="n">
-        <v>0.3796170651912689</v>
+        <v>20.41061592102051</v>
       </c>
       <c r="Z636" t="n">
-        <v>0.3795897662639618</v>
+        <v>18.76641273498535</v>
       </c>
     </row>
     <row r="637">
@@ -56482,10 +56482,10 @@
         </is>
       </c>
       <c r="Y637" t="n">
-        <v>0.3796011507511139</v>
+        <v>20.7232608795166</v>
       </c>
       <c r="Z637" t="n">
-        <v>0.3795362412929535</v>
+        <v>19.93170738220215</v>
       </c>
     </row>
     <row r="638">
@@ -56576,10 +56576,10 @@
         </is>
       </c>
       <c r="Y638" t="n">
-        <v>0.3795786798000336</v>
+        <v>20.81283378601074</v>
       </c>
       <c r="Z638" t="n">
-        <v>0.3795171082019806</v>
+        <v>20.4194450378418</v>
       </c>
     </row>
     <row r="639">
@@ -56670,10 +56670,10 @@
         </is>
       </c>
       <c r="Y639" t="n">
-        <v>0.3795640468597412</v>
+        <v>21.94008445739746</v>
       </c>
       <c r="Z639" t="n">
-        <v>0.3794666230678558</v>
+        <v>20.42468070983887</v>
       </c>
     </row>
     <row r="640">
@@ -56743,7 +56743,7 @@
       </c>
       <c r="Y640" t="inlineStr"/>
       <c r="Z640" t="n">
-        <v>0.3794119358062744</v>
+        <v>20.61467933654785</v>
       </c>
     </row>
     <row r="641">
@@ -56834,10 +56834,10 @@
         </is>
       </c>
       <c r="Y641" t="n">
-        <v>0.3796394765377045</v>
+        <v>25.64914512634277</v>
       </c>
       <c r="Z641" t="n">
-        <v>0.379639059305191</v>
+        <v>25.22584342956543</v>
       </c>
     </row>
     <row r="642">
@@ -56928,10 +56928,10 @@
         </is>
       </c>
       <c r="Y642" t="n">
-        <v>0.3796388804912567</v>
+        <v>26.23147583007812</v>
       </c>
       <c r="Z642" t="n">
-        <v>0.3796380460262299</v>
+        <v>25.63548851013184</v>
       </c>
     </row>
     <row r="643">
@@ -57022,10 +57022,10 @@
         </is>
       </c>
       <c r="Y643" t="n">
-        <v>0.3796379864215851</v>
+        <v>25.9925365447998</v>
       </c>
       <c r="Z643" t="n">
-        <v>0.3796363770961761</v>
+        <v>25.19135093688965</v>
       </c>
     </row>
     <row r="644">
@@ -57116,10 +57116,10 @@
         </is>
       </c>
       <c r="Y644" t="n">
-        <v>0.3796372711658478</v>
+        <v>26.58211326599121</v>
       </c>
       <c r="Z644" t="n">
-        <v>0.3796358406543732</v>
+        <v>26.61902809143066</v>
       </c>
     </row>
     <row r="645">
@@ -57210,10 +57210,10 @@
         </is>
       </c>
       <c r="Y645" t="n">
-        <v>0.3796344697475433</v>
+        <v>25.59971809387207</v>
       </c>
       <c r="Z645" t="n">
-        <v>0.3796336352825165</v>
+        <v>25.64520835876465</v>
       </c>
     </row>
     <row r="646">
@@ -57304,10 +57304,10 @@
         </is>
       </c>
       <c r="Y646" t="n">
-        <v>0.3796333074569702</v>
+        <v>25.92369270324707</v>
       </c>
       <c r="Z646" t="n">
-        <v>0.3796325623989105</v>
+        <v>25.89423179626465</v>
       </c>
     </row>
     <row r="647">
@@ -57377,7 +57377,7 @@
       </c>
       <c r="Y647" t="inlineStr"/>
       <c r="Z647" t="n">
-        <v>0.3796308636665344</v>
+        <v>15.17616844177246</v>
       </c>
     </row>
     <row r="648">
@@ -57447,7 +57447,7 @@
       </c>
       <c r="Y648" t="inlineStr"/>
       <c r="Z648" t="n">
-        <v>0.3796216547489166</v>
+        <v>21.41658592224121</v>
       </c>
     </row>
     <row r="649">
@@ -57517,7 +57517,7 @@
       </c>
       <c r="Y649" t="inlineStr"/>
       <c r="Z649" t="n">
-        <v>0.3796098232269287</v>
+        <v>19.99515724182129</v>
       </c>
     </row>
     <row r="650">
@@ -57587,7 +57587,7 @@
       </c>
       <c r="Y650" t="inlineStr"/>
       <c r="Z650" t="n">
-        <v>0.3796014785766602</v>
+        <v>20.17652320861816</v>
       </c>
     </row>
     <row r="651">
@@ -57678,10 +57678,10 @@
         </is>
       </c>
       <c r="Y651" t="n">
-        <v>0.3796380758285522</v>
+        <v>24.78020668029785</v>
       </c>
       <c r="Z651" t="n">
-        <v>0.3796387314796448</v>
+        <v>25.35185813903809</v>
       </c>
     </row>
     <row r="652">
@@ -57772,10 +57772,10 @@
         </is>
       </c>
       <c r="Y652" t="n">
-        <v>0.3796361088752747</v>
+        <v>25.0742301940918</v>
       </c>
       <c r="Z652" t="n">
-        <v>0.3796373903751373</v>
+        <v>25.80585289001465</v>
       </c>
     </row>
     <row r="653">
@@ -57866,10 +57866,10 @@
         </is>
       </c>
       <c r="Y653" t="n">
-        <v>0.3796350657939911</v>
+        <v>25.4008731842041</v>
       </c>
       <c r="Z653" t="n">
-        <v>0.3796357810497284</v>
+        <v>25.30967140197754</v>
       </c>
     </row>
     <row r="654">
@@ -57960,10 +57960,10 @@
         </is>
       </c>
       <c r="Y654" t="n">
-        <v>0.3796337246894836</v>
+        <v>26.36950492858887</v>
       </c>
       <c r="Z654" t="n">
-        <v>0.3796344399452209</v>
+        <v>26.43362236022949</v>
       </c>
     </row>
     <row r="655">
@@ -58054,10 +58054,10 @@
         </is>
       </c>
       <c r="Y655" t="n">
-        <v>0.3796296119689941</v>
+        <v>25.41396903991699</v>
       </c>
       <c r="Z655" t="n">
-        <v>0.3796286582946777</v>
+        <v>25.38608741760254</v>
       </c>
     </row>
     <row r="656">
@@ -58148,10 +58148,10 @@
         </is>
       </c>
       <c r="Y656" t="n">
-        <v>0.3796282112598419</v>
+        <v>25.68610954284668</v>
       </c>
       <c r="Z656" t="n">
-        <v>0.3796270489692688</v>
+        <v>25.57319259643555</v>
       </c>
     </row>
     <row r="657">
@@ -58242,10 +58242,10 @@
         </is>
       </c>
       <c r="Y657" t="n">
-        <v>0.3119836151599884</v>
+        <v>6.161768436431885</v>
       </c>
       <c r="Z657" t="n">
-        <v>0.3787779808044434</v>
+        <v>12.39095211029053</v>
       </c>
     </row>
     <row r="658">
@@ -58336,10 +58336,10 @@
         </is>
       </c>
       <c r="Y658" t="n">
-        <v>0.2454735338687897</v>
+        <v>7.629272937774658</v>
       </c>
       <c r="Z658" t="n">
-        <v>0.3779160380363464</v>
+        <v>13.53600025177002</v>
       </c>
     </row>
     <row r="659">
@@ -58430,10 +58430,10 @@
         </is>
       </c>
       <c r="Y659" t="n">
-        <v>0.1949248611927032</v>
+        <v>9.022434234619141</v>
       </c>
       <c r="Z659" t="n">
-        <v>0.3777167201042175</v>
+        <v>14.8051118850708</v>
       </c>
     </row>
     <row r="660">
@@ -58524,10 +58524,10 @@
         </is>
       </c>
       <c r="Y660" t="n">
-        <v>0.1756733357906342</v>
+        <v>9.420390129089355</v>
       </c>
       <c r="Z660" t="n">
-        <v>0.377646416425705</v>
+        <v>15.98204612731934</v>
       </c>
     </row>
     <row r="661">
@@ -58618,10 +58618,10 @@
         </is>
       </c>
       <c r="Y661" t="n">
-        <v>0.1292144060134888</v>
+        <v>10.15453720092773</v>
       </c>
       <c r="Z661" t="n">
-        <v>0.3774803578853607</v>
+        <v>16.56341361999512</v>
       </c>
     </row>
     <row r="662">
@@ -58712,10 +58712,10 @@
         </is>
       </c>
       <c r="Y662" t="n">
-        <v>0.1242563426494598</v>
+        <v>10.879075050354</v>
       </c>
       <c r="Z662" t="n">
-        <v>0.3770390450954437</v>
+        <v>16.23039627075195</v>
       </c>
     </row>
     <row r="663">
@@ -58785,7 +58785,7 @@
       </c>
       <c r="Y663" t="inlineStr"/>
       <c r="Z663" t="n">
-        <v>0.3769692778587341</v>
+        <v>17.79824829101562</v>
       </c>
     </row>
     <row r="664">
@@ -58876,10 +58876,10 @@
         </is>
       </c>
       <c r="Y664" t="n">
-        <v>0.3793726861476898</v>
+        <v>15.18147277832031</v>
       </c>
       <c r="Z664" t="n">
-        <v>0.3788950443267822</v>
+        <v>13.04146289825439</v>
       </c>
     </row>
     <row r="665">
@@ -58970,10 +58970,10 @@
         </is>
       </c>
       <c r="Y665" t="n">
-        <v>0.3791052997112274</v>
+        <v>15.39154052734375</v>
       </c>
       <c r="Z665" t="n">
-        <v>0.3781499564647675</v>
+        <v>13.97809314727783</v>
       </c>
     </row>
     <row r="666">
@@ -59064,10 +59064,10 @@
         </is>
       </c>
       <c r="Y666" t="n">
-        <v>0.3790037035942078</v>
+        <v>16.41995811462402</v>
       </c>
       <c r="Z666" t="n">
-        <v>0.3767497539520264</v>
+        <v>13.95969390869141</v>
       </c>
     </row>
     <row r="667">
@@ -59158,10 +59158,10 @@
         </is>
       </c>
       <c r="Y667" t="n">
-        <v>0.3786732852458954</v>
+        <v>15.98268032073975</v>
       </c>
       <c r="Z667" t="n">
-        <v>0.374140739440918</v>
+        <v>13.64107608795166</v>
       </c>
     </row>
     <row r="668">
@@ -59252,10 +59252,10 @@
         </is>
       </c>
       <c r="Y668" t="n">
-        <v>0.3796030282974243</v>
+        <v>20.58596229553223</v>
       </c>
       <c r="Z668" t="n">
-        <v>0.3795733153820038</v>
+        <v>18.67733573913574</v>
       </c>
     </row>
     <row r="669">
@@ -59346,10 +59346,10 @@
         </is>
       </c>
       <c r="Y669" t="n">
-        <v>0.379565954208374</v>
+        <v>19.99143409729004</v>
       </c>
       <c r="Z669" t="n">
-        <v>0.3795065581798553</v>
+        <v>18.33883857727051</v>
       </c>
     </row>
     <row r="670">
@@ -59440,10 +59440,10 @@
         </is>
       </c>
       <c r="Y670" t="n">
-        <v>0.3795527815818787</v>
+        <v>22.54777336120605</v>
       </c>
       <c r="Z670" t="n">
-        <v>0.3794066905975342</v>
+        <v>19.32673263549805</v>
       </c>
     </row>
     <row r="671">
@@ -59534,10 +59534,10 @@
         </is>
       </c>
       <c r="Y671" t="n">
-        <v>0.3795401155948639</v>
+        <v>23.07353210449219</v>
       </c>
       <c r="Z671" t="n">
-        <v>0.3792302012443542</v>
+        <v>19.15346717834473</v>
       </c>
     </row>
     <row r="672">
@@ -59628,10 +59628,10 @@
         </is>
       </c>
       <c r="Y672" t="n">
-        <v>0.3785894811153412</v>
+        <v>12.96335792541504</v>
       </c>
       <c r="Z672" t="n">
-        <v>0.3702501356601715</v>
+        <v>8.86212158203125</v>
       </c>
     </row>
     <row r="673">
@@ -59722,10 +59722,10 @@
         </is>
       </c>
       <c r="Y673" t="n">
-        <v>0.3775390088558197</v>
+        <v>14.39926815032959</v>
       </c>
       <c r="Z673" t="n">
-        <v>0.3608796000480652</v>
+        <v>11.36511993408203</v>
       </c>
     </row>
     <row r="674">
@@ -59816,10 +59816,10 @@
         </is>
       </c>
       <c r="Y674" t="n">
-        <v>0.3774091899394989</v>
+        <v>15.44363784790039</v>
       </c>
       <c r="Z674" t="n">
-        <v>0.3605200052261353</v>
+        <v>12.41847896575928</v>
       </c>
     </row>
     <row r="675">
@@ -59910,10 +59910,10 @@
         </is>
       </c>
       <c r="Y675" t="n">
-        <v>0.3773378431797028</v>
+        <v>17.75407791137695</v>
       </c>
       <c r="Z675" t="n">
-        <v>0.3601956963539124</v>
+        <v>14.12594890594482</v>
       </c>
     </row>
     <row r="676">
@@ -60004,10 +60004,10 @@
         </is>
       </c>
       <c r="Y676" t="n">
-        <v>0.3796395361423492</v>
+        <v>25.56500625610352</v>
       </c>
       <c r="Z676" t="n">
-        <v>0.379639208316803</v>
+        <v>25.27832984924316</v>
       </c>
     </row>
     <row r="677">
@@ -60098,10 +60098,10 @@
         </is>
       </c>
       <c r="Y677" t="n">
-        <v>0.3796389997005463</v>
+        <v>26.58609390258789</v>
       </c>
       <c r="Z677" t="n">
-        <v>0.3796383738517761</v>
+        <v>26.08905410766602</v>
       </c>
     </row>
     <row r="678">
@@ -60192,10 +60192,10 @@
         </is>
       </c>
       <c r="Y678" t="n">
-        <v>0.379636824131012</v>
+        <v>25.29642868041992</v>
       </c>
       <c r="Z678" t="n">
-        <v>0.3796377778053284</v>
+        <v>26.0976734161377</v>
       </c>
     </row>
     <row r="679">
@@ -60286,10 +60286,10 @@
         </is>
       </c>
       <c r="Y679" t="n">
-        <v>0.3796359300613403</v>
+        <v>26.18839073181152</v>
       </c>
       <c r="Z679" t="n">
-        <v>0.3796365857124329</v>
+        <v>26.14324569702148</v>
       </c>
     </row>
     <row r="680">
@@ -60380,10 +60380,10 @@
         </is>
       </c>
       <c r="Y680" t="n">
-        <v>0.3796344697475433</v>
+        <v>26.59842109680176</v>
       </c>
       <c r="Z680" t="n">
-        <v>0.3796359002590179</v>
+        <v>26.8259391784668</v>
       </c>
     </row>
     <row r="681">
@@ -60474,10 +60474,10 @@
         </is>
       </c>
       <c r="Y681" t="n">
-        <v>0.3796333074569702</v>
+        <v>26.12145042419434</v>
       </c>
       <c r="Z681" t="n">
-        <v>0.379635363817215</v>
+        <v>26.48382377624512</v>
       </c>
     </row>
     <row r="682">
@@ -60568,10 +60568,10 @@
         </is>
       </c>
       <c r="Y682" t="n">
-        <v>0.3796351253986359</v>
+        <v>22.34661865234375</v>
       </c>
       <c r="Z682" t="n">
-        <v>0.3796371817588806</v>
+        <v>23.18958282470703</v>
       </c>
     </row>
     <row r="683">
@@ -60662,10 +60662,10 @@
         </is>
       </c>
       <c r="Y683" t="n">
-        <v>0.3796302080154419</v>
+        <v>22.10309028625488</v>
       </c>
       <c r="Z683" t="n">
-        <v>0.379634290933609</v>
+        <v>23.51667594909668</v>
       </c>
     </row>
     <row r="684">
@@ -60756,10 +60756,10 @@
         </is>
       </c>
       <c r="Y684" t="n">
-        <v>0.379622220993042</v>
+        <v>22.02896881103516</v>
       </c>
       <c r="Z684" t="n">
-        <v>0.3796315491199493</v>
+        <v>23.37849044799805</v>
       </c>
     </row>
     <row r="685">
@@ -60850,10 +60850,10 @@
         </is>
       </c>
       <c r="Y685" t="n">
-        <v>0.3795991837978363</v>
+        <v>22.30740737915039</v>
       </c>
       <c r="Z685" t="n">
-        <v>0.3796252608299255</v>
+        <v>24.06907272338867</v>
       </c>
     </row>
     <row r="686">
@@ -60944,10 +60944,10 @@
         </is>
       </c>
       <c r="Y686" t="n">
-        <v>0.379585862159729</v>
+        <v>22.37972450256348</v>
       </c>
       <c r="Z686" t="n">
-        <v>0.3796170949935913</v>
+        <v>23.58173942565918</v>
       </c>
     </row>
     <row r="687">
@@ -61038,10 +61038,10 @@
         </is>
       </c>
       <c r="Y687" t="n">
-        <v>0.3795779049396515</v>
+        <v>22.66664695739746</v>
       </c>
       <c r="Z687" t="n">
-        <v>0.3796034753322601</v>
+        <v>22.57014656066895</v>
       </c>
     </row>
     <row r="688">
@@ -61112,10 +61112,10 @@
         </is>
       </c>
       <c r="Y688" t="n">
-        <v>0.3796336948871613</v>
+        <v>22.29329490661621</v>
       </c>
       <c r="Z688" t="n">
-        <v>0.3789829909801483</v>
+        <v>12.64291286468506</v>
       </c>
     </row>
     <row r="689">
@@ -61186,10 +61186,10 @@
         </is>
       </c>
       <c r="Y689" t="n">
-        <v>0.3796273171901703</v>
+        <v>23.32430839538574</v>
       </c>
       <c r="Z689" t="n">
-        <v>0.3783259689807892</v>
+        <v>13.87142086029053</v>
       </c>
     </row>
     <row r="690">
@@ -61260,10 +61260,10 @@
         </is>
       </c>
       <c r="Y690" t="n">
-        <v>0.3796204030513763</v>
+        <v>23.2860050201416</v>
       </c>
       <c r="Z690" t="n">
-        <v>0.3777264356613159</v>
+        <v>14.60142803192139</v>
       </c>
     </row>
     <row r="691">
@@ -61334,10 +61334,10 @@
         </is>
       </c>
       <c r="Y691" t="n">
-        <v>0.3795842528343201</v>
+        <v>23.15373992919922</v>
       </c>
       <c r="Z691" t="n">
-        <v>0.3774888813495636</v>
+        <v>15.6085844039917</v>
       </c>
     </row>
     <row r="692">
@@ -61408,10 +61408,10 @@
         </is>
       </c>
       <c r="Y692" t="n">
-        <v>0.3795760273933411</v>
+        <v>24.28966331481934</v>
       </c>
       <c r="Z692" t="n">
-        <v>0.3764081597328186</v>
+        <v>15.32589912414551</v>
       </c>
     </row>
     <row r="693">
@@ -61482,10 +61482,10 @@
         </is>
       </c>
       <c r="Y693" t="n">
-        <v>0.3795615136623383</v>
+        <v>23.39994239807129</v>
       </c>
       <c r="Z693" t="n">
-        <v>0.3758685886859894</v>
+        <v>15.34484100341797</v>
       </c>
     </row>
     <row r="694">
@@ -61576,10 +61576,10 @@
         </is>
       </c>
       <c r="Y694" t="n">
-        <v>0.3796395361423492</v>
+        <v>25.70004081726074</v>
       </c>
       <c r="Z694" t="n">
-        <v>0.3796396553516388</v>
+        <v>25.94023704528809</v>
       </c>
     </row>
     <row r="695">
@@ -61670,10 +61670,10 @@
         </is>
       </c>
       <c r="Y695" t="n">
-        <v>0.3796389997005463</v>
+        <v>26.39359092712402</v>
       </c>
       <c r="Z695" t="n">
-        <v>0.379639208316803</v>
+        <v>26.58839225769043</v>
       </c>
     </row>
     <row r="696">
@@ -61764,10 +61764,10 @@
         </is>
       </c>
       <c r="Y696" t="n">
-        <v>0.3796384036540985</v>
+        <v>26.23928260803223</v>
       </c>
       <c r="Z696" t="n">
-        <v>0.3796387910842896</v>
+        <v>26.51888275146484</v>
       </c>
     </row>
     <row r="697">
@@ -61858,10 +61858,10 @@
         </is>
       </c>
       <c r="Y697" t="n">
-        <v>0.379637598991394</v>
+        <v>26.43295478820801</v>
       </c>
       <c r="Z697" t="n">
-        <v>0.3796384036540985</v>
+        <v>26.93857383728027</v>
       </c>
     </row>
     <row r="698">
@@ -61952,10 +61952,10 @@
         </is>
       </c>
       <c r="Y698" t="n">
-        <v>0.3796371519565582</v>
+        <v>27.13591194152832</v>
       </c>
       <c r="Z698" t="n">
-        <v>0.3796376585960388</v>
+        <v>26.92402839660645</v>
       </c>
     </row>
     <row r="699">
@@ -62046,10 +62046,10 @@
         </is>
       </c>
       <c r="Y699" t="n">
-        <v>0.3796367943286896</v>
+        <v>26.78843879699707</v>
       </c>
       <c r="Z699" t="n">
-        <v>0.3796367645263672</v>
+        <v>26.23320388793945</v>
       </c>
     </row>
     <row r="700">
@@ -62140,10 +62140,10 @@
         </is>
       </c>
       <c r="Y700" t="n">
-        <v>0.3796364068984985</v>
+        <v>26.88619041442871</v>
       </c>
       <c r="Z700" t="n">
-        <v>0.3796358406543732</v>
+        <v>26.08144187927246</v>
       </c>
     </row>
     <row r="701">
@@ -62234,10 +62234,10 @@
         </is>
       </c>
       <c r="Y701" t="n">
-        <v>0.3796360492706299</v>
+        <v>24.07518196105957</v>
       </c>
       <c r="Z701" t="n">
-        <v>0.3796359896659851</v>
+        <v>23.96012687683105</v>
       </c>
     </row>
     <row r="702">
@@ -62328,10 +62328,10 @@
         </is>
       </c>
       <c r="Y702" t="n">
-        <v>0.3796320259571075</v>
+        <v>23.62908744812012</v>
       </c>
       <c r="Z702" t="n">
-        <v>0.379631906747818</v>
+        <v>23.58460426330566</v>
       </c>
     </row>
     <row r="703">
@@ -62422,10 +62422,10 @@
         </is>
       </c>
       <c r="Y703" t="n">
-        <v>0.3796299695968628</v>
+        <v>24.46705055236816</v>
       </c>
       <c r="Z703" t="n">
-        <v>0.3796293139457703</v>
+        <v>24.19855690002441</v>
       </c>
     </row>
     <row r="704">
@@ -62516,10 +62516,10 @@
         </is>
       </c>
       <c r="Y704" t="n">
-        <v>0.3796293437480927</v>
+        <v>26.66851615905762</v>
       </c>
       <c r="Z704" t="n">
-        <v>0.3796279728412628</v>
+        <v>26.26140213012695</v>
       </c>
     </row>
     <row r="705">
@@ -62610,10 +62610,10 @@
         </is>
       </c>
       <c r="Y705" t="n">
-        <v>0.3796287477016449</v>
+        <v>26.1186351776123</v>
       </c>
       <c r="Z705" t="n">
-        <v>0.3796272277832031</v>
+        <v>25.92453575134277</v>
       </c>
     </row>
     <row r="706">
@@ -62704,10 +62704,10 @@
         </is>
       </c>
       <c r="Y706" t="n">
-        <v>0.3796150088310242</v>
+        <v>19.06824493408203</v>
       </c>
       <c r="Z706" t="n">
-        <v>0.379636138677597</v>
+        <v>23.38454246520996</v>
       </c>
     </row>
     <row r="707">
@@ -62798,10 +62798,10 @@
         </is>
       </c>
       <c r="Y707" t="n">
-        <v>0.3795899450778961</v>
+        <v>18.9037036895752</v>
       </c>
       <c r="Z707" t="n">
-        <v>0.3796322345733643</v>
+        <v>23.5164794921875</v>
       </c>
     </row>
     <row r="708">
@@ -62892,10 +62892,10 @@
         </is>
       </c>
       <c r="Y708" t="n">
-        <v>0.3795836567878723</v>
+        <v>21.74988746643066</v>
       </c>
       <c r="Z708" t="n">
-        <v>0.379630446434021</v>
+        <v>24.49177360534668</v>
       </c>
     </row>
     <row r="709">
@@ -62986,10 +62986,10 @@
         </is>
       </c>
       <c r="Y709" t="n">
-        <v>0.3795806169509888</v>
+        <v>23.3059139251709</v>
       </c>
       <c r="Z709" t="n">
-        <v>0.3796293139457703</v>
+        <v>25.68625068664551</v>
       </c>
     </row>
     <row r="710">
@@ -63080,10 +63080,10 @@
         </is>
       </c>
       <c r="Y710" t="n">
-        <v>0.3796384632587433</v>
+        <v>22.97027015686035</v>
       </c>
       <c r="Z710" t="n">
-        <v>0.3796353340148926</v>
+        <v>21.91373634338379</v>
       </c>
     </row>
     <row r="711">
@@ -63174,10 +63174,10 @@
         </is>
       </c>
       <c r="Y711" t="n">
-        <v>0.3796368539333344</v>
+        <v>24.44923782348633</v>
       </c>
       <c r="Z711" t="n">
-        <v>0.3796306252479553</v>
+        <v>22.36065864562988</v>
       </c>
     </row>
     <row r="712">
@@ -63268,10 +63268,10 @@
         </is>
       </c>
       <c r="Y712" t="n">
-        <v>0.3796328902244568</v>
+        <v>23.32858085632324</v>
       </c>
       <c r="Z712" t="n">
-        <v>0.379618376493454</v>
+        <v>21.90756225585938</v>
       </c>
     </row>
     <row r="713">
@@ -63362,10 +63362,10 @@
         </is>
       </c>
       <c r="Y713" t="n">
-        <v>0.3796287477016449</v>
+        <v>23.53731155395508</v>
       </c>
       <c r="Z713" t="n">
-        <v>0.3796124160289764</v>
+        <v>22.98908233642578</v>
       </c>
     </row>
     <row r="714">
@@ -63456,10 +63456,10 @@
         </is>
       </c>
       <c r="Y714" t="n">
-        <v>0.3796239495277405</v>
+        <v>24.01242637634277</v>
       </c>
       <c r="Z714" t="n">
-        <v>0.3796039223670959</v>
+        <v>23.27971649169922</v>
       </c>
     </row>
     <row r="715">
@@ -63550,10 +63550,10 @@
         </is>
       </c>
       <c r="Y715" t="n">
-        <v>0.379618376493454</v>
+        <v>23.59166526794434</v>
       </c>
       <c r="Z715" t="n">
-        <v>0.3795945644378662</v>
+        <v>22.81867980957031</v>
       </c>
     </row>
     <row r="716">
@@ -63644,10 +63644,10 @@
         </is>
       </c>
       <c r="Y716" t="n">
-        <v>0.3796058893203735</v>
+        <v>22.13145446777344</v>
       </c>
       <c r="Z716" t="n">
-        <v>0.3795712888240814</v>
+        <v>21.23119735717773</v>
       </c>
     </row>
     <row r="717">
@@ -63738,10 +63738,10 @@
         </is>
       </c>
       <c r="Y717" t="n">
-        <v>0.3796389400959015</v>
+        <v>25.04178047180176</v>
       </c>
       <c r="Z717" t="n">
-        <v>0.3796375393867493</v>
+        <v>24.13094902038574</v>
       </c>
     </row>
     <row r="718">
@@ -63832,10 +63832,10 @@
         </is>
       </c>
       <c r="Y718" t="n">
-        <v>0.3796378076076508</v>
+        <v>24.57169342041016</v>
       </c>
       <c r="Z718" t="n">
-        <v>0.3796350061893463</v>
+        <v>23.74309158325195</v>
       </c>
     </row>
     <row r="719">
@@ -63926,10 +63926,10 @@
         </is>
       </c>
       <c r="Y719" t="n">
-        <v>0.3796365857124329</v>
+        <v>24.59177780151367</v>
       </c>
       <c r="Z719" t="n">
-        <v>0.3796328008174896</v>
+        <v>23.96346092224121</v>
       </c>
     </row>
     <row r="720">
@@ -64020,10 +64020,10 @@
         </is>
       </c>
       <c r="Y720" t="n">
-        <v>0.3796345293521881</v>
+        <v>25.51570510864258</v>
       </c>
       <c r="Z720" t="n">
-        <v>0.3796310424804688</v>
+        <v>25.62920951843262</v>
       </c>
     </row>
     <row r="721">
@@ -64114,10 +64114,10 @@
         </is>
       </c>
       <c r="Y721" t="n">
-        <v>0.3796320557594299</v>
+        <v>24.35567665100098</v>
       </c>
       <c r="Z721" t="n">
-        <v>0.3796288967132568</v>
+        <v>24.2381534576416</v>
       </c>
     </row>
     <row r="722">
@@ -64208,10 +64208,10 @@
         </is>
       </c>
       <c r="Y722" t="n">
-        <v>0.3796388804912567</v>
+        <v>25.28373146057129</v>
       </c>
       <c r="Z722" t="n">
-        <v>0.3796384632587433</v>
+        <v>25.01875495910645</v>
       </c>
     </row>
     <row r="723">
@@ -64302,10 +64302,10 @@
         </is>
       </c>
       <c r="Y723" t="n">
-        <v>0.3796377182006836</v>
+        <v>25.26869773864746</v>
       </c>
       <c r="Z723" t="n">
-        <v>0.3796368539333344</v>
+        <v>25.06633567810059</v>
       </c>
     </row>
     <row r="724">
@@ -64396,10 +64396,10 @@
         </is>
       </c>
       <c r="Y724" t="n">
-        <v>0.3796364963054657</v>
+        <v>25.39069557189941</v>
       </c>
       <c r="Z724" t="n">
-        <v>0.3796359300613403</v>
+        <v>25.71960067749023</v>
       </c>
     </row>
     <row r="725">
@@ -64490,10 +64490,10 @@
         </is>
       </c>
       <c r="Y725" t="n">
-        <v>0.3796348869800568</v>
+        <v>25.55705451965332</v>
       </c>
       <c r="Z725" t="n">
-        <v>0.3796325922012329</v>
+        <v>25.02855491638184</v>
       </c>
     </row>
     <row r="726">
@@ -64584,10 +64584,10 @@
         </is>
       </c>
       <c r="Y726" t="n">
-        <v>0.3796332478523254</v>
+        <v>22.22161674499512</v>
       </c>
       <c r="Z726" t="n">
-        <v>0.3791652023792267</v>
+        <v>13.5559196472168</v>
       </c>
     </row>
     <row r="727">
@@ -64678,10 +64678,10 @@
         </is>
       </c>
       <c r="Y727" t="n">
-        <v>0.3796264231204987</v>
+        <v>21.71903610229492</v>
       </c>
       <c r="Z727" t="n">
-        <v>0.3786903917789459</v>
+        <v>14.191162109375</v>
       </c>
     </row>
     <row r="728">
@@ -64772,10 +64772,10 @@
         </is>
       </c>
       <c r="Y728" t="n">
-        <v>0.3796195387840271</v>
+        <v>22.65031242370605</v>
       </c>
       <c r="Z728" t="n">
-        <v>0.3767636120319366</v>
+        <v>13.97451782226562</v>
       </c>
     </row>
     <row r="729">
@@ -64866,10 +64866,10 @@
         </is>
       </c>
       <c r="Y729" t="n">
-        <v>0.3796150982379913</v>
+        <v>23.72080993652344</v>
       </c>
       <c r="Z729" t="n">
-        <v>0.3756164312362671</v>
+        <v>14.17048072814941</v>
       </c>
     </row>
     <row r="730">
@@ -64960,10 +64960,10 @@
         </is>
       </c>
       <c r="Y730" t="n">
-        <v>0.3796055912971497</v>
+        <v>22.92320442199707</v>
       </c>
       <c r="Z730" t="n">
-        <v>0.3738648295402527</v>
+        <v>14.04845714569092</v>
       </c>
     </row>
     <row r="731">
@@ -65054,10 +65054,10 @@
         </is>
       </c>
       <c r="Y731" t="n">
-        <v>0.3795968294143677</v>
+        <v>22.64925384521484</v>
       </c>
       <c r="Z731" t="n">
-        <v>0.3710295557975769</v>
+        <v>13.42728137969971</v>
       </c>
     </row>
     <row r="732">
@@ -65148,10 +65148,10 @@
         </is>
       </c>
       <c r="Y732" t="n">
-        <v>0.379592627286911</v>
+        <v>23.96022033691406</v>
       </c>
       <c r="Z732" t="n">
-        <v>0.3539869487285614</v>
+        <v>13.27117252349854</v>
       </c>
     </row>
     <row r="733">
@@ -65242,10 +65242,10 @@
         </is>
       </c>
       <c r="Y733" t="n">
-        <v>0.379587858915329</v>
+        <v>23.96771812438965</v>
       </c>
       <c r="Z733" t="n">
-        <v>0.3537262976169586</v>
+        <v>14.90072536468506</v>
       </c>
     </row>
     <row r="734">
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="Y734" t="n">
-        <v>0.37958163022995</v>
+        <v>23.73262405395508</v>
       </c>
       <c r="Z734" t="n">
-        <v>0.3483745157718658</v>
+        <v>14.2199068069458</v>
       </c>
     </row>
     <row r="735">
@@ -65430,10 +65430,10 @@
         </is>
       </c>
       <c r="Y735" t="n">
-        <v>0.3795769512653351</v>
+        <v>23.59405136108398</v>
       </c>
       <c r="Z735" t="n">
-        <v>0.3476951122283936</v>
+        <v>14.70248126983643</v>
       </c>
     </row>
     <row r="736">
@@ -65524,10 +65524,10 @@
         </is>
       </c>
       <c r="Y736" t="n">
-        <v>0.3796380460262299</v>
+        <v>24.50899696350098</v>
       </c>
       <c r="Z736" t="n">
-        <v>0.379637211561203</v>
+        <v>24.03313636779785</v>
       </c>
     </row>
     <row r="737">
@@ -65618,10 +65618,10 @@
         </is>
       </c>
       <c r="Y737" t="n">
-        <v>0.3796359896659851</v>
+        <v>24.60687065124512</v>
       </c>
       <c r="Z737" t="n">
-        <v>0.3796343803405762</v>
+        <v>24.26286888122559</v>
       </c>
     </row>
     <row r="738">
@@ -65712,10 +65712,10 @@
         </is>
       </c>
       <c r="Y738" t="n">
-        <v>0.3796345889568329</v>
+        <v>25.17941474914551</v>
       </c>
       <c r="Z738" t="n">
-        <v>0.3796315789222717</v>
+        <v>24.4149055480957</v>
       </c>
     </row>
     <row r="739">
@@ -65806,10 +65806,10 @@
         </is>
       </c>
       <c r="Y739" t="n">
-        <v>0.3796335756778717</v>
+        <v>26.13625144958496</v>
       </c>
       <c r="Z739" t="n">
-        <v>0.3796304166316986</v>
+        <v>25.8900260925293</v>
       </c>
     </row>
     <row r="740">
@@ -65900,10 +65900,10 @@
         </is>
       </c>
       <c r="Y740" t="n">
-        <v>0.3796329200267792</v>
+        <v>26.40428733825684</v>
       </c>
       <c r="Z740" t="n">
-        <v>0.3796289563179016</v>
+        <v>25.83403587341309</v>
       </c>
     </row>
     <row r="741">
@@ -65994,10 +65994,10 @@
         </is>
       </c>
       <c r="Y741" t="n">
-        <v>0.379632294178009</v>
+        <v>26.33637046813965</v>
       </c>
       <c r="Z741" t="n">
-        <v>0.3796267509460449</v>
+        <v>25.4095516204834</v>
       </c>
     </row>
     <row r="742">
@@ -66088,10 +66088,10 @@
         </is>
       </c>
       <c r="Y742" t="n">
-        <v>0.3796311616897583</v>
+        <v>25.76585960388184</v>
       </c>
       <c r="Z742" t="n">
-        <v>0.3796260058879852</v>
+        <v>25.88152694702148</v>
       </c>
     </row>
     <row r="743">
@@ -66161,7 +66161,7 @@
       </c>
       <c r="Y743" t="inlineStr"/>
       <c r="Z743" t="n">
-        <v>0.3796252608299255</v>
+        <v>26.64655494689941</v>
       </c>
     </row>
     <row r="744">
@@ -66252,10 +66252,10 @@
         </is>
       </c>
       <c r="Y744" t="n">
-        <v>0.3003920614719391</v>
+        <v>6.572295188903809</v>
       </c>
       <c r="Z744" t="n">
-        <v>0.3795551657676697</v>
+        <v>17.83967590332031</v>
       </c>
     </row>
     <row r="745">
@@ -66346,10 +66346,10 @@
         </is>
       </c>
       <c r="Y745" t="n">
-        <v>0.2227717936038971</v>
+        <v>8.939478874206543</v>
       </c>
       <c r="Z745" t="n">
-        <v>0.3794702291488647</v>
+        <v>17.83674049377441</v>
       </c>
     </row>
     <row r="746">
@@ -66440,10 +66440,10 @@
         </is>
       </c>
       <c r="Y746" t="n">
-        <v>0.2170917540788651</v>
+        <v>10.68813419342041</v>
       </c>
       <c r="Z746" t="n">
-        <v>0.3794639706611633</v>
+        <v>21.17501640319824</v>
       </c>
     </row>
     <row r="747">
@@ -66534,10 +66534,10 @@
         </is>
       </c>
       <c r="Y747" t="n">
-        <v>0.2170585542917252</v>
+        <v>14.33476066589355</v>
       </c>
       <c r="Z747" t="n">
-        <v>0.3794393539428711</v>
+        <v>20.82868385314941</v>
       </c>
     </row>
     <row r="748">
@@ -66628,10 +66628,10 @@
         </is>
       </c>
       <c r="Y748" t="n">
-        <v>0.2095402628183365</v>
+        <v>12.82844638824463</v>
       </c>
       <c r="Z748" t="n">
-        <v>0.3792467415332794</v>
+        <v>18.77775764465332</v>
       </c>
     </row>
     <row r="749">
@@ -66722,10 +66722,10 @@
         </is>
       </c>
       <c r="Y749" t="n">
-        <v>0.201617956161499</v>
+        <v>12.32282543182373</v>
       </c>
       <c r="Z749" t="n">
-        <v>0.3790777027606964</v>
+        <v>18.63619613647461</v>
       </c>
     </row>
     <row r="750">
@@ -66816,10 +66816,10 @@
         </is>
       </c>
       <c r="Y750" t="n">
-        <v>0.2005864381790161</v>
+        <v>13.25389385223389</v>
       </c>
       <c r="Z750" t="n">
-        <v>0.3788626790046692</v>
+        <v>18.55567169189453</v>
       </c>
     </row>
     <row r="751">
@@ -66910,10 +66910,10 @@
         </is>
       </c>
       <c r="Y751" t="n">
-        <v>0.3796396851539612</v>
+        <v>25.8526782989502</v>
       </c>
       <c r="Z751" t="n">
-        <v>0.3796393573284149</v>
+        <v>25.47167015075684</v>
       </c>
     </row>
     <row r="752">
@@ -67004,10 +67004,10 @@
         </is>
       </c>
       <c r="Y752" t="n">
-        <v>0.3796393275260925</v>
+        <v>26.60293769836426</v>
       </c>
       <c r="Z752" t="n">
-        <v>0.379638671875</v>
+        <v>25.76910972595215</v>
       </c>
     </row>
     <row r="753">
@@ -67098,10 +67098,10 @@
         </is>
       </c>
       <c r="Y753" t="n">
-        <v>0.3796387910842896</v>
+        <v>26.59028434753418</v>
       </c>
       <c r="Z753" t="n">
-        <v>0.379637598991394</v>
+        <v>25.72536468505859</v>
       </c>
     </row>
     <row r="754">
@@ -67192,10 +67192,10 @@
         </is>
       </c>
       <c r="Y754" t="n">
-        <v>0.3796384036540985</v>
+        <v>27.00516700744629</v>
       </c>
       <c r="Z754" t="n">
-        <v>0.3796365261077881</v>
+        <v>26.18591117858887</v>
       </c>
     </row>
     <row r="755">
@@ -67286,10 +67286,10 @@
         </is>
       </c>
       <c r="Y755" t="n">
-        <v>0.3796378672122955</v>
+        <v>26.89594078063965</v>
       </c>
       <c r="Z755" t="n">
-        <v>0.3796348571777344</v>
+        <v>25.90422248840332</v>
       </c>
     </row>
     <row r="756">
@@ -67380,10 +67380,10 @@
         </is>
       </c>
       <c r="Y756" t="n">
-        <v>0.3796391189098358</v>
+        <v>25.64064979553223</v>
       </c>
       <c r="Z756" t="n">
-        <v>0.379639059305191</v>
+        <v>25.4047737121582</v>
       </c>
     </row>
     <row r="757">
@@ -67474,10 +67474,10 @@
         </is>
       </c>
       <c r="Y757" t="n">
-        <v>0.379638135433197</v>
+        <v>25.6744441986084</v>
       </c>
       <c r="Z757" t="n">
-        <v>0.3796380460262299</v>
+        <v>25.28494071960449</v>
       </c>
     </row>
     <row r="758">
@@ -67568,10 +67568,10 @@
         </is>
       </c>
       <c r="Y758" t="n">
-        <v>0.379637598991394</v>
+        <v>25.91632461547852</v>
       </c>
       <c r="Z758" t="n">
-        <v>0.3796367049217224</v>
+        <v>24.94128227233887</v>
       </c>
     </row>
     <row r="759">
@@ -67662,10 +67662,10 @@
         </is>
       </c>
       <c r="Y759" t="n">
-        <v>0.3796368539333344</v>
+        <v>26.99284172058105</v>
       </c>
       <c r="Z759" t="n">
-        <v>0.3796349167823792</v>
+        <v>26.1867733001709</v>
       </c>
     </row>
   </sheetData>
